--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>未知作者</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -44,6 +44,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">202406031900</t>
         </r>
@@ -52,6 +53,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">（开始时间，非必填）
 </t>
@@ -61,6 +63,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">202406032030</t>
         </r>
@@ -69,6 +72,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">（结束时间，非必填）</t>
         </r>
@@ -82,7 +86,55 @@
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">上一次的测试成绩。</t>
+          <t xml:space="preserve">上一次的测试成绩（方便您写评语），</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">fnschool </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">会为您自动更新，如找不到上一次测试的文件，</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">fnschool </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">会填 “</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0”</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">。</t>
         </r>
       </text>
     </comment>
@@ -456,9 +508,8 @@
   <fonts count="11">
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -506,19 +557,20 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -867,7 +919,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="60.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2253,8 +2305,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -93,6 +93,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">fnschool </t>
         </r>
@@ -101,6 +102,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">会为您自动更新，如找不到上一次测试的文件，</t>
         </r>
@@ -109,6 +111,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">fnschool </t>
         </r>
@@ -117,6 +120,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">会填 “</t>
         </r>
@@ -125,6 +129,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">0”</t>
         </r>
@@ -133,6 +138,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">。</t>
         </r>
@@ -146,7 +152,7 @@
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">分数置于标题末尾，格式如“（</t>
+          <t xml:space="preserve">在“考试纪律”列前插入或删除题目列，更新题目标题，分数置于题目末尾，格式如“（</t>
         </r>
         <r>
           <rPr>
@@ -373,7 +379,7 @@
     <t xml:space="preserve">总分</t>
   </si>
   <si>
-    <t xml:space="preserve">期中成绩</t>
+    <t xml:space="preserve">上一次测试</t>
   </si>
   <si>
     <t xml:space="preserve">1、拼音词语（4分）</t>
@@ -500,16 +506,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -557,20 +565,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -587,10 +589,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -625,6 +636,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -654,64 +700,112 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -902,1403 +996,1405 @@
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="13.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="34.99"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="13.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="12.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="12.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="12.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="11.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="12.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="11.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="34.99"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="2" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" s="1" customFormat="true" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="13" t="n">
         <f aca="false">SUM(D2:ZZ2)</f>
         <v>86.5</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="n">
+      <c r="D2" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="15" t="n">
         <v>9.5</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="7"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">SUM(D3:ZZ3)</f>
         <v>87</v>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="9" t="n">
+      <c r="D3" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="K3" s="9" t="n">
+      <c r="K3" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">SUM(D4:ZZ4)</f>
         <v>80</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="19" t="n">
         <v>93.5</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="E4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="9" t="n">
+      <c r="E4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="18" t="n">
         <v>19.5</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="18" t="n">
         <f aca="false">SUM(D5:ZZ5)</f>
         <v>68.5</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="19" t="n">
         <v>87</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="9" t="n">
+      <c r="D5" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="21" t="n">
         <v>7.5</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="18" t="n">
         <f aca="false">SUM(D6:ZZ6)</f>
         <v>81</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="19" t="n">
         <v>90.5</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="9" t="n">
+      <c r="D6" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="18" t="n">
         <f aca="false">SUM(D7:ZZ7)</f>
         <v>82</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="19" t="n">
         <v>97</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="9" t="n">
+      <c r="D7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="18" t="n">
         <v>19.5</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="21" t="n">
         <v>24.5</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="18" t="n">
         <f aca="false">SUM(D8:ZZ8)</f>
         <v>77</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="19" t="n">
         <v>86</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="D8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="9" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">SUM(D9:ZZ9)</f>
         <v>73</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="19" t="n">
         <v>89</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="9" t="n">
+      <c r="D9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="18" t="n">
         <f aca="false">SUM(D10:ZZ10)</f>
         <v>86.5</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="19" t="n">
         <v>93</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="D10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="9" t="n">
+      <c r="H10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="K10" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="21" t="n">
         <v>9.5</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="18" t="n">
         <f aca="false">SUM(D11:ZZ11)</f>
         <v>70</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="19" t="n">
         <v>74.5</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="9" t="n">
+      <c r="F11" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="21" t="n">
         <v>23.5</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="18" t="n">
         <f aca="false">SUM(D12:ZZ12)</f>
         <v>70.5</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="19" t="n">
         <v>75.5</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="9" t="n">
+      <c r="D12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="18" t="n">
         <v>11.5</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="18" t="n">
         <f aca="false">SUM(D13:ZZ13)</f>
         <v>80.5</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="19" t="n">
         <v>88.5</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="9" t="n">
+      <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="L13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="18" t="n">
         <f aca="false">SUM(D14:ZZ14)</f>
         <v>69.5</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="19" t="n">
         <v>78.5</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="9" t="n">
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="21" t="n">
         <v>9.5</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="18" t="n">
         <f aca="false">SUM(D15:ZZ15)</f>
         <v>77.5</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="19" t="n">
         <v>71.5</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="9" t="n">
+      <c r="D15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="21" t="n">
         <v>24.5</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="18" t="n">
         <f aca="false">SUM(D16:ZZ16)</f>
         <v>72.5</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="19" t="n">
         <v>76.5</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="9" t="n">
+      <c r="E16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="20" t="n">
         <v>5.5</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="18" t="n">
         <f aca="false">SUM(D17:ZZ17)</f>
         <v>80</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="19" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="9" t="n">
+      <c r="D17" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="18" t="n">
         <f aca="false">SUM(D18:ZZ18)</f>
         <v>59.5</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="19" t="n">
         <v>70</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D18" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="9" t="n">
+      <c r="F18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="21" t="n">
         <v>7.5</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="18" t="n">
         <f aca="false">SUM(D19:ZZ19)</f>
         <v>49.5</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="19" t="n">
         <v>61</v>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="9" t="n">
+      <c r="D19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="9" t="n">
+      <c r="I19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="18" t="n">
         <f aca="false">SUM(D20:ZZ20)</f>
         <v>29</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="9" t="n">
+      <c r="E20" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="K20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="n">
+      <c r="K20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="18" t="n">
         <f aca="false">SUM(D21:ZZ21)</f>
         <v>34</v>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="19" t="n">
         <v>45</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="n">
+      <c r="E21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="11" t="n">
+      <c r="G21" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="18" t="n">
         <f aca="false">SUM(D22:ZZ22)</f>
         <v>19.5</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="9" t="n">
+      <c r="E22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="9" t="n">
+      <c r="G22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="K22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n">
+      <c r="K22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="N22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="18" t="n">
         <f aca="false">SUM(D23:ZZ23)</f>
         <v>31</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="19" t="n">
         <v>13.5</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="n">
+      <c r="D23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="18" t="n">
         <f aca="false">SUM(D24:ZZ24)</f>
         <v>22</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="19" t="n">
         <v>13.5</v>
       </c>
-      <c r="D24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="9" t="n">
+      <c r="D24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="n">
+      <c r="F24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="18" t="n">
         <f aca="false">SUM(D25:ZZ25)</f>
         <v>11.5</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="19" t="n">
         <v>20.5</v>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="9" t="n">
+      <c r="D25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="9" t="n">
+      <c r="I25" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="n">
+      <c r="K25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="N25" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="18" t="n">
         <f aca="false">SUM(D26:ZZ26)</f>
         <v>19.5</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="19" t="n">
         <v>21.5</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="9" t="n">
+      <c r="D26" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="K26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="n">
+      <c r="K26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
+      <c r="N26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="18" t="n">
         <f aca="false">SUM(D27:ZZ27)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
+      <c r="C27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="3"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3" t="s">
+      <c r="A33" s="25"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="测试0" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="测试" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>未知作者</author>
+    <author>Larry Wei</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -34,6 +34,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">测试信息，格式如：
+————————
 五年级
 语文
 第五单元测试
@@ -74,7 +75,91 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">（结束时间，非必填）</t>
+          <t xml:space="preserve">（结束时间，非必填）
+————————
+单元格内换行：
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">LibreOffice</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ctrl + </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">回车；
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WPS Office</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MS Office</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">： </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Alt + </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">回车。</t>
         </r>
       </text>
     </comment>
@@ -266,7 +351,7 @@
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">一个同学有多多个评语时建议单元格内换行：
+          <t xml:space="preserve">一个同学有多个评语时建议单元格内换行：
 </t>
         </r>
         <r>
@@ -499,7 +584,7 @@
     <t xml:space="preserve">苏二十六</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">平均分</t>
   </si>
 </sst>
 </file>
@@ -512,7 +597,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
@@ -544,21 +629,27 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <name val="AR PL UKai CN"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="AR PL UKai CN"/>
-      <family val="0"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="AR PL UKai CN"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="AR PL UKai CN"/>
       <family val="0"/>
       <charset val="1"/>
@@ -574,13 +665,24 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8CE"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -700,7 +802,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -717,43 +819,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -761,7 +871,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -769,11 +879,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -781,7 +895,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -789,23 +903,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -860,7 +982,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFD8CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -993,7 +1115,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:DB33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.75"/>
@@ -1015,7 +1137,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="2" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="13" customFormat="true" ht="41.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1064,1345 +1186,4181 @@
       <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="12"/>
+      <c r="AN1" s="12"/>
+      <c r="AO1" s="12"/>
+      <c r="AP1" s="12"/>
+      <c r="AQ1" s="12"/>
+      <c r="AR1" s="12"/>
+      <c r="AS1" s="12"/>
+      <c r="AT1" s="12"/>
+      <c r="AU1" s="12"/>
+      <c r="AV1" s="12"/>
+      <c r="AW1" s="12"/>
+      <c r="AX1" s="12"/>
+      <c r="AY1" s="12"/>
+      <c r="AZ1" s="12"/>
+      <c r="BA1" s="12"/>
+      <c r="BB1" s="12"/>
+      <c r="BC1" s="12"/>
+      <c r="BD1" s="12"/>
+      <c r="BE1" s="12"/>
+      <c r="BF1" s="12"/>
+      <c r="BG1" s="12"/>
+      <c r="BH1" s="12"/>
+      <c r="BI1" s="12"/>
+      <c r="BJ1" s="12"/>
+      <c r="BK1" s="12"/>
+      <c r="BL1" s="12"/>
+      <c r="BM1" s="12"/>
+      <c r="BN1" s="12"/>
+      <c r="BO1" s="12"/>
+      <c r="BP1" s="12"/>
+      <c r="BQ1" s="12"/>
+      <c r="BR1" s="12"/>
+      <c r="BS1" s="12"/>
+      <c r="BT1" s="12"/>
+      <c r="BU1" s="12"/>
+      <c r="BV1" s="12"/>
+      <c r="BW1" s="12"/>
+      <c r="BX1" s="12"/>
+      <c r="BY1" s="12"/>
+      <c r="BZ1" s="12"/>
+      <c r="CA1" s="12"/>
+      <c r="CB1" s="12"/>
+      <c r="CC1" s="12"/>
+      <c r="CD1" s="12"/>
+      <c r="CE1" s="12"/>
+      <c r="CF1" s="12"/>
+      <c r="CG1" s="12"/>
+      <c r="CH1" s="12"/>
+      <c r="CI1" s="12"/>
+      <c r="CJ1" s="12"/>
+      <c r="CK1" s="12"/>
+      <c r="CL1" s="12"/>
+      <c r="CM1" s="12"/>
+      <c r="CN1" s="12"/>
+      <c r="CO1" s="12"/>
+      <c r="CP1" s="12"/>
+      <c r="CQ1" s="12"/>
+      <c r="CR1" s="12"/>
+      <c r="CS1" s="12"/>
+      <c r="CT1" s="12"/>
+      <c r="CU1" s="12"/>
+      <c r="CV1" s="12"/>
+      <c r="CW1" s="12"/>
+      <c r="CX1" s="12"/>
+      <c r="CY1" s="12"/>
+      <c r="CZ1" s="12"/>
+      <c r="DA1" s="12"/>
+      <c r="DB1" s="12"/>
     </row>
-    <row r="2" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+    <row r="2" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="13" t="n">
+      <c r="B2" s="15" t="n">
         <f aca="false">SUM(D2:ZZ2)</f>
         <v>86.5</v>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="15" t="n">
+      <c r="H2" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="15" t="n">
+      <c r="I2" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="15" t="n">
+      <c r="J2" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="K2" s="15" t="n">
+      <c r="K2" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="L2" s="15" t="n">
+      <c r="L2" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M2" s="15" t="n">
+      <c r="M2" s="17" t="n">
         <v>9.5</v>
       </c>
-      <c r="N2" s="15" t="n">
+      <c r="N2" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="17"/>
+      <c r="AI2" s="17"/>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
+      <c r="AL2" s="17"/>
+      <c r="AM2" s="17"/>
+      <c r="AN2" s="17"/>
+      <c r="AO2" s="17"/>
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="AR2" s="17"/>
+      <c r="AS2" s="17"/>
+      <c r="AT2" s="17"/>
+      <c r="AU2" s="17"/>
+      <c r="AV2" s="17"/>
+      <c r="AW2" s="17"/>
+      <c r="AX2" s="17"/>
+      <c r="AY2" s="17"/>
+      <c r="AZ2" s="17"/>
+      <c r="BA2" s="17"/>
+      <c r="BB2" s="17"/>
+      <c r="BC2" s="17"/>
+      <c r="BD2" s="17"/>
+      <c r="BE2" s="17"/>
+      <c r="BF2" s="17"/>
+      <c r="BG2" s="17"/>
+      <c r="BH2" s="17"/>
+      <c r="BI2" s="17"/>
+      <c r="BJ2" s="17"/>
+      <c r="BK2" s="17"/>
+      <c r="BL2" s="17"/>
+      <c r="BM2" s="17"/>
+      <c r="BN2" s="17"/>
+      <c r="BO2" s="17"/>
+      <c r="BP2" s="17"/>
+      <c r="BQ2" s="17"/>
+      <c r="BR2" s="17"/>
+      <c r="BS2" s="17"/>
+      <c r="BT2" s="17"/>
+      <c r="BU2" s="17"/>
+      <c r="BV2" s="17"/>
+      <c r="BW2" s="17"/>
+      <c r="BX2" s="17"/>
+      <c r="BY2" s="17"/>
+      <c r="BZ2" s="17"/>
+      <c r="CA2" s="17"/>
+      <c r="CB2" s="17"/>
+      <c r="CC2" s="17"/>
+      <c r="CD2" s="17"/>
+      <c r="CE2" s="17"/>
+      <c r="CF2" s="17"/>
+      <c r="CG2" s="17"/>
+      <c r="CH2" s="17"/>
+      <c r="CI2" s="17"/>
+      <c r="CJ2" s="17"/>
+      <c r="CK2" s="17"/>
+      <c r="CL2" s="17"/>
+      <c r="CM2" s="17"/>
+      <c r="CN2" s="17"/>
+      <c r="CO2" s="17"/>
+      <c r="CP2" s="17"/>
+      <c r="CQ2" s="17"/>
+      <c r="CR2" s="17"/>
+      <c r="CS2" s="17"/>
+      <c r="CT2" s="17"/>
+      <c r="CU2" s="17"/>
+      <c r="CV2" s="17"/>
+      <c r="CW2" s="17"/>
+      <c r="CX2" s="17"/>
+      <c r="CY2" s="17"/>
+      <c r="CZ2" s="17"/>
+      <c r="DA2" s="17"/>
+      <c r="DB2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="21" t="n">
         <f aca="false">SUM(D3:ZZ3)</f>
         <v>87</v>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="22" t="n">
         <v>95</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L3" s="20" t="n">
+      <c r="L3" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="M3" s="21" t="n">
+      <c r="M3" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="21" t="n">
+      <c r="N3" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
+      <c r="BD3" s="25"/>
+      <c r="BE3" s="25"/>
+      <c r="BF3" s="25"/>
+      <c r="BG3" s="25"/>
+      <c r="BH3" s="25"/>
+      <c r="BI3" s="25"/>
+      <c r="BJ3" s="25"/>
+      <c r="BK3" s="25"/>
+      <c r="BL3" s="25"/>
+      <c r="BM3" s="25"/>
+      <c r="BN3" s="25"/>
+      <c r="BO3" s="25"/>
+      <c r="BP3" s="25"/>
+      <c r="BQ3" s="25"/>
+      <c r="BR3" s="25"/>
+      <c r="BS3" s="25"/>
+      <c r="BT3" s="25"/>
+      <c r="BU3" s="25"/>
+      <c r="BV3" s="25"/>
+      <c r="BW3" s="25"/>
+      <c r="BX3" s="25"/>
+      <c r="BY3" s="25"/>
+      <c r="BZ3" s="25"/>
+      <c r="CA3" s="25"/>
+      <c r="CB3" s="25"/>
+      <c r="CC3" s="25"/>
+      <c r="CD3" s="25"/>
+      <c r="CE3" s="25"/>
+      <c r="CF3" s="25"/>
+      <c r="CG3" s="25"/>
+      <c r="CH3" s="25"/>
+      <c r="CI3" s="25"/>
+      <c r="CJ3" s="25"/>
+      <c r="CK3" s="25"/>
+      <c r="CL3" s="25"/>
+      <c r="CM3" s="25"/>
+      <c r="CN3" s="25"/>
+      <c r="CO3" s="25"/>
+      <c r="CP3" s="25"/>
+      <c r="CQ3" s="25"/>
+      <c r="CR3" s="25"/>
+      <c r="CS3" s="25"/>
+      <c r="CT3" s="25"/>
+      <c r="CU3" s="25"/>
+      <c r="CV3" s="25"/>
+      <c r="CW3" s="25"/>
+      <c r="CX3" s="25"/>
+      <c r="CY3" s="25"/>
+      <c r="CZ3" s="25"/>
+      <c r="DA3" s="25"/>
+      <c r="DB3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="21" t="n">
         <f aca="false">SUM(D4:ZZ4)</f>
         <v>80</v>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="22" t="n">
         <v>93.5</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="21" t="n">
         <v>19.5</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="20" t="n">
+      <c r="L4" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M4" s="21" t="n">
+      <c r="M4" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="21" t="n">
+      <c r="N4" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25"/>
+      <c r="AC4" s="25"/>
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="25"/>
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="25"/>
+      <c r="AJ4" s="25"/>
+      <c r="AK4" s="25"/>
+      <c r="AL4" s="25"/>
+      <c r="AM4" s="25"/>
+      <c r="AN4" s="25"/>
+      <c r="AO4" s="25"/>
+      <c r="AP4" s="25"/>
+      <c r="AQ4" s="25"/>
+      <c r="AR4" s="25"/>
+      <c r="AS4" s="25"/>
+      <c r="AT4" s="25"/>
+      <c r="AU4" s="25"/>
+      <c r="AV4" s="25"/>
+      <c r="AW4" s="25"/>
+      <c r="AX4" s="25"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25"/>
+      <c r="BD4" s="25"/>
+      <c r="BE4" s="25"/>
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="25"/>
+      <c r="BH4" s="25"/>
+      <c r="BI4" s="25"/>
+      <c r="BJ4" s="25"/>
+      <c r="BK4" s="25"/>
+      <c r="BL4" s="25"/>
+      <c r="BM4" s="25"/>
+      <c r="BN4" s="25"/>
+      <c r="BO4" s="25"/>
+      <c r="BP4" s="25"/>
+      <c r="BQ4" s="25"/>
+      <c r="BR4" s="25"/>
+      <c r="BS4" s="25"/>
+      <c r="BT4" s="25"/>
+      <c r="BU4" s="25"/>
+      <c r="BV4" s="25"/>
+      <c r="BW4" s="25"/>
+      <c r="BX4" s="25"/>
+      <c r="BY4" s="25"/>
+      <c r="BZ4" s="25"/>
+      <c r="CA4" s="25"/>
+      <c r="CB4" s="25"/>
+      <c r="CC4" s="25"/>
+      <c r="CD4" s="25"/>
+      <c r="CE4" s="25"/>
+      <c r="CF4" s="25"/>
+      <c r="CG4" s="25"/>
+      <c r="CH4" s="25"/>
+      <c r="CI4" s="25"/>
+      <c r="CJ4" s="25"/>
+      <c r="CK4" s="25"/>
+      <c r="CL4" s="25"/>
+      <c r="CM4" s="25"/>
+      <c r="CN4" s="25"/>
+      <c r="CO4" s="25"/>
+      <c r="CP4" s="25"/>
+      <c r="CQ4" s="25"/>
+      <c r="CR4" s="25"/>
+      <c r="CS4" s="25"/>
+      <c r="CT4" s="25"/>
+      <c r="CU4" s="25"/>
+      <c r="CV4" s="25"/>
+      <c r="CW4" s="25"/>
+      <c r="CX4" s="25"/>
+      <c r="CY4" s="25"/>
+      <c r="CZ4" s="25"/>
+      <c r="DA4" s="25"/>
+      <c r="DB4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="21" t="n">
         <f aca="false">SUM(D5:ZZ5)</f>
         <v>68.5</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="22" t="n">
         <v>87</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L5" s="20" t="n">
+      <c r="L5" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="M5" s="21" t="n">
+      <c r="M5" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="N5" s="21" t="n">
+      <c r="N5" s="24" t="n">
         <v>24</v>
       </c>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+      <c r="AG5" s="25"/>
+      <c r="AH5" s="25"/>
+      <c r="AI5" s="25"/>
+      <c r="AJ5" s="25"/>
+      <c r="AK5" s="25"/>
+      <c r="AL5" s="25"/>
+      <c r="AM5" s="25"/>
+      <c r="AN5" s="25"/>
+      <c r="AO5" s="25"/>
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="25"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="25"/>
+      <c r="AV5" s="25"/>
+      <c r="AW5" s="25"/>
+      <c r="AX5" s="25"/>
+      <c r="AY5" s="25"/>
+      <c r="AZ5" s="25"/>
+      <c r="BA5" s="25"/>
+      <c r="BB5" s="25"/>
+      <c r="BC5" s="25"/>
+      <c r="BD5" s="25"/>
+      <c r="BE5" s="25"/>
+      <c r="BF5" s="25"/>
+      <c r="BG5" s="25"/>
+      <c r="BH5" s="25"/>
+      <c r="BI5" s="25"/>
+      <c r="BJ5" s="25"/>
+      <c r="BK5" s="25"/>
+      <c r="BL5" s="25"/>
+      <c r="BM5" s="25"/>
+      <c r="BN5" s="25"/>
+      <c r="BO5" s="25"/>
+      <c r="BP5" s="25"/>
+      <c r="BQ5" s="25"/>
+      <c r="BR5" s="25"/>
+      <c r="BS5" s="25"/>
+      <c r="BT5" s="25"/>
+      <c r="BU5" s="25"/>
+      <c r="BV5" s="25"/>
+      <c r="BW5" s="25"/>
+      <c r="BX5" s="25"/>
+      <c r="BY5" s="25"/>
+      <c r="BZ5" s="25"/>
+      <c r="CA5" s="25"/>
+      <c r="CB5" s="25"/>
+      <c r="CC5" s="25"/>
+      <c r="CD5" s="25"/>
+      <c r="CE5" s="25"/>
+      <c r="CF5" s="25"/>
+      <c r="CG5" s="25"/>
+      <c r="CH5" s="25"/>
+      <c r="CI5" s="25"/>
+      <c r="CJ5" s="25"/>
+      <c r="CK5" s="25"/>
+      <c r="CL5" s="25"/>
+      <c r="CM5" s="25"/>
+      <c r="CN5" s="25"/>
+      <c r="CO5" s="25"/>
+      <c r="CP5" s="25"/>
+      <c r="CQ5" s="25"/>
+      <c r="CR5" s="25"/>
+      <c r="CS5" s="25"/>
+      <c r="CT5" s="25"/>
+      <c r="CU5" s="25"/>
+      <c r="CV5" s="25"/>
+      <c r="CW5" s="25"/>
+      <c r="CX5" s="25"/>
+      <c r="CY5" s="25"/>
+      <c r="CZ5" s="25"/>
+      <c r="DA5" s="25"/>
+      <c r="DB5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="21" t="n">
         <f aca="false">SUM(D6:ZZ6)</f>
         <v>81</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="22" t="n">
         <v>90.5</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="L6" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="21" t="n">
+      <c r="M6" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="N6" s="21" t="n">
+      <c r="N6" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AL6" s="25"/>
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="25"/>
+      <c r="AO6" s="25"/>
+      <c r="AP6" s="25"/>
+      <c r="AQ6" s="25"/>
+      <c r="AR6" s="25"/>
+      <c r="AS6" s="25"/>
+      <c r="AT6" s="25"/>
+      <c r="AU6" s="25"/>
+      <c r="AV6" s="25"/>
+      <c r="AW6" s="25"/>
+      <c r="AX6" s="25"/>
+      <c r="AY6" s="25"/>
+      <c r="AZ6" s="25"/>
+      <c r="BA6" s="25"/>
+      <c r="BB6" s="25"/>
+      <c r="BC6" s="25"/>
+      <c r="BD6" s="25"/>
+      <c r="BE6" s="25"/>
+      <c r="BF6" s="25"/>
+      <c r="BG6" s="25"/>
+      <c r="BH6" s="25"/>
+      <c r="BI6" s="25"/>
+      <c r="BJ6" s="25"/>
+      <c r="BK6" s="25"/>
+      <c r="BL6" s="25"/>
+      <c r="BM6" s="25"/>
+      <c r="BN6" s="25"/>
+      <c r="BO6" s="25"/>
+      <c r="BP6" s="25"/>
+      <c r="BQ6" s="25"/>
+      <c r="BR6" s="25"/>
+      <c r="BS6" s="25"/>
+      <c r="BT6" s="25"/>
+      <c r="BU6" s="25"/>
+      <c r="BV6" s="25"/>
+      <c r="BW6" s="25"/>
+      <c r="BX6" s="25"/>
+      <c r="BY6" s="25"/>
+      <c r="BZ6" s="25"/>
+      <c r="CA6" s="25"/>
+      <c r="CB6" s="25"/>
+      <c r="CC6" s="25"/>
+      <c r="CD6" s="25"/>
+      <c r="CE6" s="25"/>
+      <c r="CF6" s="25"/>
+      <c r="CG6" s="25"/>
+      <c r="CH6" s="25"/>
+      <c r="CI6" s="25"/>
+      <c r="CJ6" s="25"/>
+      <c r="CK6" s="25"/>
+      <c r="CL6" s="25"/>
+      <c r="CM6" s="25"/>
+      <c r="CN6" s="25"/>
+      <c r="CO6" s="25"/>
+      <c r="CP6" s="25"/>
+      <c r="CQ6" s="25"/>
+      <c r="CR6" s="25"/>
+      <c r="CS6" s="25"/>
+      <c r="CT6" s="25"/>
+      <c r="CU6" s="25"/>
+      <c r="CV6" s="25"/>
+      <c r="CW6" s="25"/>
+      <c r="CX6" s="25"/>
+      <c r="CY6" s="25"/>
+      <c r="CZ6" s="25"/>
+      <c r="DA6" s="25"/>
+      <c r="DB6" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="21" t="n">
         <f aca="false">SUM(D7:ZZ7)</f>
         <v>82</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="22" t="n">
         <v>97</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="21" t="n">
         <v>19.5</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="L7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M7" s="21" t="n">
+      <c r="M7" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="N7" s="21" t="n">
+      <c r="N7" s="24" t="n">
         <v>24.5</v>
       </c>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="25"/>
+      <c r="AI7" s="25"/>
+      <c r="AJ7" s="25"/>
+      <c r="AK7" s="25"/>
+      <c r="AL7" s="25"/>
+      <c r="AM7" s="25"/>
+      <c r="AN7" s="25"/>
+      <c r="AO7" s="25"/>
+      <c r="AP7" s="25"/>
+      <c r="AQ7" s="25"/>
+      <c r="AR7" s="25"/>
+      <c r="AS7" s="25"/>
+      <c r="AT7" s="25"/>
+      <c r="AU7" s="25"/>
+      <c r="AV7" s="25"/>
+      <c r="AW7" s="25"/>
+      <c r="AX7" s="25"/>
+      <c r="AY7" s="25"/>
+      <c r="AZ7" s="25"/>
+      <c r="BA7" s="25"/>
+      <c r="BB7" s="25"/>
+      <c r="BC7" s="25"/>
+      <c r="BD7" s="25"/>
+      <c r="BE7" s="25"/>
+      <c r="BF7" s="25"/>
+      <c r="BG7" s="25"/>
+      <c r="BH7" s="25"/>
+      <c r="BI7" s="25"/>
+      <c r="BJ7" s="25"/>
+      <c r="BK7" s="25"/>
+      <c r="BL7" s="25"/>
+      <c r="BM7" s="25"/>
+      <c r="BN7" s="25"/>
+      <c r="BO7" s="25"/>
+      <c r="BP7" s="25"/>
+      <c r="BQ7" s="25"/>
+      <c r="BR7" s="25"/>
+      <c r="BS7" s="25"/>
+      <c r="BT7" s="25"/>
+      <c r="BU7" s="25"/>
+      <c r="BV7" s="25"/>
+      <c r="BW7" s="25"/>
+      <c r="BX7" s="25"/>
+      <c r="BY7" s="25"/>
+      <c r="BZ7" s="25"/>
+      <c r="CA7" s="25"/>
+      <c r="CB7" s="25"/>
+      <c r="CC7" s="25"/>
+      <c r="CD7" s="25"/>
+      <c r="CE7" s="25"/>
+      <c r="CF7" s="25"/>
+      <c r="CG7" s="25"/>
+      <c r="CH7" s="25"/>
+      <c r="CI7" s="25"/>
+      <c r="CJ7" s="25"/>
+      <c r="CK7" s="25"/>
+      <c r="CL7" s="25"/>
+      <c r="CM7" s="25"/>
+      <c r="CN7" s="25"/>
+      <c r="CO7" s="25"/>
+      <c r="CP7" s="25"/>
+      <c r="CQ7" s="25"/>
+      <c r="CR7" s="25"/>
+      <c r="CS7" s="25"/>
+      <c r="CT7" s="25"/>
+      <c r="CU7" s="25"/>
+      <c r="CV7" s="25"/>
+      <c r="CW7" s="25"/>
+      <c r="CX7" s="25"/>
+      <c r="CY7" s="25"/>
+      <c r="CZ7" s="25"/>
+      <c r="DA7" s="25"/>
+      <c r="DB7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="21" t="n">
         <f aca="false">SUM(D8:ZZ8)</f>
         <v>77</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="22" t="n">
         <v>86</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="20" t="n">
+      <c r="L8" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M8" s="21" t="n">
+      <c r="M8" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="N8" s="21" t="n">
+      <c r="N8" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="25"/>
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="25"/>
+      <c r="AR8" s="25"/>
+      <c r="AS8" s="25"/>
+      <c r="AT8" s="25"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="25"/>
+      <c r="AW8" s="25"/>
+      <c r="AX8" s="25"/>
+      <c r="AY8" s="25"/>
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="25"/>
+      <c r="BB8" s="25"/>
+      <c r="BC8" s="25"/>
+      <c r="BD8" s="25"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="25"/>
+      <c r="BG8" s="25"/>
+      <c r="BH8" s="25"/>
+      <c r="BI8" s="25"/>
+      <c r="BJ8" s="25"/>
+      <c r="BK8" s="25"/>
+      <c r="BL8" s="25"/>
+      <c r="BM8" s="25"/>
+      <c r="BN8" s="25"/>
+      <c r="BO8" s="25"/>
+      <c r="BP8" s="25"/>
+      <c r="BQ8" s="25"/>
+      <c r="BR8" s="25"/>
+      <c r="BS8" s="25"/>
+      <c r="BT8" s="25"/>
+      <c r="BU8" s="25"/>
+      <c r="BV8" s="25"/>
+      <c r="BW8" s="25"/>
+      <c r="BX8" s="25"/>
+      <c r="BY8" s="25"/>
+      <c r="BZ8" s="25"/>
+      <c r="CA8" s="25"/>
+      <c r="CB8" s="25"/>
+      <c r="CC8" s="25"/>
+      <c r="CD8" s="25"/>
+      <c r="CE8" s="25"/>
+      <c r="CF8" s="25"/>
+      <c r="CG8" s="25"/>
+      <c r="CH8" s="25"/>
+      <c r="CI8" s="25"/>
+      <c r="CJ8" s="25"/>
+      <c r="CK8" s="25"/>
+      <c r="CL8" s="25"/>
+      <c r="CM8" s="25"/>
+      <c r="CN8" s="25"/>
+      <c r="CO8" s="25"/>
+      <c r="CP8" s="25"/>
+      <c r="CQ8" s="25"/>
+      <c r="CR8" s="25"/>
+      <c r="CS8" s="25"/>
+      <c r="CT8" s="25"/>
+      <c r="CU8" s="25"/>
+      <c r="CV8" s="25"/>
+      <c r="CW8" s="25"/>
+      <c r="CX8" s="25"/>
+      <c r="CY8" s="25"/>
+      <c r="CZ8" s="25"/>
+      <c r="DA8" s="25"/>
+      <c r="DB8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="21" t="n">
         <f aca="false">SUM(D9:ZZ9)</f>
         <v>73</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="22" t="n">
         <v>89</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M9" s="21" t="n">
+      <c r="M9" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="21" t="n">
+      <c r="N9" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="25"/>
+      <c r="AL9" s="25"/>
+      <c r="AM9" s="25"/>
+      <c r="AN9" s="25"/>
+      <c r="AO9" s="25"/>
+      <c r="AP9" s="25"/>
+      <c r="AQ9" s="25"/>
+      <c r="AR9" s="25"/>
+      <c r="AS9" s="25"/>
+      <c r="AT9" s="25"/>
+      <c r="AU9" s="25"/>
+      <c r="AV9" s="25"/>
+      <c r="AW9" s="25"/>
+      <c r="AX9" s="25"/>
+      <c r="AY9" s="25"/>
+      <c r="AZ9" s="25"/>
+      <c r="BA9" s="25"/>
+      <c r="BB9" s="25"/>
+      <c r="BC9" s="25"/>
+      <c r="BD9" s="25"/>
+      <c r="BE9" s="25"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="25"/>
+      <c r="BI9" s="25"/>
+      <c r="BJ9" s="25"/>
+      <c r="BK9" s="25"/>
+      <c r="BL9" s="25"/>
+      <c r="BM9" s="25"/>
+      <c r="BN9" s="25"/>
+      <c r="BO9" s="25"/>
+      <c r="BP9" s="25"/>
+      <c r="BQ9" s="25"/>
+      <c r="BR9" s="25"/>
+      <c r="BS9" s="25"/>
+      <c r="BT9" s="25"/>
+      <c r="BU9" s="25"/>
+      <c r="BV9" s="25"/>
+      <c r="BW9" s="25"/>
+      <c r="BX9" s="25"/>
+      <c r="BY9" s="25"/>
+      <c r="BZ9" s="25"/>
+      <c r="CA9" s="25"/>
+      <c r="CB9" s="25"/>
+      <c r="CC9" s="25"/>
+      <c r="CD9" s="25"/>
+      <c r="CE9" s="25"/>
+      <c r="CF9" s="25"/>
+      <c r="CG9" s="25"/>
+      <c r="CH9" s="25"/>
+      <c r="CI9" s="25"/>
+      <c r="CJ9" s="25"/>
+      <c r="CK9" s="25"/>
+      <c r="CL9" s="25"/>
+      <c r="CM9" s="25"/>
+      <c r="CN9" s="25"/>
+      <c r="CO9" s="25"/>
+      <c r="CP9" s="25"/>
+      <c r="CQ9" s="25"/>
+      <c r="CR9" s="25"/>
+      <c r="CS9" s="25"/>
+      <c r="CT9" s="25"/>
+      <c r="CU9" s="25"/>
+      <c r="CV9" s="25"/>
+      <c r="CW9" s="25"/>
+      <c r="CX9" s="25"/>
+      <c r="CY9" s="25"/>
+      <c r="CZ9" s="25"/>
+      <c r="DA9" s="25"/>
+      <c r="DB9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="21" t="n">
         <f aca="false">SUM(D10:ZZ10)</f>
         <v>86.5</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="22" t="n">
         <v>93</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="K10" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="L10" s="21" t="n">
+      <c r="L10" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="21" t="n">
+      <c r="M10" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="N10" s="21" t="n">
+      <c r="N10" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="P10" s="21"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="25"/>
+      <c r="AM10" s="25"/>
+      <c r="AN10" s="25"/>
+      <c r="AO10" s="25"/>
+      <c r="AP10" s="25"/>
+      <c r="AQ10" s="25"/>
+      <c r="AR10" s="25"/>
+      <c r="AS10" s="25"/>
+      <c r="AT10" s="25"/>
+      <c r="AU10" s="25"/>
+      <c r="AV10" s="25"/>
+      <c r="AW10" s="25"/>
+      <c r="AX10" s="25"/>
+      <c r="AY10" s="25"/>
+      <c r="AZ10" s="25"/>
+      <c r="BA10" s="25"/>
+      <c r="BB10" s="25"/>
+      <c r="BC10" s="25"/>
+      <c r="BD10" s="25"/>
+      <c r="BE10" s="25"/>
+      <c r="BF10" s="25"/>
+      <c r="BG10" s="25"/>
+      <c r="BH10" s="25"/>
+      <c r="BI10" s="25"/>
+      <c r="BJ10" s="25"/>
+      <c r="BK10" s="25"/>
+      <c r="BL10" s="25"/>
+      <c r="BM10" s="25"/>
+      <c r="BN10" s="25"/>
+      <c r="BO10" s="25"/>
+      <c r="BP10" s="25"/>
+      <c r="BQ10" s="25"/>
+      <c r="BR10" s="25"/>
+      <c r="BS10" s="25"/>
+      <c r="BT10" s="25"/>
+      <c r="BU10" s="25"/>
+      <c r="BV10" s="25"/>
+      <c r="BW10" s="25"/>
+      <c r="BX10" s="25"/>
+      <c r="BY10" s="25"/>
+      <c r="BZ10" s="25"/>
+      <c r="CA10" s="25"/>
+      <c r="CB10" s="25"/>
+      <c r="CC10" s="25"/>
+      <c r="CD10" s="25"/>
+      <c r="CE10" s="25"/>
+      <c r="CF10" s="25"/>
+      <c r="CG10" s="25"/>
+      <c r="CH10" s="25"/>
+      <c r="CI10" s="25"/>
+      <c r="CJ10" s="25"/>
+      <c r="CK10" s="25"/>
+      <c r="CL10" s="25"/>
+      <c r="CM10" s="25"/>
+      <c r="CN10" s="25"/>
+      <c r="CO10" s="25"/>
+      <c r="CP10" s="25"/>
+      <c r="CQ10" s="25"/>
+      <c r="CR10" s="25"/>
+      <c r="CS10" s="25"/>
+      <c r="CT10" s="25"/>
+      <c r="CU10" s="25"/>
+      <c r="CV10" s="25"/>
+      <c r="CW10" s="25"/>
+      <c r="CX10" s="25"/>
+      <c r="CY10" s="25"/>
+      <c r="CZ10" s="25"/>
+      <c r="DA10" s="25"/>
+      <c r="DB10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="21" t="n">
         <f aca="false">SUM(D11:ZZ11)</f>
         <v>70</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="22" t="n">
         <v>74.5</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="K11" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="L11" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="21" t="n">
+      <c r="M11" s="24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" s="21" t="n">
+      <c r="N11" s="24" t="n">
         <v>23.5</v>
       </c>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+      <c r="AK11" s="25"/>
+      <c r="AL11" s="25"/>
+      <c r="AM11" s="25"/>
+      <c r="AN11" s="25"/>
+      <c r="AO11" s="25"/>
+      <c r="AP11" s="25"/>
+      <c r="AQ11" s="25"/>
+      <c r="AR11" s="25"/>
+      <c r="AS11" s="25"/>
+      <c r="AT11" s="25"/>
+      <c r="AU11" s="25"/>
+      <c r="AV11" s="25"/>
+      <c r="AW11" s="25"/>
+      <c r="AX11" s="25"/>
+      <c r="AY11" s="25"/>
+      <c r="AZ11" s="25"/>
+      <c r="BA11" s="25"/>
+      <c r="BB11" s="25"/>
+      <c r="BC11" s="25"/>
+      <c r="BD11" s="25"/>
+      <c r="BE11" s="25"/>
+      <c r="BF11" s="25"/>
+      <c r="BG11" s="25"/>
+      <c r="BH11" s="25"/>
+      <c r="BI11" s="25"/>
+      <c r="BJ11" s="25"/>
+      <c r="BK11" s="25"/>
+      <c r="BL11" s="25"/>
+      <c r="BM11" s="25"/>
+      <c r="BN11" s="25"/>
+      <c r="BO11" s="25"/>
+      <c r="BP11" s="25"/>
+      <c r="BQ11" s="25"/>
+      <c r="BR11" s="25"/>
+      <c r="BS11" s="25"/>
+      <c r="BT11" s="25"/>
+      <c r="BU11" s="25"/>
+      <c r="BV11" s="25"/>
+      <c r="BW11" s="25"/>
+      <c r="BX11" s="25"/>
+      <c r="BY11" s="25"/>
+      <c r="BZ11" s="25"/>
+      <c r="CA11" s="25"/>
+      <c r="CB11" s="25"/>
+      <c r="CC11" s="25"/>
+      <c r="CD11" s="25"/>
+      <c r="CE11" s="25"/>
+      <c r="CF11" s="25"/>
+      <c r="CG11" s="25"/>
+      <c r="CH11" s="25"/>
+      <c r="CI11" s="25"/>
+      <c r="CJ11" s="25"/>
+      <c r="CK11" s="25"/>
+      <c r="CL11" s="25"/>
+      <c r="CM11" s="25"/>
+      <c r="CN11" s="25"/>
+      <c r="CO11" s="25"/>
+      <c r="CP11" s="25"/>
+      <c r="CQ11" s="25"/>
+      <c r="CR11" s="25"/>
+      <c r="CS11" s="25"/>
+      <c r="CT11" s="25"/>
+      <c r="CU11" s="25"/>
+      <c r="CV11" s="25"/>
+      <c r="CW11" s="25"/>
+      <c r="CX11" s="25"/>
+      <c r="CY11" s="25"/>
+      <c r="CZ11" s="25"/>
+      <c r="DA11" s="25"/>
+      <c r="DB11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="21" t="n">
         <f aca="false">SUM(D12:ZZ12)</f>
         <v>70.5</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="22" t="n">
         <v>75.5</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="21" t="n">
         <v>11.5</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="20" t="n">
+      <c r="L12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="M12" s="21" t="n">
+      <c r="M12" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="21" t="n">
+      <c r="N12" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="25"/>
+      <c r="AK12" s="25"/>
+      <c r="AL12" s="25"/>
+      <c r="AM12" s="25"/>
+      <c r="AN12" s="25"/>
+      <c r="AO12" s="25"/>
+      <c r="AP12" s="25"/>
+      <c r="AQ12" s="25"/>
+      <c r="AR12" s="25"/>
+      <c r="AS12" s="25"/>
+      <c r="AT12" s="25"/>
+      <c r="AU12" s="25"/>
+      <c r="AV12" s="25"/>
+      <c r="AW12" s="25"/>
+      <c r="AX12" s="25"/>
+      <c r="AY12" s="25"/>
+      <c r="AZ12" s="25"/>
+      <c r="BA12" s="25"/>
+      <c r="BB12" s="25"/>
+      <c r="BC12" s="25"/>
+      <c r="BD12" s="25"/>
+      <c r="BE12" s="25"/>
+      <c r="BF12" s="25"/>
+      <c r="BG12" s="25"/>
+      <c r="BH12" s="25"/>
+      <c r="BI12" s="25"/>
+      <c r="BJ12" s="25"/>
+      <c r="BK12" s="25"/>
+      <c r="BL12" s="25"/>
+      <c r="BM12" s="25"/>
+      <c r="BN12" s="25"/>
+      <c r="BO12" s="25"/>
+      <c r="BP12" s="25"/>
+      <c r="BQ12" s="25"/>
+      <c r="BR12" s="25"/>
+      <c r="BS12" s="25"/>
+      <c r="BT12" s="25"/>
+      <c r="BU12" s="25"/>
+      <c r="BV12" s="25"/>
+      <c r="BW12" s="25"/>
+      <c r="BX12" s="25"/>
+      <c r="BY12" s="25"/>
+      <c r="BZ12" s="25"/>
+      <c r="CA12" s="25"/>
+      <c r="CB12" s="25"/>
+      <c r="CC12" s="25"/>
+      <c r="CD12" s="25"/>
+      <c r="CE12" s="25"/>
+      <c r="CF12" s="25"/>
+      <c r="CG12" s="25"/>
+      <c r="CH12" s="25"/>
+      <c r="CI12" s="25"/>
+      <c r="CJ12" s="25"/>
+      <c r="CK12" s="25"/>
+      <c r="CL12" s="25"/>
+      <c r="CM12" s="25"/>
+      <c r="CN12" s="25"/>
+      <c r="CO12" s="25"/>
+      <c r="CP12" s="25"/>
+      <c r="CQ12" s="25"/>
+      <c r="CR12" s="25"/>
+      <c r="CS12" s="25"/>
+      <c r="CT12" s="25"/>
+      <c r="CU12" s="25"/>
+      <c r="CV12" s="25"/>
+      <c r="CW12" s="25"/>
+      <c r="CX12" s="25"/>
+      <c r="CY12" s="25"/>
+      <c r="CZ12" s="25"/>
+      <c r="DA12" s="25"/>
+      <c r="DB12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="21" t="n">
         <f aca="false">SUM(D13:ZZ13)</f>
         <v>80.5</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="22" t="n">
         <v>88.5</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K13" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L13" s="20" t="n">
+      <c r="L13" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M13" s="21" t="n">
+      <c r="M13" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="N13" s="21" t="n">
+      <c r="N13" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="25"/>
+      <c r="AK13" s="25"/>
+      <c r="AL13" s="25"/>
+      <c r="AM13" s="25"/>
+      <c r="AN13" s="25"/>
+      <c r="AO13" s="25"/>
+      <c r="AP13" s="25"/>
+      <c r="AQ13" s="25"/>
+      <c r="AR13" s="25"/>
+      <c r="AS13" s="25"/>
+      <c r="AT13" s="25"/>
+      <c r="AU13" s="25"/>
+      <c r="AV13" s="25"/>
+      <c r="AW13" s="25"/>
+      <c r="AX13" s="25"/>
+      <c r="AY13" s="25"/>
+      <c r="AZ13" s="25"/>
+      <c r="BA13" s="25"/>
+      <c r="BB13" s="25"/>
+      <c r="BC13" s="25"/>
+      <c r="BD13" s="25"/>
+      <c r="BE13" s="25"/>
+      <c r="BF13" s="25"/>
+      <c r="BG13" s="25"/>
+      <c r="BH13" s="25"/>
+      <c r="BI13" s="25"/>
+      <c r="BJ13" s="25"/>
+      <c r="BK13" s="25"/>
+      <c r="BL13" s="25"/>
+      <c r="BM13" s="25"/>
+      <c r="BN13" s="25"/>
+      <c r="BO13" s="25"/>
+      <c r="BP13" s="25"/>
+      <c r="BQ13" s="25"/>
+      <c r="BR13" s="25"/>
+      <c r="BS13" s="25"/>
+      <c r="BT13" s="25"/>
+      <c r="BU13" s="25"/>
+      <c r="BV13" s="25"/>
+      <c r="BW13" s="25"/>
+      <c r="BX13" s="25"/>
+      <c r="BY13" s="25"/>
+      <c r="BZ13" s="25"/>
+      <c r="CA13" s="25"/>
+      <c r="CB13" s="25"/>
+      <c r="CC13" s="25"/>
+      <c r="CD13" s="25"/>
+      <c r="CE13" s="25"/>
+      <c r="CF13" s="25"/>
+      <c r="CG13" s="25"/>
+      <c r="CH13" s="25"/>
+      <c r="CI13" s="25"/>
+      <c r="CJ13" s="25"/>
+      <c r="CK13" s="25"/>
+      <c r="CL13" s="25"/>
+      <c r="CM13" s="25"/>
+      <c r="CN13" s="25"/>
+      <c r="CO13" s="25"/>
+      <c r="CP13" s="25"/>
+      <c r="CQ13" s="25"/>
+      <c r="CR13" s="25"/>
+      <c r="CS13" s="25"/>
+      <c r="CT13" s="25"/>
+      <c r="CU13" s="25"/>
+      <c r="CV13" s="25"/>
+      <c r="CW13" s="25"/>
+      <c r="CX13" s="25"/>
+      <c r="CY13" s="25"/>
+      <c r="CZ13" s="25"/>
+      <c r="DA13" s="25"/>
+      <c r="DB13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="21" t="n">
         <f aca="false">SUM(D14:ZZ14)</f>
         <v>69.5</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="22" t="n">
         <v>78.5</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="K14" s="18" t="n">
+      <c r="K14" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L14" s="20" t="n">
+      <c r="L14" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="M14" s="21" t="n">
+      <c r="M14" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="N14" s="21" t="n">
+      <c r="N14" s="24" t="n">
         <v>24</v>
       </c>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
+      <c r="AH14" s="25"/>
+      <c r="AI14" s="25"/>
+      <c r="AJ14" s="25"/>
+      <c r="AK14" s="25"/>
+      <c r="AL14" s="25"/>
+      <c r="AM14" s="25"/>
+      <c r="AN14" s="25"/>
+      <c r="AO14" s="25"/>
+      <c r="AP14" s="25"/>
+      <c r="AQ14" s="25"/>
+      <c r="AR14" s="25"/>
+      <c r="AS14" s="25"/>
+      <c r="AT14" s="25"/>
+      <c r="AU14" s="25"/>
+      <c r="AV14" s="25"/>
+      <c r="AW14" s="25"/>
+      <c r="AX14" s="25"/>
+      <c r="AY14" s="25"/>
+      <c r="AZ14" s="25"/>
+      <c r="BA14" s="25"/>
+      <c r="BB14" s="25"/>
+      <c r="BC14" s="25"/>
+      <c r="BD14" s="25"/>
+      <c r="BE14" s="25"/>
+      <c r="BF14" s="25"/>
+      <c r="BG14" s="25"/>
+      <c r="BH14" s="25"/>
+      <c r="BI14" s="25"/>
+      <c r="BJ14" s="25"/>
+      <c r="BK14" s="25"/>
+      <c r="BL14" s="25"/>
+      <c r="BM14" s="25"/>
+      <c r="BN14" s="25"/>
+      <c r="BO14" s="25"/>
+      <c r="BP14" s="25"/>
+      <c r="BQ14" s="25"/>
+      <c r="BR14" s="25"/>
+      <c r="BS14" s="25"/>
+      <c r="BT14" s="25"/>
+      <c r="BU14" s="25"/>
+      <c r="BV14" s="25"/>
+      <c r="BW14" s="25"/>
+      <c r="BX14" s="25"/>
+      <c r="BY14" s="25"/>
+      <c r="BZ14" s="25"/>
+      <c r="CA14" s="25"/>
+      <c r="CB14" s="25"/>
+      <c r="CC14" s="25"/>
+      <c r="CD14" s="25"/>
+      <c r="CE14" s="25"/>
+      <c r="CF14" s="25"/>
+      <c r="CG14" s="25"/>
+      <c r="CH14" s="25"/>
+      <c r="CI14" s="25"/>
+      <c r="CJ14" s="25"/>
+      <c r="CK14" s="25"/>
+      <c r="CL14" s="25"/>
+      <c r="CM14" s="25"/>
+      <c r="CN14" s="25"/>
+      <c r="CO14" s="25"/>
+      <c r="CP14" s="25"/>
+      <c r="CQ14" s="25"/>
+      <c r="CR14" s="25"/>
+      <c r="CS14" s="25"/>
+      <c r="CT14" s="25"/>
+      <c r="CU14" s="25"/>
+      <c r="CV14" s="25"/>
+      <c r="CW14" s="25"/>
+      <c r="CX14" s="25"/>
+      <c r="CY14" s="25"/>
+      <c r="CZ14" s="25"/>
+      <c r="DA14" s="25"/>
+      <c r="DB14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="21" t="n">
         <f aca="false">SUM(D15:ZZ15)</f>
         <v>77.5</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="22" t="n">
         <v>71.5</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="20" t="n">
+      <c r="L15" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M15" s="21" t="n">
+      <c r="M15" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="N15" s="21" t="n">
+      <c r="N15" s="24" t="n">
         <v>24.5</v>
       </c>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="25"/>
+      <c r="AJ15" s="25"/>
+      <c r="AK15" s="25"/>
+      <c r="AL15" s="25"/>
+      <c r="AM15" s="25"/>
+      <c r="AN15" s="25"/>
+      <c r="AO15" s="25"/>
+      <c r="AP15" s="25"/>
+      <c r="AQ15" s="25"/>
+      <c r="AR15" s="25"/>
+      <c r="AS15" s="25"/>
+      <c r="AT15" s="25"/>
+      <c r="AU15" s="25"/>
+      <c r="AV15" s="25"/>
+      <c r="AW15" s="25"/>
+      <c r="AX15" s="25"/>
+      <c r="AY15" s="25"/>
+      <c r="AZ15" s="25"/>
+      <c r="BA15" s="25"/>
+      <c r="BB15" s="25"/>
+      <c r="BC15" s="25"/>
+      <c r="BD15" s="25"/>
+      <c r="BE15" s="25"/>
+      <c r="BF15" s="25"/>
+      <c r="BG15" s="25"/>
+      <c r="BH15" s="25"/>
+      <c r="BI15" s="25"/>
+      <c r="BJ15" s="25"/>
+      <c r="BK15" s="25"/>
+      <c r="BL15" s="25"/>
+      <c r="BM15" s="25"/>
+      <c r="BN15" s="25"/>
+      <c r="BO15" s="25"/>
+      <c r="BP15" s="25"/>
+      <c r="BQ15" s="25"/>
+      <c r="BR15" s="25"/>
+      <c r="BS15" s="25"/>
+      <c r="BT15" s="25"/>
+      <c r="BU15" s="25"/>
+      <c r="BV15" s="25"/>
+      <c r="BW15" s="25"/>
+      <c r="BX15" s="25"/>
+      <c r="BY15" s="25"/>
+      <c r="BZ15" s="25"/>
+      <c r="CA15" s="25"/>
+      <c r="CB15" s="25"/>
+      <c r="CC15" s="25"/>
+      <c r="CD15" s="25"/>
+      <c r="CE15" s="25"/>
+      <c r="CF15" s="25"/>
+      <c r="CG15" s="25"/>
+      <c r="CH15" s="25"/>
+      <c r="CI15" s="25"/>
+      <c r="CJ15" s="25"/>
+      <c r="CK15" s="25"/>
+      <c r="CL15" s="25"/>
+      <c r="CM15" s="25"/>
+      <c r="CN15" s="25"/>
+      <c r="CO15" s="25"/>
+      <c r="CP15" s="25"/>
+      <c r="CQ15" s="25"/>
+      <c r="CR15" s="25"/>
+      <c r="CS15" s="25"/>
+      <c r="CT15" s="25"/>
+      <c r="CU15" s="25"/>
+      <c r="CV15" s="25"/>
+      <c r="CW15" s="25"/>
+      <c r="CX15" s="25"/>
+      <c r="CY15" s="25"/>
+      <c r="CZ15" s="25"/>
+      <c r="DA15" s="25"/>
+      <c r="DB15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="21" t="n">
         <f aca="false">SUM(D16:ZZ16)</f>
         <v>72.5</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="22" t="n">
         <v>76.5</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L16" s="20" t="n">
+      <c r="L16" s="23" t="n">
         <v>5.5</v>
       </c>
-      <c r="M16" s="21" t="n">
+      <c r="M16" s="24" t="n">
         <v>6.5</v>
       </c>
-      <c r="N16" s="21" t="n">
+      <c r="N16" s="24" t="n">
         <v>24</v>
       </c>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="25"/>
+      <c r="AI16" s="25"/>
+      <c r="AJ16" s="25"/>
+      <c r="AK16" s="25"/>
+      <c r="AL16" s="25"/>
+      <c r="AM16" s="25"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="25"/>
+      <c r="AQ16" s="25"/>
+      <c r="AR16" s="25"/>
+      <c r="AS16" s="25"/>
+      <c r="AT16" s="25"/>
+      <c r="AU16" s="25"/>
+      <c r="AV16" s="25"/>
+      <c r="AW16" s="25"/>
+      <c r="AX16" s="25"/>
+      <c r="AY16" s="25"/>
+      <c r="AZ16" s="25"/>
+      <c r="BA16" s="25"/>
+      <c r="BB16" s="25"/>
+      <c r="BC16" s="25"/>
+      <c r="BD16" s="25"/>
+      <c r="BE16" s="25"/>
+      <c r="BF16" s="25"/>
+      <c r="BG16" s="25"/>
+      <c r="BH16" s="25"/>
+      <c r="BI16" s="25"/>
+      <c r="BJ16" s="25"/>
+      <c r="BK16" s="25"/>
+      <c r="BL16" s="25"/>
+      <c r="BM16" s="25"/>
+      <c r="BN16" s="25"/>
+      <c r="BO16" s="25"/>
+      <c r="BP16" s="25"/>
+      <c r="BQ16" s="25"/>
+      <c r="BR16" s="25"/>
+      <c r="BS16" s="25"/>
+      <c r="BT16" s="25"/>
+      <c r="BU16" s="25"/>
+      <c r="BV16" s="25"/>
+      <c r="BW16" s="25"/>
+      <c r="BX16" s="25"/>
+      <c r="BY16" s="25"/>
+      <c r="BZ16" s="25"/>
+      <c r="CA16" s="25"/>
+      <c r="CB16" s="25"/>
+      <c r="CC16" s="25"/>
+      <c r="CD16" s="25"/>
+      <c r="CE16" s="25"/>
+      <c r="CF16" s="25"/>
+      <c r="CG16" s="25"/>
+      <c r="CH16" s="25"/>
+      <c r="CI16" s="25"/>
+      <c r="CJ16" s="25"/>
+      <c r="CK16" s="25"/>
+      <c r="CL16" s="25"/>
+      <c r="CM16" s="25"/>
+      <c r="CN16" s="25"/>
+      <c r="CO16" s="25"/>
+      <c r="CP16" s="25"/>
+      <c r="CQ16" s="25"/>
+      <c r="CR16" s="25"/>
+      <c r="CS16" s="25"/>
+      <c r="CT16" s="25"/>
+      <c r="CU16" s="25"/>
+      <c r="CV16" s="25"/>
+      <c r="CW16" s="25"/>
+      <c r="CX16" s="25"/>
+      <c r="CY16" s="25"/>
+      <c r="CZ16" s="25"/>
+      <c r="DA16" s="25"/>
+      <c r="DB16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="21" t="n">
         <f aca="false">SUM(D17:ZZ17)</f>
         <v>80</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="22" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="H17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="K17" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="20" t="n">
+      <c r="L17" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="21" t="n">
+      <c r="M17" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="N17" s="21" t="n">
+      <c r="N17" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AL17" s="25"/>
+      <c r="AM17" s="25"/>
+      <c r="AN17" s="25"/>
+      <c r="AO17" s="25"/>
+      <c r="AP17" s="25"/>
+      <c r="AQ17" s="25"/>
+      <c r="AR17" s="25"/>
+      <c r="AS17" s="25"/>
+      <c r="AT17" s="25"/>
+      <c r="AU17" s="25"/>
+      <c r="AV17" s="25"/>
+      <c r="AW17" s="25"/>
+      <c r="AX17" s="25"/>
+      <c r="AY17" s="25"/>
+      <c r="AZ17" s="25"/>
+      <c r="BA17" s="25"/>
+      <c r="BB17" s="25"/>
+      <c r="BC17" s="25"/>
+      <c r="BD17" s="25"/>
+      <c r="BE17" s="25"/>
+      <c r="BF17" s="25"/>
+      <c r="BG17" s="25"/>
+      <c r="BH17" s="25"/>
+      <c r="BI17" s="25"/>
+      <c r="BJ17" s="25"/>
+      <c r="BK17" s="25"/>
+      <c r="BL17" s="25"/>
+      <c r="BM17" s="25"/>
+      <c r="BN17" s="25"/>
+      <c r="BO17" s="25"/>
+      <c r="BP17" s="25"/>
+      <c r="BQ17" s="25"/>
+      <c r="BR17" s="25"/>
+      <c r="BS17" s="25"/>
+      <c r="BT17" s="25"/>
+      <c r="BU17" s="25"/>
+      <c r="BV17" s="25"/>
+      <c r="BW17" s="25"/>
+      <c r="BX17" s="25"/>
+      <c r="BY17" s="25"/>
+      <c r="BZ17" s="25"/>
+      <c r="CA17" s="25"/>
+      <c r="CB17" s="25"/>
+      <c r="CC17" s="25"/>
+      <c r="CD17" s="25"/>
+      <c r="CE17" s="25"/>
+      <c r="CF17" s="25"/>
+      <c r="CG17" s="25"/>
+      <c r="CH17" s="25"/>
+      <c r="CI17" s="25"/>
+      <c r="CJ17" s="25"/>
+      <c r="CK17" s="25"/>
+      <c r="CL17" s="25"/>
+      <c r="CM17" s="25"/>
+      <c r="CN17" s="25"/>
+      <c r="CO17" s="25"/>
+      <c r="CP17" s="25"/>
+      <c r="CQ17" s="25"/>
+      <c r="CR17" s="25"/>
+      <c r="CS17" s="25"/>
+      <c r="CT17" s="25"/>
+      <c r="CU17" s="25"/>
+      <c r="CV17" s="25"/>
+      <c r="CW17" s="25"/>
+      <c r="CX17" s="25"/>
+      <c r="CY17" s="25"/>
+      <c r="CZ17" s="25"/>
+      <c r="DA17" s="25"/>
+      <c r="DB17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="21" t="n">
         <f aca="false">SUM(D18:ZZ18)</f>
         <v>59.5</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="22" t="n">
         <v>70</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K18" s="18" t="n">
+      <c r="K18" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="20" t="n">
+      <c r="L18" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M18" s="21" t="n">
+      <c r="M18" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="N18" s="21" t="n">
+      <c r="N18" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="25"/>
+      <c r="AI18" s="25"/>
+      <c r="AJ18" s="25"/>
+      <c r="AK18" s="25"/>
+      <c r="AL18" s="25"/>
+      <c r="AM18" s="25"/>
+      <c r="AN18" s="25"/>
+      <c r="AO18" s="25"/>
+      <c r="AP18" s="25"/>
+      <c r="AQ18" s="25"/>
+      <c r="AR18" s="25"/>
+      <c r="AS18" s="25"/>
+      <c r="AT18" s="25"/>
+      <c r="AU18" s="25"/>
+      <c r="AV18" s="25"/>
+      <c r="AW18" s="25"/>
+      <c r="AX18" s="25"/>
+      <c r="AY18" s="25"/>
+      <c r="AZ18" s="25"/>
+      <c r="BA18" s="25"/>
+      <c r="BB18" s="25"/>
+      <c r="BC18" s="25"/>
+      <c r="BD18" s="25"/>
+      <c r="BE18" s="25"/>
+      <c r="BF18" s="25"/>
+      <c r="BG18" s="25"/>
+      <c r="BH18" s="25"/>
+      <c r="BI18" s="25"/>
+      <c r="BJ18" s="25"/>
+      <c r="BK18" s="25"/>
+      <c r="BL18" s="25"/>
+      <c r="BM18" s="25"/>
+      <c r="BN18" s="25"/>
+      <c r="BO18" s="25"/>
+      <c r="BP18" s="25"/>
+      <c r="BQ18" s="25"/>
+      <c r="BR18" s="25"/>
+      <c r="BS18" s="25"/>
+      <c r="BT18" s="25"/>
+      <c r="BU18" s="25"/>
+      <c r="BV18" s="25"/>
+      <c r="BW18" s="25"/>
+      <c r="BX18" s="25"/>
+      <c r="BY18" s="25"/>
+      <c r="BZ18" s="25"/>
+      <c r="CA18" s="25"/>
+      <c r="CB18" s="25"/>
+      <c r="CC18" s="25"/>
+      <c r="CD18" s="25"/>
+      <c r="CE18" s="25"/>
+      <c r="CF18" s="25"/>
+      <c r="CG18" s="25"/>
+      <c r="CH18" s="25"/>
+      <c r="CI18" s="25"/>
+      <c r="CJ18" s="25"/>
+      <c r="CK18" s="25"/>
+      <c r="CL18" s="25"/>
+      <c r="CM18" s="25"/>
+      <c r="CN18" s="25"/>
+      <c r="CO18" s="25"/>
+      <c r="CP18" s="25"/>
+      <c r="CQ18" s="25"/>
+      <c r="CR18" s="25"/>
+      <c r="CS18" s="25"/>
+      <c r="CT18" s="25"/>
+      <c r="CU18" s="25"/>
+      <c r="CV18" s="25"/>
+      <c r="CW18" s="25"/>
+      <c r="CX18" s="25"/>
+      <c r="CY18" s="25"/>
+      <c r="CZ18" s="25"/>
+      <c r="DA18" s="25"/>
+      <c r="DB18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="21" t="n">
         <f aca="false">SUM(D19:ZZ19)</f>
         <v>49.5</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="22" t="n">
         <v>61</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="18" t="n">
+      <c r="H19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="K19" s="18" t="n">
+      <c r="K19" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="20" t="n">
+      <c r="L19" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="21" t="n">
+      <c r="M19" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="N19" s="21" t="n">
+      <c r="N19" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="25"/>
+      <c r="AI19" s="25"/>
+      <c r="AJ19" s="25"/>
+      <c r="AK19" s="25"/>
+      <c r="AL19" s="25"/>
+      <c r="AM19" s="25"/>
+      <c r="AN19" s="25"/>
+      <c r="AO19" s="25"/>
+      <c r="AP19" s="25"/>
+      <c r="AQ19" s="25"/>
+      <c r="AR19" s="25"/>
+      <c r="AS19" s="25"/>
+      <c r="AT19" s="25"/>
+      <c r="AU19" s="25"/>
+      <c r="AV19" s="25"/>
+      <c r="AW19" s="25"/>
+      <c r="AX19" s="25"/>
+      <c r="AY19" s="25"/>
+      <c r="AZ19" s="25"/>
+      <c r="BA19" s="25"/>
+      <c r="BB19" s="25"/>
+      <c r="BC19" s="25"/>
+      <c r="BD19" s="25"/>
+      <c r="BE19" s="25"/>
+      <c r="BF19" s="25"/>
+      <c r="BG19" s="25"/>
+      <c r="BH19" s="25"/>
+      <c r="BI19" s="25"/>
+      <c r="BJ19" s="25"/>
+      <c r="BK19" s="25"/>
+      <c r="BL19" s="25"/>
+      <c r="BM19" s="25"/>
+      <c r="BN19" s="25"/>
+      <c r="BO19" s="25"/>
+      <c r="BP19" s="25"/>
+      <c r="BQ19" s="25"/>
+      <c r="BR19" s="25"/>
+      <c r="BS19" s="25"/>
+      <c r="BT19" s="25"/>
+      <c r="BU19" s="25"/>
+      <c r="BV19" s="25"/>
+      <c r="BW19" s="25"/>
+      <c r="BX19" s="25"/>
+      <c r="BY19" s="25"/>
+      <c r="BZ19" s="25"/>
+      <c r="CA19" s="25"/>
+      <c r="CB19" s="25"/>
+      <c r="CC19" s="25"/>
+      <c r="CD19" s="25"/>
+      <c r="CE19" s="25"/>
+      <c r="CF19" s="25"/>
+      <c r="CG19" s="25"/>
+      <c r="CH19" s="25"/>
+      <c r="CI19" s="25"/>
+      <c r="CJ19" s="25"/>
+      <c r="CK19" s="25"/>
+      <c r="CL19" s="25"/>
+      <c r="CM19" s="25"/>
+      <c r="CN19" s="25"/>
+      <c r="CO19" s="25"/>
+      <c r="CP19" s="25"/>
+      <c r="CQ19" s="25"/>
+      <c r="CR19" s="25"/>
+      <c r="CS19" s="25"/>
+      <c r="CT19" s="25"/>
+      <c r="CU19" s="25"/>
+      <c r="CV19" s="25"/>
+      <c r="CW19" s="25"/>
+      <c r="CX19" s="25"/>
+      <c r="CY19" s="25"/>
+      <c r="CZ19" s="25"/>
+      <c r="DA19" s="25"/>
+      <c r="DB19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="21" t="n">
         <f aca="false">SUM(D20:ZZ20)</f>
         <v>29</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K20" s="18" t="n">
+      <c r="K20" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="L20" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="21" t="n">
+      <c r="M20" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="N20" s="21" t="n">
+      <c r="N20" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="25"/>
+      <c r="AJ20" s="25"/>
+      <c r="AK20" s="25"/>
+      <c r="AL20" s="25"/>
+      <c r="AM20" s="25"/>
+      <c r="AN20" s="25"/>
+      <c r="AO20" s="25"/>
+      <c r="AP20" s="25"/>
+      <c r="AQ20" s="25"/>
+      <c r="AR20" s="25"/>
+      <c r="AS20" s="25"/>
+      <c r="AT20" s="25"/>
+      <c r="AU20" s="25"/>
+      <c r="AV20" s="25"/>
+      <c r="AW20" s="25"/>
+      <c r="AX20" s="25"/>
+      <c r="AY20" s="25"/>
+      <c r="AZ20" s="25"/>
+      <c r="BA20" s="25"/>
+      <c r="BB20" s="25"/>
+      <c r="BC20" s="25"/>
+      <c r="BD20" s="25"/>
+      <c r="BE20" s="25"/>
+      <c r="BF20" s="25"/>
+      <c r="BG20" s="25"/>
+      <c r="BH20" s="25"/>
+      <c r="BI20" s="25"/>
+      <c r="BJ20" s="25"/>
+      <c r="BK20" s="25"/>
+      <c r="BL20" s="25"/>
+      <c r="BM20" s="25"/>
+      <c r="BN20" s="25"/>
+      <c r="BO20" s="25"/>
+      <c r="BP20" s="25"/>
+      <c r="BQ20" s="25"/>
+      <c r="BR20" s="25"/>
+      <c r="BS20" s="25"/>
+      <c r="BT20" s="25"/>
+      <c r="BU20" s="25"/>
+      <c r="BV20" s="25"/>
+      <c r="BW20" s="25"/>
+      <c r="BX20" s="25"/>
+      <c r="BY20" s="25"/>
+      <c r="BZ20" s="25"/>
+      <c r="CA20" s="25"/>
+      <c r="CB20" s="25"/>
+      <c r="CC20" s="25"/>
+      <c r="CD20" s="25"/>
+      <c r="CE20" s="25"/>
+      <c r="CF20" s="25"/>
+      <c r="CG20" s="25"/>
+      <c r="CH20" s="25"/>
+      <c r="CI20" s="25"/>
+      <c r="CJ20" s="25"/>
+      <c r="CK20" s="25"/>
+      <c r="CL20" s="25"/>
+      <c r="CM20" s="25"/>
+      <c r="CN20" s="25"/>
+      <c r="CO20" s="25"/>
+      <c r="CP20" s="25"/>
+      <c r="CQ20" s="25"/>
+      <c r="CR20" s="25"/>
+      <c r="CS20" s="25"/>
+      <c r="CT20" s="25"/>
+      <c r="CU20" s="25"/>
+      <c r="CV20" s="25"/>
+      <c r="CW20" s="25"/>
+      <c r="CX20" s="25"/>
+      <c r="CY20" s="25"/>
+      <c r="CZ20" s="25"/>
+      <c r="DA20" s="25"/>
+      <c r="DB20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="21" t="n">
         <f aca="false">SUM(D21:ZZ21)</f>
         <v>34</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="K21" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="20" t="n">
+      <c r="L21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="21" t="n">
+      <c r="M21" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="21" t="n">
+      <c r="N21" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="25"/>
+      <c r="AJ21" s="25"/>
+      <c r="AK21" s="25"/>
+      <c r="AL21" s="25"/>
+      <c r="AM21" s="25"/>
+      <c r="AN21" s="25"/>
+      <c r="AO21" s="25"/>
+      <c r="AP21" s="25"/>
+      <c r="AQ21" s="25"/>
+      <c r="AR21" s="25"/>
+      <c r="AS21" s="25"/>
+      <c r="AT21" s="25"/>
+      <c r="AU21" s="25"/>
+      <c r="AV21" s="25"/>
+      <c r="AW21" s="25"/>
+      <c r="AX21" s="25"/>
+      <c r="AY21" s="25"/>
+      <c r="AZ21" s="25"/>
+      <c r="BA21" s="25"/>
+      <c r="BB21" s="25"/>
+      <c r="BC21" s="25"/>
+      <c r="BD21" s="25"/>
+      <c r="BE21" s="25"/>
+      <c r="BF21" s="25"/>
+      <c r="BG21" s="25"/>
+      <c r="BH21" s="25"/>
+      <c r="BI21" s="25"/>
+      <c r="BJ21" s="25"/>
+      <c r="BK21" s="25"/>
+      <c r="BL21" s="25"/>
+      <c r="BM21" s="25"/>
+      <c r="BN21" s="25"/>
+      <c r="BO21" s="25"/>
+      <c r="BP21" s="25"/>
+      <c r="BQ21" s="25"/>
+      <c r="BR21" s="25"/>
+      <c r="BS21" s="25"/>
+      <c r="BT21" s="25"/>
+      <c r="BU21" s="25"/>
+      <c r="BV21" s="25"/>
+      <c r="BW21" s="25"/>
+      <c r="BX21" s="25"/>
+      <c r="BY21" s="25"/>
+      <c r="BZ21" s="25"/>
+      <c r="CA21" s="25"/>
+      <c r="CB21" s="25"/>
+      <c r="CC21" s="25"/>
+      <c r="CD21" s="25"/>
+      <c r="CE21" s="25"/>
+      <c r="CF21" s="25"/>
+      <c r="CG21" s="25"/>
+      <c r="CH21" s="25"/>
+      <c r="CI21" s="25"/>
+      <c r="CJ21" s="25"/>
+      <c r="CK21" s="25"/>
+      <c r="CL21" s="25"/>
+      <c r="CM21" s="25"/>
+      <c r="CN21" s="25"/>
+      <c r="CO21" s="25"/>
+      <c r="CP21" s="25"/>
+      <c r="CQ21" s="25"/>
+      <c r="CR21" s="25"/>
+      <c r="CS21" s="25"/>
+      <c r="CT21" s="25"/>
+      <c r="CU21" s="25"/>
+      <c r="CV21" s="25"/>
+      <c r="CW21" s="25"/>
+      <c r="CX21" s="25"/>
+      <c r="CY21" s="25"/>
+      <c r="CZ21" s="25"/>
+      <c r="DA21" s="25"/>
+      <c r="DB21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="21" t="n">
         <f aca="false">SUM(D22:ZZ22)</f>
         <v>19.5</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="18" t="n">
+      <c r="G22" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="H22" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="K22" s="18" t="n">
+      <c r="K22" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="L22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="21" t="n">
+      <c r="M22" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="N22" s="21" t="n">
+      <c r="N22" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="25"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="25"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="25"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="25"/>
+      <c r="AQ22" s="25"/>
+      <c r="AR22" s="25"/>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="25"/>
+      <c r="AU22" s="25"/>
+      <c r="AV22" s="25"/>
+      <c r="AW22" s="25"/>
+      <c r="AX22" s="25"/>
+      <c r="AY22" s="25"/>
+      <c r="AZ22" s="25"/>
+      <c r="BA22" s="25"/>
+      <c r="BB22" s="25"/>
+      <c r="BC22" s="25"/>
+      <c r="BD22" s="25"/>
+      <c r="BE22" s="25"/>
+      <c r="BF22" s="25"/>
+      <c r="BG22" s="25"/>
+      <c r="BH22" s="25"/>
+      <c r="BI22" s="25"/>
+      <c r="BJ22" s="25"/>
+      <c r="BK22" s="25"/>
+      <c r="BL22" s="25"/>
+      <c r="BM22" s="25"/>
+      <c r="BN22" s="25"/>
+      <c r="BO22" s="25"/>
+      <c r="BP22" s="25"/>
+      <c r="BQ22" s="25"/>
+      <c r="BR22" s="25"/>
+      <c r="BS22" s="25"/>
+      <c r="BT22" s="25"/>
+      <c r="BU22" s="25"/>
+      <c r="BV22" s="25"/>
+      <c r="BW22" s="25"/>
+      <c r="BX22" s="25"/>
+      <c r="BY22" s="25"/>
+      <c r="BZ22" s="25"/>
+      <c r="CA22" s="25"/>
+      <c r="CB22" s="25"/>
+      <c r="CC22" s="25"/>
+      <c r="CD22" s="25"/>
+      <c r="CE22" s="25"/>
+      <c r="CF22" s="25"/>
+      <c r="CG22" s="25"/>
+      <c r="CH22" s="25"/>
+      <c r="CI22" s="25"/>
+      <c r="CJ22" s="25"/>
+      <c r="CK22" s="25"/>
+      <c r="CL22" s="25"/>
+      <c r="CM22" s="25"/>
+      <c r="CN22" s="25"/>
+      <c r="CO22" s="25"/>
+      <c r="CP22" s="25"/>
+      <c r="CQ22" s="25"/>
+      <c r="CR22" s="25"/>
+      <c r="CS22" s="25"/>
+      <c r="CT22" s="25"/>
+      <c r="CU22" s="25"/>
+      <c r="CV22" s="25"/>
+      <c r="CW22" s="25"/>
+      <c r="CX22" s="25"/>
+      <c r="CY22" s="25"/>
+      <c r="CZ22" s="25"/>
+      <c r="DA22" s="25"/>
+      <c r="DB22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="21" t="n">
         <f aca="false">SUM(D23:ZZ23)</f>
         <v>31</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="22" t="n">
         <v>13.5</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="18" t="n">
+      <c r="H23" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="18" t="n">
+      <c r="K23" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="20" t="n">
+      <c r="L23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="21" t="n">
+      <c r="M23" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="21" t="n">
+      <c r="N23" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="25"/>
+      <c r="AL23" s="25"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+      <c r="AR23" s="25"/>
+      <c r="AS23" s="25"/>
+      <c r="AT23" s="25"/>
+      <c r="AU23" s="25"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="25"/>
+      <c r="AX23" s="25"/>
+      <c r="AY23" s="25"/>
+      <c r="AZ23" s="25"/>
+      <c r="BA23" s="25"/>
+      <c r="BB23" s="25"/>
+      <c r="BC23" s="25"/>
+      <c r="BD23" s="25"/>
+      <c r="BE23" s="25"/>
+      <c r="BF23" s="25"/>
+      <c r="BG23" s="25"/>
+      <c r="BH23" s="25"/>
+      <c r="BI23" s="25"/>
+      <c r="BJ23" s="25"/>
+      <c r="BK23" s="25"/>
+      <c r="BL23" s="25"/>
+      <c r="BM23" s="25"/>
+      <c r="BN23" s="25"/>
+      <c r="BO23" s="25"/>
+      <c r="BP23" s="25"/>
+      <c r="BQ23" s="25"/>
+      <c r="BR23" s="25"/>
+      <c r="BS23" s="25"/>
+      <c r="BT23" s="25"/>
+      <c r="BU23" s="25"/>
+      <c r="BV23" s="25"/>
+      <c r="BW23" s="25"/>
+      <c r="BX23" s="25"/>
+      <c r="BY23" s="25"/>
+      <c r="BZ23" s="25"/>
+      <c r="CA23" s="25"/>
+      <c r="CB23" s="25"/>
+      <c r="CC23" s="25"/>
+      <c r="CD23" s="25"/>
+      <c r="CE23" s="25"/>
+      <c r="CF23" s="25"/>
+      <c r="CG23" s="25"/>
+      <c r="CH23" s="25"/>
+      <c r="CI23" s="25"/>
+      <c r="CJ23" s="25"/>
+      <c r="CK23" s="25"/>
+      <c r="CL23" s="25"/>
+      <c r="CM23" s="25"/>
+      <c r="CN23" s="25"/>
+      <c r="CO23" s="25"/>
+      <c r="CP23" s="25"/>
+      <c r="CQ23" s="25"/>
+      <c r="CR23" s="25"/>
+      <c r="CS23" s="25"/>
+      <c r="CT23" s="25"/>
+      <c r="CU23" s="25"/>
+      <c r="CV23" s="25"/>
+      <c r="CW23" s="25"/>
+      <c r="CX23" s="25"/>
+      <c r="CY23" s="25"/>
+      <c r="CZ23" s="25"/>
+      <c r="DA23" s="25"/>
+      <c r="DB23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="21" t="n">
         <f aca="false">SUM(D24:ZZ24)</f>
         <v>22</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="22" t="n">
         <v>13.5</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="G24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="18" t="n">
+      <c r="H24" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="18" t="n">
+      <c r="I24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J24" s="20" t="n">
+      <c r="J24" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="21" t="n">
+      <c r="K24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="L24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="M24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="21" t="n">
+      <c r="N24" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="25"/>
+      <c r="AJ24" s="25"/>
+      <c r="AK24" s="25"/>
+      <c r="AL24" s="25"/>
+      <c r="AM24" s="25"/>
+      <c r="AN24" s="25"/>
+      <c r="AO24" s="25"/>
+      <c r="AP24" s="25"/>
+      <c r="AQ24" s="25"/>
+      <c r="AR24" s="25"/>
+      <c r="AS24" s="25"/>
+      <c r="AT24" s="25"/>
+      <c r="AU24" s="25"/>
+      <c r="AV24" s="25"/>
+      <c r="AW24" s="25"/>
+      <c r="AX24" s="25"/>
+      <c r="AY24" s="25"/>
+      <c r="AZ24" s="25"/>
+      <c r="BA24" s="25"/>
+      <c r="BB24" s="25"/>
+      <c r="BC24" s="25"/>
+      <c r="BD24" s="25"/>
+      <c r="BE24" s="25"/>
+      <c r="BF24" s="25"/>
+      <c r="BG24" s="25"/>
+      <c r="BH24" s="25"/>
+      <c r="BI24" s="25"/>
+      <c r="BJ24" s="25"/>
+      <c r="BK24" s="25"/>
+      <c r="BL24" s="25"/>
+      <c r="BM24" s="25"/>
+      <c r="BN24" s="25"/>
+      <c r="BO24" s="25"/>
+      <c r="BP24" s="25"/>
+      <c r="BQ24" s="25"/>
+      <c r="BR24" s="25"/>
+      <c r="BS24" s="25"/>
+      <c r="BT24" s="25"/>
+      <c r="BU24" s="25"/>
+      <c r="BV24" s="25"/>
+      <c r="BW24" s="25"/>
+      <c r="BX24" s="25"/>
+      <c r="BY24" s="25"/>
+      <c r="BZ24" s="25"/>
+      <c r="CA24" s="25"/>
+      <c r="CB24" s="25"/>
+      <c r="CC24" s="25"/>
+      <c r="CD24" s="25"/>
+      <c r="CE24" s="25"/>
+      <c r="CF24" s="25"/>
+      <c r="CG24" s="25"/>
+      <c r="CH24" s="25"/>
+      <c r="CI24" s="25"/>
+      <c r="CJ24" s="25"/>
+      <c r="CK24" s="25"/>
+      <c r="CL24" s="25"/>
+      <c r="CM24" s="25"/>
+      <c r="CN24" s="25"/>
+      <c r="CO24" s="25"/>
+      <c r="CP24" s="25"/>
+      <c r="CQ24" s="25"/>
+      <c r="CR24" s="25"/>
+      <c r="CS24" s="25"/>
+      <c r="CT24" s="25"/>
+      <c r="CU24" s="25"/>
+      <c r="CV24" s="25"/>
+      <c r="CW24" s="25"/>
+      <c r="CX24" s="25"/>
+      <c r="CY24" s="25"/>
+      <c r="CZ24" s="25"/>
+      <c r="DA24" s="25"/>
+      <c r="DB24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="21" t="n">
         <f aca="false">SUM(D25:ZZ25)</f>
         <v>11.5</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="22" t="n">
         <v>20.5</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="18" t="n">
+      <c r="H25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="18" t="n">
+      <c r="K25" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="20" t="n">
+      <c r="L25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="21" t="n">
+      <c r="M25" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="N25" s="21" t="n">
+      <c r="N25" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
+      <c r="AI25" s="25"/>
+      <c r="AJ25" s="25"/>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="25"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="25"/>
+      <c r="AO25" s="25"/>
+      <c r="AP25" s="25"/>
+      <c r="AQ25" s="25"/>
+      <c r="AR25" s="25"/>
+      <c r="AS25" s="25"/>
+      <c r="AT25" s="25"/>
+      <c r="AU25" s="25"/>
+      <c r="AV25" s="25"/>
+      <c r="AW25" s="25"/>
+      <c r="AX25" s="25"/>
+      <c r="AY25" s="25"/>
+      <c r="AZ25" s="25"/>
+      <c r="BA25" s="25"/>
+      <c r="BB25" s="25"/>
+      <c r="BC25" s="25"/>
+      <c r="BD25" s="25"/>
+      <c r="BE25" s="25"/>
+      <c r="BF25" s="25"/>
+      <c r="BG25" s="25"/>
+      <c r="BH25" s="25"/>
+      <c r="BI25" s="25"/>
+      <c r="BJ25" s="25"/>
+      <c r="BK25" s="25"/>
+      <c r="BL25" s="25"/>
+      <c r="BM25" s="25"/>
+      <c r="BN25" s="25"/>
+      <c r="BO25" s="25"/>
+      <c r="BP25" s="25"/>
+      <c r="BQ25" s="25"/>
+      <c r="BR25" s="25"/>
+      <c r="BS25" s="25"/>
+      <c r="BT25" s="25"/>
+      <c r="BU25" s="25"/>
+      <c r="BV25" s="25"/>
+      <c r="BW25" s="25"/>
+      <c r="BX25" s="25"/>
+      <c r="BY25" s="25"/>
+      <c r="BZ25" s="25"/>
+      <c r="CA25" s="25"/>
+      <c r="CB25" s="25"/>
+      <c r="CC25" s="25"/>
+      <c r="CD25" s="25"/>
+      <c r="CE25" s="25"/>
+      <c r="CF25" s="25"/>
+      <c r="CG25" s="25"/>
+      <c r="CH25" s="25"/>
+      <c r="CI25" s="25"/>
+      <c r="CJ25" s="25"/>
+      <c r="CK25" s="25"/>
+      <c r="CL25" s="25"/>
+      <c r="CM25" s="25"/>
+      <c r="CN25" s="25"/>
+      <c r="CO25" s="25"/>
+      <c r="CP25" s="25"/>
+      <c r="CQ25" s="25"/>
+      <c r="CR25" s="25"/>
+      <c r="CS25" s="25"/>
+      <c r="CT25" s="25"/>
+      <c r="CU25" s="25"/>
+      <c r="CV25" s="25"/>
+      <c r="CW25" s="25"/>
+      <c r="CX25" s="25"/>
+      <c r="CY25" s="25"/>
+      <c r="CZ25" s="25"/>
+      <c r="DA25" s="25"/>
+      <c r="DB25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="21" t="n">
         <f aca="false">SUM(D26:ZZ26)</f>
         <v>19.5</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="22" t="n">
         <v>21.5</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="18" t="n">
+      <c r="I26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="K26" s="18" t="n">
+      <c r="K26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="20" t="n">
+      <c r="L26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="21" t="n">
+      <c r="M26" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="N26" s="21" t="n">
+      <c r="N26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25"/>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="25"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="25"/>
+      <c r="AO26" s="25"/>
+      <c r="AP26" s="25"/>
+      <c r="AQ26" s="25"/>
+      <c r="AR26" s="25"/>
+      <c r="AS26" s="25"/>
+      <c r="AT26" s="25"/>
+      <c r="AU26" s="25"/>
+      <c r="AV26" s="25"/>
+      <c r="AW26" s="25"/>
+      <c r="AX26" s="25"/>
+      <c r="AY26" s="25"/>
+      <c r="AZ26" s="25"/>
+      <c r="BA26" s="25"/>
+      <c r="BB26" s="25"/>
+      <c r="BC26" s="25"/>
+      <c r="BD26" s="25"/>
+      <c r="BE26" s="25"/>
+      <c r="BF26" s="25"/>
+      <c r="BG26" s="25"/>
+      <c r="BH26" s="25"/>
+      <c r="BI26" s="25"/>
+      <c r="BJ26" s="25"/>
+      <c r="BK26" s="25"/>
+      <c r="BL26" s="25"/>
+      <c r="BM26" s="25"/>
+      <c r="BN26" s="25"/>
+      <c r="BO26" s="25"/>
+      <c r="BP26" s="25"/>
+      <c r="BQ26" s="25"/>
+      <c r="BR26" s="25"/>
+      <c r="BS26" s="25"/>
+      <c r="BT26" s="25"/>
+      <c r="BU26" s="25"/>
+      <c r="BV26" s="25"/>
+      <c r="BW26" s="25"/>
+      <c r="BX26" s="25"/>
+      <c r="BY26" s="25"/>
+      <c r="BZ26" s="25"/>
+      <c r="CA26" s="25"/>
+      <c r="CB26" s="25"/>
+      <c r="CC26" s="25"/>
+      <c r="CD26" s="25"/>
+      <c r="CE26" s="25"/>
+      <c r="CF26" s="25"/>
+      <c r="CG26" s="25"/>
+      <c r="CH26" s="25"/>
+      <c r="CI26" s="25"/>
+      <c r="CJ26" s="25"/>
+      <c r="CK26" s="25"/>
+      <c r="CL26" s="25"/>
+      <c r="CM26" s="25"/>
+      <c r="CN26" s="25"/>
+      <c r="CO26" s="25"/>
+      <c r="CP26" s="25"/>
+      <c r="CQ26" s="25"/>
+      <c r="CR26" s="25"/>
+      <c r="CS26" s="25"/>
+      <c r="CT26" s="25"/>
+      <c r="CU26" s="25"/>
+      <c r="CV26" s="25"/>
+      <c r="CW26" s="25"/>
+      <c r="CX26" s="25"/>
+      <c r="CY26" s="25"/>
+      <c r="CZ26" s="25"/>
+      <c r="DA26" s="25"/>
+      <c r="DB26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="21" t="n">
         <f aca="false">SUM(D27:ZZ27)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="18" t="n">
+      <c r="I27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="18" t="n">
+      <c r="J27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="18" t="n">
+      <c r="K27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="20" t="n">
+      <c r="L27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="21" t="n">
+      <c r="M27" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="21" t="n">
+      <c r="N27" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="25"/>
+      <c r="AK27" s="25"/>
+      <c r="AL27" s="25"/>
+      <c r="AM27" s="25"/>
+      <c r="AN27" s="25"/>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="25"/>
+      <c r="AQ27" s="25"/>
+      <c r="AR27" s="25"/>
+      <c r="AS27" s="25"/>
+      <c r="AT27" s="25"/>
+      <c r="AU27" s="25"/>
+      <c r="AV27" s="25"/>
+      <c r="AW27" s="25"/>
+      <c r="AX27" s="25"/>
+      <c r="AY27" s="25"/>
+      <c r="AZ27" s="25"/>
+      <c r="BA27" s="25"/>
+      <c r="BB27" s="25"/>
+      <c r="BC27" s="25"/>
+      <c r="BD27" s="25"/>
+      <c r="BE27" s="25"/>
+      <c r="BF27" s="25"/>
+      <c r="BG27" s="25"/>
+      <c r="BH27" s="25"/>
+      <c r="BI27" s="25"/>
+      <c r="BJ27" s="25"/>
+      <c r="BK27" s="25"/>
+      <c r="BL27" s="25"/>
+      <c r="BM27" s="25"/>
+      <c r="BN27" s="25"/>
+      <c r="BO27" s="25"/>
+      <c r="BP27" s="25"/>
+      <c r="BQ27" s="25"/>
+      <c r="BR27" s="25"/>
+      <c r="BS27" s="25"/>
+      <c r="BT27" s="25"/>
+      <c r="BU27" s="25"/>
+      <c r="BV27" s="25"/>
+      <c r="BW27" s="25"/>
+      <c r="BX27" s="25"/>
+      <c r="BY27" s="25"/>
+      <c r="BZ27" s="25"/>
+      <c r="CA27" s="25"/>
+      <c r="CB27" s="25"/>
+      <c r="CC27" s="25"/>
+      <c r="CD27" s="25"/>
+      <c r="CE27" s="25"/>
+      <c r="CF27" s="25"/>
+      <c r="CG27" s="25"/>
+      <c r="CH27" s="25"/>
+      <c r="CI27" s="25"/>
+      <c r="CJ27" s="25"/>
+      <c r="CK27" s="25"/>
+      <c r="CL27" s="25"/>
+      <c r="CM27" s="25"/>
+      <c r="CN27" s="25"/>
+      <c r="CO27" s="25"/>
+      <c r="CP27" s="25"/>
+      <c r="CQ27" s="25"/>
+      <c r="CR27" s="25"/>
+      <c r="CS27" s="25"/>
+      <c r="CT27" s="25"/>
+      <c r="CU27" s="25"/>
+      <c r="CV27" s="25"/>
+      <c r="CW27" s="25"/>
+      <c r="CX27" s="25"/>
+      <c r="CY27" s="25"/>
+      <c r="CZ27" s="25"/>
+      <c r="DA27" s="25"/>
+      <c r="DB27" s="25"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="21"/>
+    <row r="28" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>58.3653846153846</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>63.5</v>
+      </c>
+      <c r="D28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>2.84615384615385</v>
+      </c>
+      <c r="E28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>2.03846153846154</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>0.384615384615385</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>2.61538461538462</v>
+      </c>
+      <c r="H28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>2.80769230769231</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>2.57692307692308</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>12.0576923076923</v>
+      </c>
+      <c r="K28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>3.61538461538462</v>
+      </c>
+      <c r="L28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>4.90384615384615</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>5.53846153846154</v>
+      </c>
+      <c r="N28" s="27" t="n">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>18.9807692307692</v>
+      </c>
+      <c r="O28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="P28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="R28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="S28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="T28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="U28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="V28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="W28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="X28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="Y28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="Z28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AA28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AB28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AC28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AD28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AH28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AK28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AL28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AM28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AN28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AO28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AP28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AQ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AR28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AS28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AT28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AU28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AV28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AW28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AX28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AY28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="AZ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BA28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BB28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BC28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BD28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BE28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BF28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BG28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BH28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BI28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BJ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BK28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BL28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BM28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BN28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BO28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BP28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BQ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BR28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BS28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BT28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BU28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BV28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BW28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BX28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BY28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="BZ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CA28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CB28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CC28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CD28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CE28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CF28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CG28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CH28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CI28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CJ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CK28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CL28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CM28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CN28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CO28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CP28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CQ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CR28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CS28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CT28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CU28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CV28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CW28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CX28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CY28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="CZ28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="DA28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
+      <c r="DB28" s="27" t="str">
+        <f aca="true">IF(INDIRECT(ADDRESS(1,COLUMN()))="评语：","",IF(COUNT(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW(),COLUMN())))=0,"",AVERAGE(INDIRECT(ADDRESS(2,COLUMN())&amp;":"&amp;ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Larry Wei</author>
+    <author>Wei Larry</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -85,6 +85,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">LibreOffice</t>
         </r>
@@ -93,6 +94,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">：</t>
         </r>
@@ -101,6 +103,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Ctrl + </t>
         </r>
@@ -109,6 +112,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">回车；
 </t>
@@ -118,6 +122,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">WPS Office</t>
         </r>
@@ -126,6 +131,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">、</t>
         </r>
@@ -134,6 +140,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">MS Office</t>
         </r>
@@ -142,6 +149,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">： </t>
         </r>
@@ -150,6 +158,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Alt + </t>
         </r>
@@ -158,8 +167,21 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">回车。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">在“平均分”行前插入或删除“学生 行”，总分列请您自行拖拽补充。</t>
         </r>
       </text>
     </comment>
@@ -327,7 +349,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">。</t>
+          <t xml:space="preserve">。平均分行请自行拖拽补齐。</t>
         </r>
       </text>
     </comment>
@@ -597,7 +619,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
@@ -664,11 +686,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -5359,8 +5376,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Larry Wei</author>
+    <author>Wei Larry</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0">
@@ -5153,8 +5153,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -81,7 +81,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">。</t>
+          <t xml:space="preserve">。（选填）</t>
         </r>
       </text>
     </comment>
@@ -297,7 +297,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">。</t>
+          <t xml:space="preserve">。（选填）</t>
         </r>
       </text>
     </comment>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -721,17 +721,18 @@
         <u val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="@"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <border diagonalUp="false" diagonalDown="false">
-        <left style="double">
+        <left style="mediumDashed">
           <color rgb="FFBF0041"/>
         </left>
-        <right style="double">
+        <right style="mediumDashed">
           <color rgb="FFBF0041"/>
         </right>
-        <top style="double">
+        <top style="mediumDashed">
           <color rgb="FFBF0041"/>
         </top>
-        <bottom style="double">
+        <bottom style="mediumDashed">
           <color rgb="FFBF0041"/>
         </bottom>
         <diagonal/>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Larry Wei</author>
+    <author>Wei Larry</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -614,19 +614,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -721,7 +721,6 @@
         <u val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="@"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <border diagonalUp="false" diagonalDown="false">
         <left style="mediumDashed">
           <color rgb="FFBF0041"/>
@@ -1164,37 +1163,37 @@
       <c r="D2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="10" t="s">
         <v>16</v>
       </c>
       <c r="P2" s="11"/>
@@ -5250,8 +5249,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -4982,10 +4982,7 @@
     </row>
     <row r="30" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24"/>
-      <c r="B30" s="17" t="str">
-        <f aca="false">IF(SUM(D30:AML30)&gt;0,SUM(D30:AML30),"")</f>
-        <v/>
-      </c>
+      <c r="B30" s="17"/>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
@@ -5091,10 +5088,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26"/>
-      <c r="B31" s="17" t="str">
-        <f aca="false">IF(SUM(D31:AML31)&gt;0,SUM(D31:AML31),"")</f>
-        <v/>
-      </c>
+      <c r="B31" s="17"/>
       <c r="C31" s="27"/>
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
@@ -5111,10 +5105,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26"/>
-      <c r="B32" s="17" t="str">
-        <f aca="false">IF(SUM(D32:AML32)&gt;0,SUM(D32:AML32),"")</f>
-        <v/>
-      </c>
+      <c r="B32" s="17"/>
       <c r="C32" s="27"/>
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
@@ -5131,10 +5122,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26"/>
-      <c r="B33" s="17" t="str">
-        <f aca="false">IF(SUM(D33:AML33)&gt;0,SUM(D33:AML33),"")</f>
-        <v/>
-      </c>
+      <c r="B33" s="17"/>
       <c r="C33" s="27"/>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
@@ -5151,10 +5139,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26"/>
-      <c r="B34" s="17" t="str">
-        <f aca="false">IF(SUM(D34:AML34)&gt;0,SUM(D34:AML34),"")</f>
-        <v/>
-      </c>
+      <c r="B34" s="17"/>
       <c r="C34" s="27"/>
       <c r="D34" s="28"/>
       <c r="E34" s="28"/>
@@ -5171,10 +5156,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26"/>
-      <c r="B35" s="17" t="str">
-        <f aca="false">IF(SUM(D35:AML35)&gt;0,SUM(D35:AML35),"")</f>
-        <v/>
-      </c>
+      <c r="B35" s="17"/>
       <c r="C35" s="27"/>
       <c r="D35" s="28"/>
       <c r="E35" s="28"/>
@@ -5190,16 +5172,10 @@
       <c r="O35" s="28"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="17" t="str">
-        <f aca="false">IF(SUM(D36:AML36)&gt;0,SUM(D36:AML36),"")</f>
-        <v/>
-      </c>
+      <c r="B36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="17" t="str">
-        <f aca="false">IF(SUM(D37:AML37)&gt;0,SUM(D37:AML37),"")</f>
-        <v/>
-      </c>
+      <c r="B37" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -236,7 +236,7 @@
     <t xml:space="preserve">总分</t>
   </si>
   <si>
-    <t xml:space="preserve">上一次测试</t>
+    <t xml:space="preserve">近期无测试</t>
   </si>
   <si>
     <t xml:space="preserve">考试纪律</t>
@@ -1010,7 +1010,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DX37"/>
+  <dimension ref="A1:DX256"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
@@ -1287,9 +1287,9 @@
         <f aca="false">IF(SUM(B4:B1027)&gt;0,AVERAGE(B4:B1027),"")</f>
         <v>60.7</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="13" t="str">
         <f aca="false">IF(SUM(C4:C1027)&gt;0,AVERAGE(C4:C1027),"")</f>
-        <v>63.5</v>
+        <v/>
       </c>
       <c r="D3" s="13" t="str">
         <f aca="false">IF(SUM(D4:D1027)&gt;0,AVERAGE(D4:D1027),"")</f>
@@ -1800,9 +1800,7 @@
         <f aca="false">IF(SUM(D4:AML4)&gt;0,SUM(D4:AML4),"")</f>
         <v>86.5</v>
       </c>
-      <c r="C4" s="16" t="n">
-        <v>92</v>
-      </c>
+      <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17" t="n">
         <v>4</v>
@@ -1936,9 +1934,7 @@
         <f aca="false">IF(SUM(D5:AML5)&gt;0,SUM(D5:AML5),"")</f>
         <v>87</v>
       </c>
-      <c r="C5" s="16" t="n">
-        <v>95</v>
-      </c>
+      <c r="C5" s="16"/>
       <c r="D5" s="20"/>
       <c r="E5" s="20" t="n">
         <v>4</v>
@@ -2072,9 +2068,7 @@
         <f aca="false">IF(SUM(D6:AML6)&gt;0,SUM(D6:AML6),"")</f>
         <v>80</v>
       </c>
-      <c r="C6" s="16" t="n">
-        <v>93.5</v>
-      </c>
+      <c r="C6" s="16"/>
       <c r="D6" s="20"/>
       <c r="E6" s="20" t="n">
         <v>3.5</v>
@@ -2208,9 +2202,7 @@
         <f aca="false">IF(SUM(D7:AML7)&gt;0,SUM(D7:AML7),"")</f>
         <v>68.5</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>87</v>
-      </c>
+      <c r="C7" s="16"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20" t="n">
         <v>4</v>
@@ -2344,9 +2336,7 @@
         <f aca="false">IF(SUM(D8:AML8)&gt;0,SUM(D8:AML8),"")</f>
         <v>81</v>
       </c>
-      <c r="C8" s="16" t="n">
-        <v>90.5</v>
-      </c>
+      <c r="C8" s="16"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20" t="n">
         <v>4</v>
@@ -2480,9 +2470,7 @@
         <f aca="false">IF(SUM(D9:AML9)&gt;0,SUM(D9:AML9),"")</f>
         <v>82</v>
       </c>
-      <c r="C9" s="16" t="n">
-        <v>97</v>
-      </c>
+      <c r="C9" s="16"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20" t="n">
         <v>4</v>
@@ -2616,9 +2604,7 @@
         <f aca="false">IF(SUM(D10:AML10)&gt;0,SUM(D10:AML10),"")</f>
         <v>77</v>
       </c>
-      <c r="C10" s="16" t="n">
-        <v>86</v>
-      </c>
+      <c r="C10" s="16"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20" t="n">
         <v>4</v>
@@ -2752,9 +2738,7 @@
         <f aca="false">IF(SUM(D11:AML11)&gt;0,SUM(D11:AML11),"")</f>
         <v>73</v>
       </c>
-      <c r="C11" s="16" t="n">
-        <v>89</v>
-      </c>
+      <c r="C11" s="16"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20" t="n">
         <v>4</v>
@@ -2888,9 +2872,7 @@
         <f aca="false">IF(SUM(D12:AML12)&gt;0,SUM(D12:AML12),"")</f>
         <v>86.5</v>
       </c>
-      <c r="C12" s="16" t="n">
-        <v>93</v>
-      </c>
+      <c r="C12" s="16"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="n">
         <v>4</v>
@@ -3024,9 +3006,7 @@
         <f aca="false">IF(SUM(D13:AML13)&gt;0,SUM(D13:AML13),"")</f>
         <v>70</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>74.5</v>
-      </c>
+      <c r="C13" s="16"/>
       <c r="D13" s="20"/>
       <c r="E13" s="20" t="n">
         <v>4</v>
@@ -3160,9 +3140,7 @@
         <f aca="false">IF(SUM(D14:AML14)&gt;0,SUM(D14:AML14),"")</f>
         <v>70.5</v>
       </c>
-      <c r="C14" s="16" t="n">
-        <v>75.5</v>
-      </c>
+      <c r="C14" s="16"/>
       <c r="D14" s="20"/>
       <c r="E14" s="20" t="n">
         <v>4</v>
@@ -3296,9 +3274,7 @@
         <f aca="false">IF(SUM(D15:AML15)&gt;0,SUM(D15:AML15),"")</f>
         <v>80.5</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>88.5</v>
-      </c>
+      <c r="C15" s="16"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20" t="n">
         <v>3.5</v>
@@ -3432,9 +3408,7 @@
         <f aca="false">IF(SUM(D16:AML16)&gt;0,SUM(D16:AML16),"")</f>
         <v>69.5</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>78.5</v>
-      </c>
+      <c r="C16" s="16"/>
       <c r="D16" s="20"/>
       <c r="E16" s="20" t="n">
         <v>3</v>
@@ -3568,9 +3542,7 @@
         <f aca="false">IF(SUM(D17:AML17)&gt;0,SUM(D17:AML17),"")</f>
         <v>77.5</v>
       </c>
-      <c r="C17" s="16" t="n">
-        <v>71.5</v>
-      </c>
+      <c r="C17" s="16"/>
       <c r="D17" s="20"/>
       <c r="E17" s="20" t="n">
         <v>3</v>
@@ -3704,9 +3676,7 @@
         <f aca="false">IF(SUM(D18:AML18)&gt;0,SUM(D18:AML18),"")</f>
         <v>72.5</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>76.5</v>
-      </c>
+      <c r="C18" s="16"/>
       <c r="D18" s="20"/>
       <c r="E18" s="20" t="n">
         <v>3.5</v>
@@ -3840,9 +3810,7 @@
         <f aca="false">IF(SUM(D19:AML19)&gt;0,SUM(D19:AML19),"")</f>
         <v>80</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>82</v>
-      </c>
+      <c r="C19" s="16"/>
       <c r="D19" s="20"/>
       <c r="E19" s="20" t="n">
         <v>4</v>
@@ -3976,9 +3944,7 @@
         <f aca="false">IF(SUM(D20:AML20)&gt;0,SUM(D20:AML20),"")</f>
         <v>59.5</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>70</v>
-      </c>
+      <c r="C20" s="16"/>
       <c r="D20" s="20"/>
       <c r="E20" s="20" t="n">
         <v>2</v>
@@ -4112,9 +4078,7 @@
         <f aca="false">IF(SUM(D21:AML21)&gt;0,SUM(D21:AML21),"")</f>
         <v>49.5</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>61</v>
-      </c>
+      <c r="C21" s="16"/>
       <c r="D21" s="20"/>
       <c r="E21" s="20" t="n">
         <v>2</v>
@@ -4248,9 +4212,7 @@
         <f aca="false">IF(SUM(D22:AML22)&gt;0,SUM(D22:AML22),"")</f>
         <v>29</v>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>13</v>
-      </c>
+      <c r="C22" s="16"/>
       <c r="D22" s="20"/>
       <c r="E22" s="20" t="n">
         <v>1.5</v>
@@ -4384,9 +4346,7 @@
         <f aca="false">IF(SUM(D23:AML23)&gt;0,SUM(D23:AML23),"")</f>
         <v>34</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>45</v>
-      </c>
+      <c r="C23" s="16"/>
       <c r="D23" s="20"/>
       <c r="E23" s="20" t="n">
         <v>1</v>
@@ -4520,9 +4480,7 @@
         <f aca="false">IF(SUM(D24:AML24)&gt;0,SUM(D24:AML24),"")</f>
         <v>19.5</v>
       </c>
-      <c r="C24" s="16" t="n">
-        <v>23</v>
-      </c>
+      <c r="C24" s="16"/>
       <c r="D24" s="20"/>
       <c r="E24" s="20" t="n">
         <v>1</v>
@@ -4656,9 +4614,7 @@
         <f aca="false">IF(SUM(D25:AML25)&gt;0,SUM(D25:AML25),"")</f>
         <v>31</v>
       </c>
-      <c r="C25" s="16" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="C25" s="16"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20" t="n">
         <v>2</v>
@@ -4792,9 +4748,7 @@
         <f aca="false">IF(SUM(D26:AML26)&gt;0,SUM(D26:AML26),"")</f>
         <v>22</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="C26" s="16"/>
       <c r="D26" s="20"/>
       <c r="E26" s="20" t="n">
         <v>2</v>
@@ -4928,9 +4882,7 @@
         <f aca="false">IF(SUM(D27:AML27)&gt;0,SUM(D27:AML27),"")</f>
         <v>11.5</v>
       </c>
-      <c r="C27" s="16" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="C27" s="16"/>
       <c r="D27" s="20"/>
       <c r="E27" s="20" t="n">
         <v>0</v>
@@ -5064,9 +5016,7 @@
         <f aca="false">IF(SUM(D28:AML28)&gt;0,SUM(D28:AML28),"")</f>
         <v>19.5</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="C28" s="16"/>
       <c r="D28" s="20"/>
       <c r="E28" s="20" t="n">
         <v>2</v>
@@ -5200,9 +5150,7 @@
         <f aca="false">IF(SUM(D29:AML29)&gt;0,SUM(D29:AML29),"")</f>
         <v/>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="C29" s="16"/>
       <c r="D29" s="20"/>
       <c r="E29" s="20" t="n">
         <v>0</v>
@@ -5330,7 +5278,10 @@
     </row>
     <row r="30" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22"/>
-      <c r="B30" s="15"/>
+      <c r="B30" s="15" t="str">
+        <f aca="false">IF(SUM(D30:AML30)&gt;0,SUM(D30:AML30),"")</f>
+        <v/>
+      </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -5436,7 +5387,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="24"/>
-      <c r="B31" s="15"/>
+      <c r="B31" s="15" t="str">
+        <f aca="false">IF(SUM(D31:AML31)&gt;0,SUM(D31:AML31),"")</f>
+        <v/>
+      </c>
       <c r="C31" s="25"/>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -5453,7 +5407,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24"/>
-      <c r="B32" s="15"/>
+      <c r="B32" s="15" t="str">
+        <f aca="false">IF(SUM(D32:AML32)&gt;0,SUM(D32:AML32),"")</f>
+        <v/>
+      </c>
       <c r="C32" s="25"/>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
@@ -5470,7 +5427,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="24"/>
-      <c r="B33" s="15"/>
+      <c r="B33" s="15" t="str">
+        <f aca="false">IF(SUM(D33:AML33)&gt;0,SUM(D33:AML33),"")</f>
+        <v/>
+      </c>
       <c r="C33" s="25"/>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
@@ -5487,7 +5447,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24"/>
-      <c r="B34" s="15"/>
+      <c r="B34" s="15" t="str">
+        <f aca="false">IF(SUM(D34:AML34)&gt;0,SUM(D34:AML34),"")</f>
+        <v/>
+      </c>
       <c r="C34" s="25"/>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
@@ -5504,7 +5467,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="24"/>
-      <c r="B35" s="15"/>
+      <c r="B35" s="15" t="str">
+        <f aca="false">IF(SUM(D35:AML35)&gt;0,SUM(D35:AML35),"")</f>
+        <v/>
+      </c>
       <c r="C35" s="25"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -5520,10 +5486,1330 @@
       <c r="O35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="15"/>
+      <c r="B36" s="15" t="str">
+        <f aca="false">IF(SUM(D36:AML36)&gt;0,SUM(D36:AML36),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="15"/>
+      <c r="B37" s="15" t="str">
+        <f aca="false">IF(SUM(D37:AML37)&gt;0,SUM(D37:AML37),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="15" t="str">
+        <f aca="false">IF(SUM(D38:AML38)&gt;0,SUM(D38:AML38),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="15" t="str">
+        <f aca="false">IF(SUM(D39:AML39)&gt;0,SUM(D39:AML39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="15" t="str">
+        <f aca="false">IF(SUM(D40:AML40)&gt;0,SUM(D40:AML40),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="15" t="str">
+        <f aca="false">IF(SUM(D41:AML41)&gt;0,SUM(D41:AML41),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="15" t="str">
+        <f aca="false">IF(SUM(D42:AML42)&gt;0,SUM(D42:AML42),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="15" t="str">
+        <f aca="false">IF(SUM(D43:AML43)&gt;0,SUM(D43:AML43),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="15" t="str">
+        <f aca="false">IF(SUM(D44:AML44)&gt;0,SUM(D44:AML44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="15" t="str">
+        <f aca="false">IF(SUM(D45:AML45)&gt;0,SUM(D45:AML45),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="15" t="str">
+        <f aca="false">IF(SUM(D46:AML46)&gt;0,SUM(D46:AML46),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="15" t="str">
+        <f aca="false">IF(SUM(D47:AML47)&gt;0,SUM(D47:AML47),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="15" t="str">
+        <f aca="false">IF(SUM(D48:AML48)&gt;0,SUM(D48:AML48),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="15" t="str">
+        <f aca="false">IF(SUM(D49:AML49)&gt;0,SUM(D49:AML49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="15" t="str">
+        <f aca="false">IF(SUM(D50:AML50)&gt;0,SUM(D50:AML50),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="15" t="str">
+        <f aca="false">IF(SUM(D51:AML51)&gt;0,SUM(D51:AML51),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="15" t="str">
+        <f aca="false">IF(SUM(D52:AML52)&gt;0,SUM(D52:AML52),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="15" t="str">
+        <f aca="false">IF(SUM(D53:AML53)&gt;0,SUM(D53:AML53),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="15" t="str">
+        <f aca="false">IF(SUM(D54:AML54)&gt;0,SUM(D54:AML54),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="15" t="str">
+        <f aca="false">IF(SUM(D55:AML55)&gt;0,SUM(D55:AML55),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="15" t="str">
+        <f aca="false">IF(SUM(D56:AML56)&gt;0,SUM(D56:AML56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="15" t="str">
+        <f aca="false">IF(SUM(D57:AML57)&gt;0,SUM(D57:AML57),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="15" t="str">
+        <f aca="false">IF(SUM(D58:AML58)&gt;0,SUM(D58:AML58),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="15" t="str">
+        <f aca="false">IF(SUM(D59:AML59)&gt;0,SUM(D59:AML59),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="15" t="str">
+        <f aca="false">IF(SUM(D60:AML60)&gt;0,SUM(D60:AML60),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="15" t="str">
+        <f aca="false">IF(SUM(D61:AML61)&gt;0,SUM(D61:AML61),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="15" t="str">
+        <f aca="false">IF(SUM(D62:AML62)&gt;0,SUM(D62:AML62),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="15" t="str">
+        <f aca="false">IF(SUM(D63:AML63)&gt;0,SUM(D63:AML63),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="15" t="str">
+        <f aca="false">IF(SUM(D64:AML64)&gt;0,SUM(D64:AML64),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="15" t="str">
+        <f aca="false">IF(SUM(D65:AML65)&gt;0,SUM(D65:AML65),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="15" t="str">
+        <f aca="false">IF(SUM(D66:AML66)&gt;0,SUM(D66:AML66),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="15" t="str">
+        <f aca="false">IF(SUM(D67:AML67)&gt;0,SUM(D67:AML67),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="15" t="str">
+        <f aca="false">IF(SUM(D68:AML68)&gt;0,SUM(D68:AML68),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="15" t="str">
+        <f aca="false">IF(SUM(D69:AML69)&gt;0,SUM(D69:AML69),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="15" t="str">
+        <f aca="false">IF(SUM(D70:AML70)&gt;0,SUM(D70:AML70),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="15" t="str">
+        <f aca="false">IF(SUM(D71:AML71)&gt;0,SUM(D71:AML71),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="15" t="str">
+        <f aca="false">IF(SUM(D72:AML72)&gt;0,SUM(D72:AML72),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="15" t="str">
+        <f aca="false">IF(SUM(D73:AML73)&gt;0,SUM(D73:AML73),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="15" t="str">
+        <f aca="false">IF(SUM(D74:AML74)&gt;0,SUM(D74:AML74),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="15" t="str">
+        <f aca="false">IF(SUM(D75:AML75)&gt;0,SUM(D75:AML75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="15" t="str">
+        <f aca="false">IF(SUM(D76:AML76)&gt;0,SUM(D76:AML76),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="15" t="str">
+        <f aca="false">IF(SUM(D77:AML77)&gt;0,SUM(D77:AML77),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="15" t="str">
+        <f aca="false">IF(SUM(D78:AML78)&gt;0,SUM(D78:AML78),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="15" t="str">
+        <f aca="false">IF(SUM(D79:AML79)&gt;0,SUM(D79:AML79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="15" t="str">
+        <f aca="false">IF(SUM(D80:AML80)&gt;0,SUM(D80:AML80),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="15" t="str">
+        <f aca="false">IF(SUM(D81:AML81)&gt;0,SUM(D81:AML81),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="15" t="str">
+        <f aca="false">IF(SUM(D82:AML82)&gt;0,SUM(D82:AML82),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="15" t="str">
+        <f aca="false">IF(SUM(D83:AML83)&gt;0,SUM(D83:AML83),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="15" t="str">
+        <f aca="false">IF(SUM(D84:AML84)&gt;0,SUM(D84:AML84),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="15" t="str">
+        <f aca="false">IF(SUM(D85:AML85)&gt;0,SUM(D85:AML85),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="15" t="str">
+        <f aca="false">IF(SUM(D86:AML86)&gt;0,SUM(D86:AML86),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="15" t="str">
+        <f aca="false">IF(SUM(D87:AML87)&gt;0,SUM(D87:AML87),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="15" t="str">
+        <f aca="false">IF(SUM(D88:AML88)&gt;0,SUM(D88:AML88),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="15" t="str">
+        <f aca="false">IF(SUM(D89:AML89)&gt;0,SUM(D89:AML89),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="15" t="str">
+        <f aca="false">IF(SUM(D90:AML90)&gt;0,SUM(D90:AML90),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="15" t="str">
+        <f aca="false">IF(SUM(D91:AML91)&gt;0,SUM(D91:AML91),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="15" t="str">
+        <f aca="false">IF(SUM(D92:AML92)&gt;0,SUM(D92:AML92),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="15" t="str">
+        <f aca="false">IF(SUM(D93:AML93)&gt;0,SUM(D93:AML93),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="15" t="str">
+        <f aca="false">IF(SUM(D94:AML94)&gt;0,SUM(D94:AML94),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="15" t="str">
+        <f aca="false">IF(SUM(D95:AML95)&gt;0,SUM(D95:AML95),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="15" t="str">
+        <f aca="false">IF(SUM(D96:AML96)&gt;0,SUM(D96:AML96),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="15" t="str">
+        <f aca="false">IF(SUM(D97:AML97)&gt;0,SUM(D97:AML97),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="15" t="str">
+        <f aca="false">IF(SUM(D98:AML98)&gt;0,SUM(D98:AML98),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="15" t="str">
+        <f aca="false">IF(SUM(D99:AML99)&gt;0,SUM(D99:AML99),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="15" t="str">
+        <f aca="false">IF(SUM(D100:AML100)&gt;0,SUM(D100:AML100),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="15" t="str">
+        <f aca="false">IF(SUM(D101:AML101)&gt;0,SUM(D101:AML101),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="15" t="str">
+        <f aca="false">IF(SUM(D102:AML102)&gt;0,SUM(D102:AML102),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="15" t="str">
+        <f aca="false">IF(SUM(D103:AML103)&gt;0,SUM(D103:AML103),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="15" t="str">
+        <f aca="false">IF(SUM(D104:AML104)&gt;0,SUM(D104:AML104),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="15" t="str">
+        <f aca="false">IF(SUM(D105:AML105)&gt;0,SUM(D105:AML105),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="15" t="str">
+        <f aca="false">IF(SUM(D106:AML106)&gt;0,SUM(D106:AML106),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="15" t="str">
+        <f aca="false">IF(SUM(D107:AML107)&gt;0,SUM(D107:AML107),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="15" t="str">
+        <f aca="false">IF(SUM(D108:AML108)&gt;0,SUM(D108:AML108),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="15" t="str">
+        <f aca="false">IF(SUM(D109:AML109)&gt;0,SUM(D109:AML109),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="15" t="str">
+        <f aca="false">IF(SUM(D110:AML110)&gt;0,SUM(D110:AML110),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="15" t="str">
+        <f aca="false">IF(SUM(D111:AML111)&gt;0,SUM(D111:AML111),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="15" t="str">
+        <f aca="false">IF(SUM(D112:AML112)&gt;0,SUM(D112:AML112),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="15" t="str">
+        <f aca="false">IF(SUM(D113:AML113)&gt;0,SUM(D113:AML113),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="15" t="str">
+        <f aca="false">IF(SUM(D114:AML114)&gt;0,SUM(D114:AML114),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="15" t="str">
+        <f aca="false">IF(SUM(D115:AML115)&gt;0,SUM(D115:AML115),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="15" t="str">
+        <f aca="false">IF(SUM(D116:AML116)&gt;0,SUM(D116:AML116),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="15" t="str">
+        <f aca="false">IF(SUM(D117:AML117)&gt;0,SUM(D117:AML117),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="15" t="str">
+        <f aca="false">IF(SUM(D118:AML118)&gt;0,SUM(D118:AML118),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="15" t="str">
+        <f aca="false">IF(SUM(D119:AML119)&gt;0,SUM(D119:AML119),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="15" t="str">
+        <f aca="false">IF(SUM(D120:AML120)&gt;0,SUM(D120:AML120),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="15" t="str">
+        <f aca="false">IF(SUM(D121:AML121)&gt;0,SUM(D121:AML121),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="15" t="str">
+        <f aca="false">IF(SUM(D122:AML122)&gt;0,SUM(D122:AML122),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="15" t="str">
+        <f aca="false">IF(SUM(D123:AML123)&gt;0,SUM(D123:AML123),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="15" t="str">
+        <f aca="false">IF(SUM(D124:AML124)&gt;0,SUM(D124:AML124),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="15" t="str">
+        <f aca="false">IF(SUM(D125:AML125)&gt;0,SUM(D125:AML125),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="15" t="str">
+        <f aca="false">IF(SUM(D126:AML126)&gt;0,SUM(D126:AML126),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="15" t="str">
+        <f aca="false">IF(SUM(D127:AML127)&gt;0,SUM(D127:AML127),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="15" t="str">
+        <f aca="false">IF(SUM(D128:AML128)&gt;0,SUM(D128:AML128),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="15" t="str">
+        <f aca="false">IF(SUM(D129:AML129)&gt;0,SUM(D129:AML129),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="15" t="str">
+        <f aca="false">IF(SUM(D130:AML130)&gt;0,SUM(D130:AML130),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="15" t="str">
+        <f aca="false">IF(SUM(D131:AML131)&gt;0,SUM(D131:AML131),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="15" t="str">
+        <f aca="false">IF(SUM(D132:AML132)&gt;0,SUM(D132:AML132),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="15" t="str">
+        <f aca="false">IF(SUM(D133:AML133)&gt;0,SUM(D133:AML133),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="15" t="str">
+        <f aca="false">IF(SUM(D134:AML134)&gt;0,SUM(D134:AML134),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="15" t="str">
+        <f aca="false">IF(SUM(D135:AML135)&gt;0,SUM(D135:AML135),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="15" t="str">
+        <f aca="false">IF(SUM(D136:AML136)&gt;0,SUM(D136:AML136),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="15" t="str">
+        <f aca="false">IF(SUM(D137:AML137)&gt;0,SUM(D137:AML137),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="15" t="str">
+        <f aca="false">IF(SUM(D138:AML138)&gt;0,SUM(D138:AML138),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="15" t="str">
+        <f aca="false">IF(SUM(D139:AML139)&gt;0,SUM(D139:AML139),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="15" t="str">
+        <f aca="false">IF(SUM(D140:AML140)&gt;0,SUM(D140:AML140),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="15" t="str">
+        <f aca="false">IF(SUM(D141:AML141)&gt;0,SUM(D141:AML141),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="15" t="str">
+        <f aca="false">IF(SUM(D142:AML142)&gt;0,SUM(D142:AML142),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="15" t="str">
+        <f aca="false">IF(SUM(D143:AML143)&gt;0,SUM(D143:AML143),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="15" t="str">
+        <f aca="false">IF(SUM(D144:AML144)&gt;0,SUM(D144:AML144),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="15" t="str">
+        <f aca="false">IF(SUM(D145:AML145)&gt;0,SUM(D145:AML145),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="15" t="str">
+        <f aca="false">IF(SUM(D146:AML146)&gt;0,SUM(D146:AML146),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="15" t="str">
+        <f aca="false">IF(SUM(D147:AML147)&gt;0,SUM(D147:AML147),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="15" t="str">
+        <f aca="false">IF(SUM(D148:AML148)&gt;0,SUM(D148:AML148),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="15" t="str">
+        <f aca="false">IF(SUM(D149:AML149)&gt;0,SUM(D149:AML149),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="15" t="str">
+        <f aca="false">IF(SUM(D150:AML150)&gt;0,SUM(D150:AML150),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B151" s="15" t="str">
+        <f aca="false">IF(SUM(D151:AML151)&gt;0,SUM(D151:AML151),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="15" t="str">
+        <f aca="false">IF(SUM(D152:AML152)&gt;0,SUM(D152:AML152),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="15" t="str">
+        <f aca="false">IF(SUM(D153:AML153)&gt;0,SUM(D153:AML153),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="15" t="str">
+        <f aca="false">IF(SUM(D154:AML154)&gt;0,SUM(D154:AML154),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="15" t="str">
+        <f aca="false">IF(SUM(D155:AML155)&gt;0,SUM(D155:AML155),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="15" t="str">
+        <f aca="false">IF(SUM(D156:AML156)&gt;0,SUM(D156:AML156),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="15" t="str">
+        <f aca="false">IF(SUM(D157:AML157)&gt;0,SUM(D157:AML157),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="15" t="str">
+        <f aca="false">IF(SUM(D158:AML158)&gt;0,SUM(D158:AML158),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="15" t="str">
+        <f aca="false">IF(SUM(D159:AML159)&gt;0,SUM(D159:AML159),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="15" t="str">
+        <f aca="false">IF(SUM(D160:AML160)&gt;0,SUM(D160:AML160),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="15" t="str">
+        <f aca="false">IF(SUM(D161:AML161)&gt;0,SUM(D161:AML161),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B162" s="15" t="str">
+        <f aca="false">IF(SUM(D162:AML162)&gt;0,SUM(D162:AML162),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="15" t="str">
+        <f aca="false">IF(SUM(D163:AML163)&gt;0,SUM(D163:AML163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="15" t="str">
+        <f aca="false">IF(SUM(D164:AML164)&gt;0,SUM(D164:AML164),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B165" s="15" t="str">
+        <f aca="false">IF(SUM(D165:AML165)&gt;0,SUM(D165:AML165),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="15" t="str">
+        <f aca="false">IF(SUM(D166:AML166)&gt;0,SUM(D166:AML166),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="15" t="str">
+        <f aca="false">IF(SUM(D167:AML167)&gt;0,SUM(D167:AML167),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="15" t="str">
+        <f aca="false">IF(SUM(D168:AML168)&gt;0,SUM(D168:AML168),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="15" t="str">
+        <f aca="false">IF(SUM(D169:AML169)&gt;0,SUM(D169:AML169),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="15" t="str">
+        <f aca="false">IF(SUM(D170:AML170)&gt;0,SUM(D170:AML170),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="15" t="str">
+        <f aca="false">IF(SUM(D171:AML171)&gt;0,SUM(D171:AML171),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="15" t="str">
+        <f aca="false">IF(SUM(D172:AML172)&gt;0,SUM(D172:AML172),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="15" t="str">
+        <f aca="false">IF(SUM(D173:AML173)&gt;0,SUM(D173:AML173),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="15" t="str">
+        <f aca="false">IF(SUM(D174:AML174)&gt;0,SUM(D174:AML174),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="15" t="str">
+        <f aca="false">IF(SUM(D175:AML175)&gt;0,SUM(D175:AML175),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="15" t="str">
+        <f aca="false">IF(SUM(D176:AML176)&gt;0,SUM(D176:AML176),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="15" t="str">
+        <f aca="false">IF(SUM(D177:AML177)&gt;0,SUM(D177:AML177),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="15" t="str">
+        <f aca="false">IF(SUM(D178:AML178)&gt;0,SUM(D178:AML178),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="15" t="str">
+        <f aca="false">IF(SUM(D179:AML179)&gt;0,SUM(D179:AML179),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="15" t="str">
+        <f aca="false">IF(SUM(D180:AML180)&gt;0,SUM(D180:AML180),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B181" s="15" t="str">
+        <f aca="false">IF(SUM(D181:AML181)&gt;0,SUM(D181:AML181),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B182" s="15" t="str">
+        <f aca="false">IF(SUM(D182:AML182)&gt;0,SUM(D182:AML182),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B183" s="15" t="str">
+        <f aca="false">IF(SUM(D183:AML183)&gt;0,SUM(D183:AML183),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B184" s="15" t="str">
+        <f aca="false">IF(SUM(D184:AML184)&gt;0,SUM(D184:AML184),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B185" s="15" t="str">
+        <f aca="false">IF(SUM(D185:AML185)&gt;0,SUM(D185:AML185),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B186" s="15" t="str">
+        <f aca="false">IF(SUM(D186:AML186)&gt;0,SUM(D186:AML186),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B187" s="15" t="str">
+        <f aca="false">IF(SUM(D187:AML187)&gt;0,SUM(D187:AML187),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B188" s="15" t="str">
+        <f aca="false">IF(SUM(D188:AML188)&gt;0,SUM(D188:AML188),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B189" s="15" t="str">
+        <f aca="false">IF(SUM(D189:AML189)&gt;0,SUM(D189:AML189),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="15" t="str">
+        <f aca="false">IF(SUM(D190:AML190)&gt;0,SUM(D190:AML190),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B191" s="15" t="str">
+        <f aca="false">IF(SUM(D191:AML191)&gt;0,SUM(D191:AML191),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="15" t="str">
+        <f aca="false">IF(SUM(D192:AML192)&gt;0,SUM(D192:AML192),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B193" s="15" t="str">
+        <f aca="false">IF(SUM(D193:AML193)&gt;0,SUM(D193:AML193),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B194" s="15" t="str">
+        <f aca="false">IF(SUM(D194:AML194)&gt;0,SUM(D194:AML194),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B195" s="15" t="str">
+        <f aca="false">IF(SUM(D195:AML195)&gt;0,SUM(D195:AML195),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="15" t="str">
+        <f aca="false">IF(SUM(D196:AML196)&gt;0,SUM(D196:AML196),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="15" t="str">
+        <f aca="false">IF(SUM(D197:AML197)&gt;0,SUM(D197:AML197),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B198" s="15" t="str">
+        <f aca="false">IF(SUM(D198:AML198)&gt;0,SUM(D198:AML198),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B199" s="15" t="str">
+        <f aca="false">IF(SUM(D199:AML199)&gt;0,SUM(D199:AML199),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="15" t="str">
+        <f aca="false">IF(SUM(D200:AML200)&gt;0,SUM(D200:AML200),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B201" s="15" t="str">
+        <f aca="false">IF(SUM(D201:AML201)&gt;0,SUM(D201:AML201),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B202" s="15" t="str">
+        <f aca="false">IF(SUM(D202:AML202)&gt;0,SUM(D202:AML202),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B203" s="15" t="str">
+        <f aca="false">IF(SUM(D203:AML203)&gt;0,SUM(D203:AML203),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="15" t="str">
+        <f aca="false">IF(SUM(D204:AML204)&gt;0,SUM(D204:AML204),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="15" t="str">
+        <f aca="false">IF(SUM(D205:AML205)&gt;0,SUM(D205:AML205),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="15" t="str">
+        <f aca="false">IF(SUM(D206:AML206)&gt;0,SUM(D206:AML206),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="15" t="str">
+        <f aca="false">IF(SUM(D207:AML207)&gt;0,SUM(D207:AML207),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="15" t="str">
+        <f aca="false">IF(SUM(D208:AML208)&gt;0,SUM(D208:AML208),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="15" t="str">
+        <f aca="false">IF(SUM(D209:AML209)&gt;0,SUM(D209:AML209),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="15" t="str">
+        <f aca="false">IF(SUM(D210:AML210)&gt;0,SUM(D210:AML210),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="15" t="str">
+        <f aca="false">IF(SUM(D211:AML211)&gt;0,SUM(D211:AML211),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="15" t="str">
+        <f aca="false">IF(SUM(D212:AML212)&gt;0,SUM(D212:AML212),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="15" t="str">
+        <f aca="false">IF(SUM(D213:AML213)&gt;0,SUM(D213:AML213),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="15" t="str">
+        <f aca="false">IF(SUM(D214:AML214)&gt;0,SUM(D214:AML214),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="15" t="str">
+        <f aca="false">IF(SUM(D215:AML215)&gt;0,SUM(D215:AML215),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="15" t="str">
+        <f aca="false">IF(SUM(D216:AML216)&gt;0,SUM(D216:AML216),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="15" t="str">
+        <f aca="false">IF(SUM(D217:AML217)&gt;0,SUM(D217:AML217),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="15" t="str">
+        <f aca="false">IF(SUM(D218:AML218)&gt;0,SUM(D218:AML218),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="15" t="str">
+        <f aca="false">IF(SUM(D219:AML219)&gt;0,SUM(D219:AML219),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B220" s="15" t="str">
+        <f aca="false">IF(SUM(D220:AML220)&gt;0,SUM(D220:AML220),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="15" t="str">
+        <f aca="false">IF(SUM(D221:AML221)&gt;0,SUM(D221:AML221),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B222" s="15" t="str">
+        <f aca="false">IF(SUM(D222:AML222)&gt;0,SUM(D222:AML222),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B223" s="15" t="str">
+        <f aca="false">IF(SUM(D223:AML223)&gt;0,SUM(D223:AML223),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B224" s="15" t="str">
+        <f aca="false">IF(SUM(D224:AML224)&gt;0,SUM(D224:AML224),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B225" s="15" t="str">
+        <f aca="false">IF(SUM(D225:AML225)&gt;0,SUM(D225:AML225),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B226" s="15" t="str">
+        <f aca="false">IF(SUM(D226:AML226)&gt;0,SUM(D226:AML226),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B227" s="15" t="str">
+        <f aca="false">IF(SUM(D227:AML227)&gt;0,SUM(D227:AML227),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B228" s="15" t="str">
+        <f aca="false">IF(SUM(D228:AML228)&gt;0,SUM(D228:AML228),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B229" s="15" t="str">
+        <f aca="false">IF(SUM(D229:AML229)&gt;0,SUM(D229:AML229),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B230" s="15" t="str">
+        <f aca="false">IF(SUM(D230:AML230)&gt;0,SUM(D230:AML230),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B231" s="15" t="str">
+        <f aca="false">IF(SUM(D231:AML231)&gt;0,SUM(D231:AML231),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B232" s="15" t="str">
+        <f aca="false">IF(SUM(D232:AML232)&gt;0,SUM(D232:AML232),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B233" s="15" t="str">
+        <f aca="false">IF(SUM(D233:AML233)&gt;0,SUM(D233:AML233),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B234" s="15" t="str">
+        <f aca="false">IF(SUM(D234:AML234)&gt;0,SUM(D234:AML234),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B235" s="15" t="str">
+        <f aca="false">IF(SUM(D235:AML235)&gt;0,SUM(D235:AML235),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="15" t="str">
+        <f aca="false">IF(SUM(D236:AML236)&gt;0,SUM(D236:AML236),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B237" s="15" t="str">
+        <f aca="false">IF(SUM(D237:AML237)&gt;0,SUM(D237:AML237),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B238" s="15" t="str">
+        <f aca="false">IF(SUM(D238:AML238)&gt;0,SUM(D238:AML238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B239" s="15" t="str">
+        <f aca="false">IF(SUM(D239:AML239)&gt;0,SUM(D239:AML239),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B240" s="15" t="str">
+        <f aca="false">IF(SUM(D240:AML240)&gt;0,SUM(D240:AML240),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B241" s="15" t="str">
+        <f aca="false">IF(SUM(D241:AML241)&gt;0,SUM(D241:AML241),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B242" s="15" t="str">
+        <f aca="false">IF(SUM(D242:AML242)&gt;0,SUM(D242:AML242),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B243" s="15" t="str">
+        <f aca="false">IF(SUM(D243:AML243)&gt;0,SUM(D243:AML243),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B244" s="15" t="str">
+        <f aca="false">IF(SUM(D244:AML244)&gt;0,SUM(D244:AML244),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B245" s="15" t="str">
+        <f aca="false">IF(SUM(D245:AML245)&gt;0,SUM(D245:AML245),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B246" s="15" t="str">
+        <f aca="false">IF(SUM(D246:AML246)&gt;0,SUM(D246:AML246),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B247" s="15" t="str">
+        <f aca="false">IF(SUM(D247:AML247)&gt;0,SUM(D247:AML247),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B248" s="15" t="str">
+        <f aca="false">IF(SUM(D248:AML248)&gt;0,SUM(D248:AML248),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B249" s="15" t="str">
+        <f aca="false">IF(SUM(D249:AML249)&gt;0,SUM(D249:AML249),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B250" s="15" t="str">
+        <f aca="false">IF(SUM(D250:AML250)&gt;0,SUM(D250:AML250),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B251" s="15" t="str">
+        <f aca="false">IF(SUM(D251:AML251)&gt;0,SUM(D251:AML251),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B252" s="15" t="str">
+        <f aca="false">IF(SUM(D252:AML252)&gt;0,SUM(D252:AML252),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B253" s="15" t="str">
+        <f aca="false">IF(SUM(D253:AML253)&gt;0,SUM(D253:AML253),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B254" s="15" t="str">
+        <f aca="false">IF(SUM(D254:AML254)&gt;0,SUM(D254:AML254),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B255" s="15" t="str">
+        <f aca="false">IF(SUM(D255:AML255)&gt;0,SUM(D255:AML255),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B256" s="15" t="str">
+        <f aca="false">IF(SUM(D256:AML256)&gt;0,SUM(D256:AML256),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Wei Larry</author>
+    <author>Larry Wei</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -606,10 +606,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -627,6 +623,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1142,150 +1142,150 @@
       <c r="CZ1" s="6"/>
       <c r="DA1" s="6"/>
     </row>
-    <row r="2" s="12" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="11" customFormat="true" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-      <c r="AL2" s="11"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="11"/>
-      <c r="AO2" s="11"/>
-      <c r="AP2" s="11"/>
-      <c r="AQ2" s="11"/>
-      <c r="AR2" s="11"/>
-      <c r="AS2" s="11"/>
-      <c r="AT2" s="11"/>
-      <c r="AU2" s="11"/>
-      <c r="AV2" s="11"/>
-      <c r="AW2" s="11"/>
-      <c r="AX2" s="11"/>
-      <c r="AY2" s="11"/>
-      <c r="AZ2" s="11"/>
-      <c r="BA2" s="11"/>
-      <c r="BB2" s="11"/>
-      <c r="BC2" s="11"/>
-      <c r="BD2" s="11"/>
-      <c r="BE2" s="11"/>
-      <c r="BF2" s="11"/>
-      <c r="BG2" s="11"/>
-      <c r="BH2" s="11"/>
-      <c r="BI2" s="11"/>
-      <c r="BJ2" s="11"/>
-      <c r="BK2" s="11"/>
-      <c r="BL2" s="11"/>
-      <c r="BM2" s="11"/>
-      <c r="BN2" s="11"/>
-      <c r="BO2" s="11"/>
-      <c r="BP2" s="11"/>
-      <c r="BQ2" s="11"/>
-      <c r="BR2" s="11"/>
-      <c r="BS2" s="11"/>
-      <c r="BT2" s="11"/>
-      <c r="BU2" s="11"/>
-      <c r="BV2" s="11"/>
-      <c r="BW2" s="11"/>
-      <c r="BX2" s="11"/>
-      <c r="BY2" s="11"/>
-      <c r="BZ2" s="11"/>
-      <c r="CA2" s="11"/>
-      <c r="CB2" s="11"/>
-      <c r="CC2" s="11"/>
-      <c r="CD2" s="11"/>
-      <c r="CE2" s="11"/>
-      <c r="CF2" s="11"/>
-      <c r="CG2" s="11"/>
-      <c r="CH2" s="11"/>
-      <c r="CI2" s="11"/>
-      <c r="CJ2" s="11"/>
-      <c r="CK2" s="11"/>
-      <c r="CL2" s="11"/>
-      <c r="CM2" s="11"/>
-      <c r="CN2" s="11"/>
-      <c r="CO2" s="11"/>
-      <c r="CP2" s="11"/>
-      <c r="CQ2" s="11"/>
-      <c r="CR2" s="11"/>
-      <c r="CS2" s="11"/>
-      <c r="CT2" s="11"/>
-      <c r="CU2" s="11"/>
-      <c r="CV2" s="11"/>
-      <c r="CW2" s="11"/>
-      <c r="CX2" s="11"/>
-      <c r="CY2" s="11"/>
-      <c r="CZ2" s="11"/>
-      <c r="DA2" s="11"/>
-    </row>
-    <row r="3" s="14" customFormat="true" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="10"/>
+      <c r="AL2" s="10"/>
+      <c r="AM2" s="10"/>
+      <c r="AN2" s="10"/>
+      <c r="AO2" s="10"/>
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10"/>
+      <c r="AR2" s="10"/>
+      <c r="AS2" s="10"/>
+      <c r="AT2" s="10"/>
+      <c r="AU2" s="10"/>
+      <c r="AV2" s="10"/>
+      <c r="AW2" s="10"/>
+      <c r="AX2" s="10"/>
+      <c r="AY2" s="10"/>
+      <c r="AZ2" s="10"/>
+      <c r="BA2" s="10"/>
+      <c r="BB2" s="10"/>
+      <c r="BC2" s="10"/>
+      <c r="BD2" s="10"/>
+      <c r="BE2" s="10"/>
+      <c r="BF2" s="10"/>
+      <c r="BG2" s="10"/>
+      <c r="BH2" s="10"/>
+      <c r="BI2" s="10"/>
+      <c r="BJ2" s="10"/>
+      <c r="BK2" s="10"/>
+      <c r="BL2" s="10"/>
+      <c r="BM2" s="10"/>
+      <c r="BN2" s="10"/>
+      <c r="BO2" s="10"/>
+      <c r="BP2" s="10"/>
+      <c r="BQ2" s="10"/>
+      <c r="BR2" s="10"/>
+      <c r="BS2" s="10"/>
+      <c r="BT2" s="10"/>
+      <c r="BU2" s="10"/>
+      <c r="BV2" s="10"/>
+      <c r="BW2" s="10"/>
+      <c r="BX2" s="10"/>
+      <c r="BY2" s="10"/>
+      <c r="BZ2" s="10"/>
+      <c r="CA2" s="10"/>
+      <c r="CB2" s="10"/>
+      <c r="CC2" s="10"/>
+      <c r="CD2" s="10"/>
+      <c r="CE2" s="10"/>
+      <c r="CF2" s="10"/>
+      <c r="CG2" s="10"/>
+      <c r="CH2" s="10"/>
+      <c r="CI2" s="10"/>
+      <c r="CJ2" s="10"/>
+      <c r="CK2" s="10"/>
+      <c r="CL2" s="10"/>
+      <c r="CM2" s="10"/>
+      <c r="CN2" s="10"/>
+      <c r="CO2" s="10"/>
+      <c r="CP2" s="10"/>
+      <c r="CQ2" s="10"/>
+      <c r="CR2" s="10"/>
+      <c r="CS2" s="10"/>
+      <c r="CT2" s="10"/>
+      <c r="CU2" s="10"/>
+      <c r="CV2" s="10"/>
+      <c r="CW2" s="10"/>
+      <c r="CX2" s="10"/>
+      <c r="CY2" s="10"/>
+      <c r="CZ2" s="10"/>
+      <c r="DA2" s="10"/>
+    </row>
+    <row r="3" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="13" t="str">
         <f aca="false">IF(SUM(B4:B1027)&gt;0,AVERAGE(B4:B1027),"")</f>
-        <v>60.7</v>
+        <v/>
       </c>
       <c r="C3" s="13" t="str">
         <f aca="false">IF(SUM(C4:C1027)&gt;0,AVERAGE(C4:C1027),"")</f>
@@ -1295,49 +1295,49 @@
         <f aca="false">IF(SUM(D4:D1027)&gt;0,AVERAGE(D4:D1027),"")</f>
         <v/>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="13" t="str">
         <f aca="false">IF(SUM(E4:E1027)&gt;0,AVERAGE(E4:E1027),"")</f>
-        <v>2.84615384615385</v>
-      </c>
-      <c r="F3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="F3" s="13" t="str">
         <f aca="false">IF(SUM(F4:F1027)&gt;0,AVERAGE(F4:F1027),"")</f>
-        <v>2.03846153846154</v>
-      </c>
-      <c r="G3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="G3" s="13" t="str">
         <f aca="false">IF(SUM(G4:G1027)&gt;0,AVERAGE(G4:G1027),"")</f>
-        <v>0.384615384615385</v>
-      </c>
-      <c r="H3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="H3" s="13" t="str">
         <f aca="false">IF(SUM(H4:H1027)&gt;0,AVERAGE(H4:H1027),"")</f>
-        <v>2.61538461538462</v>
-      </c>
-      <c r="I3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="I3" s="13" t="str">
         <f aca="false">IF(SUM(I4:I1027)&gt;0,AVERAGE(I4:I1027),"")</f>
-        <v>2.80769230769231</v>
-      </c>
-      <c r="J3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="J3" s="13" t="str">
         <f aca="false">IF(SUM(J4:J1027)&gt;0,AVERAGE(J4:J1027),"")</f>
-        <v>2.57692307692308</v>
-      </c>
-      <c r="K3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="K3" s="13" t="str">
         <f aca="false">IF(SUM(K4:K1027)&gt;0,AVERAGE(K4:K1027),"")</f>
-        <v>12.0576923076923</v>
-      </c>
-      <c r="L3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="L3" s="13" t="str">
         <f aca="false">IF(SUM(L4:L1027)&gt;0,AVERAGE(L4:L1027),"")</f>
-        <v>3.61538461538462</v>
-      </c>
-      <c r="M3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="M3" s="13" t="str">
         <f aca="false">IF(SUM(M4:M1027)&gt;0,AVERAGE(M4:M1027),"")</f>
-        <v>4.90384615384615</v>
-      </c>
-      <c r="N3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="N3" s="13" t="str">
         <f aca="false">IF(SUM(N4:N1027)&gt;0,AVERAGE(N4:N1027),"")</f>
-        <v>5.53846153846154</v>
-      </c>
-      <c r="O3" s="13" t="n">
+        <v/>
+      </c>
+      <c r="O3" s="13" t="str">
         <f aca="false">IF(SUM(O4:O1027)&gt;0,AVERAGE(O4:O1027),"")</f>
-        <v>18.9807692307692</v>
+        <v/>
       </c>
       <c r="P3" s="13" t="str">
         <f aca="false">IF(SUM(P4:P1027)&gt;0,AVERAGE(P4:P1027),"")</f>
@@ -1792,49 +1792,27 @@
         <v/>
       </c>
     </row>
-    <row r="4" s="19" customFormat="true" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="15" t="str">
         <f aca="false">IF(SUM(D4:AML4)&gt;0,SUM(D4:AML4),"")</f>
-        <v>86.5</v>
+        <v/>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
-      <c r="E4" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="L4" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="N4" s="17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O4" s="17" t="n">
-        <v>25</v>
-      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="18"/>
       <c r="R4" s="18"/>
@@ -1926,49 +1904,27 @@
       <c r="CZ4" s="18"/>
       <c r="DA4" s="18"/>
     </row>
-    <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="15" t="str">
         <f aca="false">IF(SUM(D5:AML5)&gt;0,SUM(D5:AML5),"")</f>
-        <v>87</v>
+        <v/>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="20"/>
-      <c r="E5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="L5" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N5" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
       <c r="R5" s="21"/>
@@ -2060,49 +2016,27 @@
       <c r="CZ5" s="21"/>
       <c r="DA5" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="15" t="str">
         <f aca="false">IF(SUM(D6:AML6)&gt;0,SUM(D6:AML6),"")</f>
-        <v>80</v>
+        <v/>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L6" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
       <c r="R6" s="21"/>
@@ -2194,49 +2128,27 @@
       <c r="CZ6" s="21"/>
       <c r="DA6" s="21"/>
     </row>
-    <row r="7" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="15" t="str">
         <f aca="false">IF(SUM(D7:AML7)&gt;0,SUM(D7:AML7),"")</f>
-        <v>68.5</v>
+        <v/>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="20"/>
-      <c r="E7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="N7" s="20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O7" s="20" t="n">
-        <v>24</v>
-      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
       <c r="P7" s="21"/>
       <c r="Q7" s="21"/>
       <c r="R7" s="21"/>
@@ -2328,49 +2240,27 @@
       <c r="CZ7" s="21"/>
       <c r="DA7" s="21"/>
     </row>
-    <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="15" t="str">
         <f aca="false">IF(SUM(D8:AML8)&gt;0,SUM(D8:AML8),"")</f>
-        <v>81</v>
+        <v/>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="20"/>
-      <c r="E8" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="L8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O8" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
       <c r="R8" s="21"/>
@@ -2462,49 +2352,27 @@
       <c r="CZ8" s="21"/>
       <c r="DA8" s="21"/>
     </row>
-    <row r="9" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="15" t="str">
         <f aca="false">IF(SUM(D9:AML9)&gt;0,SUM(D9:AML9),"")</f>
-        <v>82</v>
+        <v/>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="20"/>
-      <c r="E9" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L9" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" s="20" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="21"/>
       <c r="R9" s="21"/>
@@ -2596,49 +2464,27 @@
       <c r="CZ9" s="21"/>
       <c r="DA9" s="21"/>
     </row>
-    <row r="10" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="15" t="str">
         <f aca="false">IF(SUM(D10:AML10)&gt;0,SUM(D10:AML10),"")</f>
-        <v>77</v>
+        <v/>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="20"/>
-      <c r="E10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="L10" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N10" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
       <c r="R10" s="21"/>
@@ -2730,49 +2576,27 @@
       <c r="CZ10" s="21"/>
       <c r="DA10" s="21"/>
     </row>
-    <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="15" t="str">
         <f aca="false">IF(SUM(D11:AML11)&gt;0,SUM(D11:AML11),"")</f>
-        <v>73</v>
+        <v/>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O11" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
       <c r="R11" s="21"/>
@@ -2864,49 +2688,27 @@
       <c r="CZ11" s="21"/>
       <c r="DA11" s="21"/>
     </row>
-    <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="15" t="str">
         <f aca="false">IF(SUM(D12:AML12)&gt;0,SUM(D12:AML12),"")</f>
-        <v>86.5</v>
+        <v/>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="20"/>
-      <c r="E12" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="L12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" s="20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O12" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
       <c r="P12" s="21"/>
       <c r="Q12" s="21"/>
       <c r="R12" s="21"/>
@@ -2998,49 +2800,27 @@
       <c r="CZ12" s="21"/>
       <c r="DA12" s="21"/>
     </row>
-    <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="15" t="str">
         <f aca="false">IF(SUM(D13:AML13)&gt;0,SUM(D13:AML13),"")</f>
-        <v>70</v>
+        <v/>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="20"/>
-      <c r="E13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="L13" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O13" s="20" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
       <c r="P13" s="21"/>
       <c r="Q13" s="21"/>
       <c r="R13" s="21"/>
@@ -3132,49 +2912,27 @@
       <c r="CZ13" s="21"/>
       <c r="DA13" s="21"/>
     </row>
-    <row r="14" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="15" t="str">
         <f aca="false">IF(SUM(D14:AML14)&gt;0,SUM(D14:AML14),"")</f>
-        <v>70.5</v>
+        <v/>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L14" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N14" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
       <c r="R14" s="21"/>
@@ -3266,49 +3024,27 @@
       <c r="CZ14" s="21"/>
       <c r="DA14" s="21"/>
     </row>
-    <row r="15" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="15" t="str">
         <f aca="false">IF(SUM(D15:AML15)&gt;0,SUM(D15:AML15),"")</f>
-        <v>80.5</v>
+        <v/>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="L15" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N15" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
       <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
       <c r="R15" s="21"/>
@@ -3400,49 +3136,27 @@
       <c r="CZ15" s="21"/>
       <c r="DA15" s="21"/>
     </row>
-    <row r="16" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="15" t="str">
         <f aca="false">IF(SUM(D16:AML16)&gt;0,SUM(D16:AML16),"")</f>
-        <v>69.5</v>
+        <v/>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="L16" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O16" s="20" t="n">
-        <v>24</v>
-      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
       <c r="R16" s="21"/>
@@ -3534,49 +3248,27 @@
       <c r="CZ16" s="21"/>
       <c r="DA16" s="21"/>
     </row>
-    <row r="17" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="15" t="str">
         <f aca="false">IF(SUM(D17:AML17)&gt;0,SUM(D17:AML17),"")</f>
-        <v>77.5</v>
+        <v/>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="L17" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N17" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O17" s="20" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
       <c r="R17" s="21"/>
@@ -3668,49 +3360,27 @@
       <c r="CZ17" s="21"/>
       <c r="DA17" s="21"/>
     </row>
-    <row r="18" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="15" t="str">
         <f aca="false">IF(SUM(D18:AML18)&gt;0,SUM(D18:AML18),"")</f>
-        <v>72.5</v>
+        <v/>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="20"/>
-      <c r="E18" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="L18" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N18" s="20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O18" s="20" t="n">
-        <v>24</v>
-      </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="21"/>
       <c r="R18" s="21"/>
@@ -3802,49 +3472,27 @@
       <c r="CZ18" s="21"/>
       <c r="DA18" s="21"/>
     </row>
-    <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="15" t="str">
         <f aca="false">IF(SUM(D19:AML19)&gt;0,SUM(D19:AML19),"")</f>
-        <v>80</v>
+        <v/>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="L19" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="N19" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
       <c r="P19" s="21"/>
       <c r="Q19" s="21"/>
       <c r="R19" s="21"/>
@@ -3936,49 +3584,27 @@
       <c r="CZ19" s="21"/>
       <c r="DA19" s="21"/>
     </row>
-    <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="15" t="str">
         <f aca="false">IF(SUM(D20:AML20)&gt;0,SUM(D20:AML20),"")</f>
-        <v>59.5</v>
+        <v/>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N20" s="20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O20" s="20" t="n">
-        <v>25</v>
-      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
       <c r="R20" s="21"/>
@@ -4070,49 +3696,27 @@
       <c r="CZ20" s="21"/>
       <c r="DA20" s="21"/>
     </row>
-    <row r="21" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="15" t="str">
         <f aca="false">IF(SUM(D21:AML21)&gt;0,SUM(D21:AML21),"")</f>
-        <v>49.5</v>
+        <v/>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" s="20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O21" s="20" t="n">
-        <v>23</v>
-      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
       <c r="P21" s="21"/>
       <c r="Q21" s="21"/>
       <c r="R21" s="21"/>
@@ -4204,49 +3808,27 @@
       <c r="CZ21" s="21"/>
       <c r="DA21" s="21"/>
     </row>
-    <row r="22" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="15" t="str">
         <f aca="false">IF(SUM(D22:AML22)&gt;0,SUM(D22:AML22),"")</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O22" s="20" t="n">
-        <v>9</v>
-      </c>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="21"/>
       <c r="R22" s="21"/>
@@ -4338,49 +3920,27 @@
       <c r="CZ22" s="21"/>
       <c r="DA22" s="21"/>
     </row>
-    <row r="23" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="15" t="str">
         <f aca="false">IF(SUM(D23:AML23)&gt;0,SUM(D23:AML23),"")</f>
-        <v>34</v>
+        <v/>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
       <c r="R23" s="21"/>
@@ -4472,49 +4032,27 @@
       <c r="CZ23" s="21"/>
       <c r="DA23" s="21"/>
     </row>
-    <row r="24" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="15" t="str">
         <f aca="false">IF(SUM(D24:AML24)&gt;0,SUM(D24:AML24),"")</f>
-        <v>19.5</v>
+        <v/>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O24" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="21"/>
       <c r="R24" s="21"/>
@@ -4606,49 +4144,27 @@
       <c r="CZ24" s="21"/>
       <c r="DA24" s="21"/>
     </row>
-    <row r="25" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="15" t="n">
+      <c r="B25" s="15" t="str">
         <f aca="false">IF(SUM(D25:AML25)&gt;0,SUM(D25:AML25),"")</f>
-        <v>31</v>
+        <v/>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="20"/>
-      <c r="E25" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="20" t="n">
-        <v>12</v>
-      </c>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="R25" s="21"/>
@@ -4740,49 +4256,27 @@
       <c r="CZ25" s="21"/>
       <c r="DA25" s="21"/>
     </row>
-    <row r="26" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="15" t="str">
         <f aca="false">IF(SUM(D26:AML26)&gt;0,SUM(D26:AML26),"")</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="20" t="n">
-        <v>12</v>
-      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="20"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
       <c r="R26" s="21"/>
@@ -4874,49 +4368,27 @@
       <c r="CZ26" s="21"/>
       <c r="DA26" s="21"/>
     </row>
-    <row r="27" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="15" t="str">
         <f aca="false">IF(SUM(D27:AML27)&gt;0,SUM(D27:AML27),"")</f>
-        <v>11.5</v>
+        <v/>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O27" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
       <c r="R27" s="21"/>
@@ -5008,49 +4480,27 @@
       <c r="CZ27" s="21"/>
       <c r="DA27" s="21"/>
     </row>
-    <row r="28" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="15" t="str">
         <f aca="false">IF(SUM(D28:AML28)&gt;0,SUM(D28:AML28),"")</f>
-        <v>19.5</v>
+        <v/>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="20"/>
-      <c r="E28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O28" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
       <c r="R28" s="21"/>
@@ -5152,39 +4602,17 @@
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
       <c r="R29" s="21"/>
@@ -6841,11 +6269,7 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" error="输入错误，检测到非数字（小数）。" errorStyle="stop" errorTitle="错误提示：" operator="between" prompt="请输入数字（或小数）。" promptTitle="提示：" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4:O29" type="decimal">
-      <formula1>-100</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
+  <dataValidations count="6">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -6854,13 +6278,29 @@
       <formula1>12:0:0 am</formula1>
       <formula2>12:0:0 am</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="请输入题目，题目的分数放在“（）”或“()”里，如“（2分）”、“（2）”、“(2分)”、“(2)”都可以。" promptTitle="请输入题目" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:DX2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="请输入考试分数（整数、小数，可以为负数）。" promptTitle="请输入考试分数。" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4:DX256" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="请勿更改。" promptTitle="请勿更改" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3:DX3 B4:B256" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="批注的内容会被当作评语。" promptTitle="提示：" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A4:A256" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -61,6 +61,24 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">202404032000”</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">、“</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">20240403 2000”</t>
         </r>
         <r>
           <rPr>
@@ -205,6 +223,24 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">202404032130”</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Noto Sans CJK SC"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">、“</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">20240403 2130”</t>
         </r>
         <r>
           <rPr>
@@ -360,11 +396,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="@"/>
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -576,7 +611,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -637,7 +672,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -654,10 +689,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1142,7 +1173,7 @@
       <c r="CZ1" s="6"/>
       <c r="DA1" s="6"/>
     </row>
-    <row r="2" s="11" customFormat="true" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="11" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -1913,108 +1944,108 @@
         <v/>
       </c>
       <c r="C5" s="16"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
-      <c r="AF5" s="21"/>
-      <c r="AG5" s="21"/>
-      <c r="AH5" s="21"/>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="21"/>
-      <c r="AK5" s="21"/>
-      <c r="AL5" s="21"/>
-      <c r="AM5" s="21"/>
-      <c r="AN5" s="21"/>
-      <c r="AO5" s="21"/>
-      <c r="AP5" s="21"/>
-      <c r="AQ5" s="21"/>
-      <c r="AR5" s="21"/>
-      <c r="AS5" s="21"/>
-      <c r="AT5" s="21"/>
-      <c r="AU5" s="21"/>
-      <c r="AV5" s="21"/>
-      <c r="AW5" s="21"/>
-      <c r="AX5" s="21"/>
-      <c r="AY5" s="21"/>
-      <c r="AZ5" s="21"/>
-      <c r="BA5" s="21"/>
-      <c r="BB5" s="21"/>
-      <c r="BC5" s="21"/>
-      <c r="BD5" s="21"/>
-      <c r="BE5" s="21"/>
-      <c r="BF5" s="21"/>
-      <c r="BG5" s="21"/>
-      <c r="BH5" s="21"/>
-      <c r="BI5" s="21"/>
-      <c r="BJ5" s="21"/>
-      <c r="BK5" s="21"/>
-      <c r="BL5" s="21"/>
-      <c r="BM5" s="21"/>
-      <c r="BN5" s="21"/>
-      <c r="BO5" s="21"/>
-      <c r="BP5" s="21"/>
-      <c r="BQ5" s="21"/>
-      <c r="BR5" s="21"/>
-      <c r="BS5" s="21"/>
-      <c r="BT5" s="21"/>
-      <c r="BU5" s="21"/>
-      <c r="BV5" s="21"/>
-      <c r="BW5" s="21"/>
-      <c r="BX5" s="21"/>
-      <c r="BY5" s="21"/>
-      <c r="BZ5" s="21"/>
-      <c r="CA5" s="21"/>
-      <c r="CB5" s="21"/>
-      <c r="CC5" s="21"/>
-      <c r="CD5" s="21"/>
-      <c r="CE5" s="21"/>
-      <c r="CF5" s="21"/>
-      <c r="CG5" s="21"/>
-      <c r="CH5" s="21"/>
-      <c r="CI5" s="21"/>
-      <c r="CJ5" s="21"/>
-      <c r="CK5" s="21"/>
-      <c r="CL5" s="21"/>
-      <c r="CM5" s="21"/>
-      <c r="CN5" s="21"/>
-      <c r="CO5" s="21"/>
-      <c r="CP5" s="21"/>
-      <c r="CQ5" s="21"/>
-      <c r="CR5" s="21"/>
-      <c r="CS5" s="21"/>
-      <c r="CT5" s="21"/>
-      <c r="CU5" s="21"/>
-      <c r="CV5" s="21"/>
-      <c r="CW5" s="21"/>
-      <c r="CX5" s="21"/>
-      <c r="CY5" s="21"/>
-      <c r="CZ5" s="21"/>
-      <c r="DA5" s="21"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="20"/>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="20"/>
+      <c r="AS5" s="20"/>
+      <c r="AT5" s="20"/>
+      <c r="AU5" s="20"/>
+      <c r="AV5" s="20"/>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="20"/>
+      <c r="BA5" s="20"/>
+      <c r="BB5" s="20"/>
+      <c r="BC5" s="20"/>
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="20"/>
+      <c r="BF5" s="20"/>
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="20"/>
+      <c r="BI5" s="20"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="20"/>
+      <c r="BL5" s="20"/>
+      <c r="BM5" s="20"/>
+      <c r="BN5" s="20"/>
+      <c r="BO5" s="20"/>
+      <c r="BP5" s="20"/>
+      <c r="BQ5" s="20"/>
+      <c r="BR5" s="20"/>
+      <c r="BS5" s="20"/>
+      <c r="BT5" s="20"/>
+      <c r="BU5" s="20"/>
+      <c r="BV5" s="20"/>
+      <c r="BW5" s="20"/>
+      <c r="BX5" s="20"/>
+      <c r="BY5" s="20"/>
+      <c r="BZ5" s="20"/>
+      <c r="CA5" s="20"/>
+      <c r="CB5" s="20"/>
+      <c r="CC5" s="20"/>
+      <c r="CD5" s="20"/>
+      <c r="CE5" s="20"/>
+      <c r="CF5" s="20"/>
+      <c r="CG5" s="20"/>
+      <c r="CH5" s="20"/>
+      <c r="CI5" s="20"/>
+      <c r="CJ5" s="20"/>
+      <c r="CK5" s="20"/>
+      <c r="CL5" s="20"/>
+      <c r="CM5" s="20"/>
+      <c r="CN5" s="20"/>
+      <c r="CO5" s="20"/>
+      <c r="CP5" s="20"/>
+      <c r="CQ5" s="20"/>
+      <c r="CR5" s="20"/>
+      <c r="CS5" s="20"/>
+      <c r="CT5" s="20"/>
+      <c r="CU5" s="20"/>
+      <c r="CV5" s="20"/>
+      <c r="CW5" s="20"/>
+      <c r="CX5" s="20"/>
+      <c r="CY5" s="20"/>
+      <c r="CZ5" s="20"/>
+      <c r="DA5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -2025,108 +2056,108 @@
         <v/>
       </c>
       <c r="C6" s="16"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="21"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
-      <c r="AD6" s="21"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="21"/>
-      <c r="AG6" s="21"/>
-      <c r="AH6" s="21"/>
-      <c r="AI6" s="21"/>
-      <c r="AJ6" s="21"/>
-      <c r="AK6" s="21"/>
-      <c r="AL6" s="21"/>
-      <c r="AM6" s="21"/>
-      <c r="AN6" s="21"/>
-      <c r="AO6" s="21"/>
-      <c r="AP6" s="21"/>
-      <c r="AQ6" s="21"/>
-      <c r="AR6" s="21"/>
-      <c r="AS6" s="21"/>
-      <c r="AT6" s="21"/>
-      <c r="AU6" s="21"/>
-      <c r="AV6" s="21"/>
-      <c r="AW6" s="21"/>
-      <c r="AX6" s="21"/>
-      <c r="AY6" s="21"/>
-      <c r="AZ6" s="21"/>
-      <c r="BA6" s="21"/>
-      <c r="BB6" s="21"/>
-      <c r="BC6" s="21"/>
-      <c r="BD6" s="21"/>
-      <c r="BE6" s="21"/>
-      <c r="BF6" s="21"/>
-      <c r="BG6" s="21"/>
-      <c r="BH6" s="21"/>
-      <c r="BI6" s="21"/>
-      <c r="BJ6" s="21"/>
-      <c r="BK6" s="21"/>
-      <c r="BL6" s="21"/>
-      <c r="BM6" s="21"/>
-      <c r="BN6" s="21"/>
-      <c r="BO6" s="21"/>
-      <c r="BP6" s="21"/>
-      <c r="BQ6" s="21"/>
-      <c r="BR6" s="21"/>
-      <c r="BS6" s="21"/>
-      <c r="BT6" s="21"/>
-      <c r="BU6" s="21"/>
-      <c r="BV6" s="21"/>
-      <c r="BW6" s="21"/>
-      <c r="BX6" s="21"/>
-      <c r="BY6" s="21"/>
-      <c r="BZ6" s="21"/>
-      <c r="CA6" s="21"/>
-      <c r="CB6" s="21"/>
-      <c r="CC6" s="21"/>
-      <c r="CD6" s="21"/>
-      <c r="CE6" s="21"/>
-      <c r="CF6" s="21"/>
-      <c r="CG6" s="21"/>
-      <c r="CH6" s="21"/>
-      <c r="CI6" s="21"/>
-      <c r="CJ6" s="21"/>
-      <c r="CK6" s="21"/>
-      <c r="CL6" s="21"/>
-      <c r="CM6" s="21"/>
-      <c r="CN6" s="21"/>
-      <c r="CO6" s="21"/>
-      <c r="CP6" s="21"/>
-      <c r="CQ6" s="21"/>
-      <c r="CR6" s="21"/>
-      <c r="CS6" s="21"/>
-      <c r="CT6" s="21"/>
-      <c r="CU6" s="21"/>
-      <c r="CV6" s="21"/>
-      <c r="CW6" s="21"/>
-      <c r="CX6" s="21"/>
-      <c r="CY6" s="21"/>
-      <c r="CZ6" s="21"/>
-      <c r="DA6" s="21"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="20"/>
+      <c r="AJ6" s="20"/>
+      <c r="AK6" s="20"/>
+      <c r="AL6" s="20"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="20"/>
+      <c r="AP6" s="20"/>
+      <c r="AQ6" s="20"/>
+      <c r="AR6" s="20"/>
+      <c r="AS6" s="20"/>
+      <c r="AT6" s="20"/>
+      <c r="AU6" s="20"/>
+      <c r="AV6" s="20"/>
+      <c r="AW6" s="20"/>
+      <c r="AX6" s="20"/>
+      <c r="AY6" s="20"/>
+      <c r="AZ6" s="20"/>
+      <c r="BA6" s="20"/>
+      <c r="BB6" s="20"/>
+      <c r="BC6" s="20"/>
+      <c r="BD6" s="20"/>
+      <c r="BE6" s="20"/>
+      <c r="BF6" s="20"/>
+      <c r="BG6" s="20"/>
+      <c r="BH6" s="20"/>
+      <c r="BI6" s="20"/>
+      <c r="BJ6" s="20"/>
+      <c r="BK6" s="20"/>
+      <c r="BL6" s="20"/>
+      <c r="BM6" s="20"/>
+      <c r="BN6" s="20"/>
+      <c r="BO6" s="20"/>
+      <c r="BP6" s="20"/>
+      <c r="BQ6" s="20"/>
+      <c r="BR6" s="20"/>
+      <c r="BS6" s="20"/>
+      <c r="BT6" s="20"/>
+      <c r="BU6" s="20"/>
+      <c r="BV6" s="20"/>
+      <c r="BW6" s="20"/>
+      <c r="BX6" s="20"/>
+      <c r="BY6" s="20"/>
+      <c r="BZ6" s="20"/>
+      <c r="CA6" s="20"/>
+      <c r="CB6" s="20"/>
+      <c r="CC6" s="20"/>
+      <c r="CD6" s="20"/>
+      <c r="CE6" s="20"/>
+      <c r="CF6" s="20"/>
+      <c r="CG6" s="20"/>
+      <c r="CH6" s="20"/>
+      <c r="CI6" s="20"/>
+      <c r="CJ6" s="20"/>
+      <c r="CK6" s="20"/>
+      <c r="CL6" s="20"/>
+      <c r="CM6" s="20"/>
+      <c r="CN6" s="20"/>
+      <c r="CO6" s="20"/>
+      <c r="CP6" s="20"/>
+      <c r="CQ6" s="20"/>
+      <c r="CR6" s="20"/>
+      <c r="CS6" s="20"/>
+      <c r="CT6" s="20"/>
+      <c r="CU6" s="20"/>
+      <c r="CV6" s="20"/>
+      <c r="CW6" s="20"/>
+      <c r="CX6" s="20"/>
+      <c r="CY6" s="20"/>
+      <c r="CZ6" s="20"/>
+      <c r="DA6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -2137,108 +2168,108 @@
         <v/>
       </c>
       <c r="C7" s="16"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
-      <c r="V7" s="21"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="21"/>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="21"/>
-      <c r="AG7" s="21"/>
-      <c r="AH7" s="21"/>
-      <c r="AI7" s="21"/>
-      <c r="AJ7" s="21"/>
-      <c r="AK7" s="21"/>
-      <c r="AL7" s="21"/>
-      <c r="AM7" s="21"/>
-      <c r="AN7" s="21"/>
-      <c r="AO7" s="21"/>
-      <c r="AP7" s="21"/>
-      <c r="AQ7" s="21"/>
-      <c r="AR7" s="21"/>
-      <c r="AS7" s="21"/>
-      <c r="AT7" s="21"/>
-      <c r="AU7" s="21"/>
-      <c r="AV7" s="21"/>
-      <c r="AW7" s="21"/>
-      <c r="AX7" s="21"/>
-      <c r="AY7" s="21"/>
-      <c r="AZ7" s="21"/>
-      <c r="BA7" s="21"/>
-      <c r="BB7" s="21"/>
-      <c r="BC7" s="21"/>
-      <c r="BD7" s="21"/>
-      <c r="BE7" s="21"/>
-      <c r="BF7" s="21"/>
-      <c r="BG7" s="21"/>
-      <c r="BH7" s="21"/>
-      <c r="BI7" s="21"/>
-      <c r="BJ7" s="21"/>
-      <c r="BK7" s="21"/>
-      <c r="BL7" s="21"/>
-      <c r="BM7" s="21"/>
-      <c r="BN7" s="21"/>
-      <c r="BO7" s="21"/>
-      <c r="BP7" s="21"/>
-      <c r="BQ7" s="21"/>
-      <c r="BR7" s="21"/>
-      <c r="BS7" s="21"/>
-      <c r="BT7" s="21"/>
-      <c r="BU7" s="21"/>
-      <c r="BV7" s="21"/>
-      <c r="BW7" s="21"/>
-      <c r="BX7" s="21"/>
-      <c r="BY7" s="21"/>
-      <c r="BZ7" s="21"/>
-      <c r="CA7" s="21"/>
-      <c r="CB7" s="21"/>
-      <c r="CC7" s="21"/>
-      <c r="CD7" s="21"/>
-      <c r="CE7" s="21"/>
-      <c r="CF7" s="21"/>
-      <c r="CG7" s="21"/>
-      <c r="CH7" s="21"/>
-      <c r="CI7" s="21"/>
-      <c r="CJ7" s="21"/>
-      <c r="CK7" s="21"/>
-      <c r="CL7" s="21"/>
-      <c r="CM7" s="21"/>
-      <c r="CN7" s="21"/>
-      <c r="CO7" s="21"/>
-      <c r="CP7" s="21"/>
-      <c r="CQ7" s="21"/>
-      <c r="CR7" s="21"/>
-      <c r="CS7" s="21"/>
-      <c r="CT7" s="21"/>
-      <c r="CU7" s="21"/>
-      <c r="CV7" s="21"/>
-      <c r="CW7" s="21"/>
-      <c r="CX7" s="21"/>
-      <c r="CY7" s="21"/>
-      <c r="CZ7" s="21"/>
-      <c r="DA7" s="21"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
+      <c r="AI7" s="20"/>
+      <c r="AJ7" s="20"/>
+      <c r="AK7" s="20"/>
+      <c r="AL7" s="20"/>
+      <c r="AM7" s="20"/>
+      <c r="AN7" s="20"/>
+      <c r="AO7" s="20"/>
+      <c r="AP7" s="20"/>
+      <c r="AQ7" s="20"/>
+      <c r="AR7" s="20"/>
+      <c r="AS7" s="20"/>
+      <c r="AT7" s="20"/>
+      <c r="AU7" s="20"/>
+      <c r="AV7" s="20"/>
+      <c r="AW7" s="20"/>
+      <c r="AX7" s="20"/>
+      <c r="AY7" s="20"/>
+      <c r="AZ7" s="20"/>
+      <c r="BA7" s="20"/>
+      <c r="BB7" s="20"/>
+      <c r="BC7" s="20"/>
+      <c r="BD7" s="20"/>
+      <c r="BE7" s="20"/>
+      <c r="BF7" s="20"/>
+      <c r="BG7" s="20"/>
+      <c r="BH7" s="20"/>
+      <c r="BI7" s="20"/>
+      <c r="BJ7" s="20"/>
+      <c r="BK7" s="20"/>
+      <c r="BL7" s="20"/>
+      <c r="BM7" s="20"/>
+      <c r="BN7" s="20"/>
+      <c r="BO7" s="20"/>
+      <c r="BP7" s="20"/>
+      <c r="BQ7" s="20"/>
+      <c r="BR7" s="20"/>
+      <c r="BS7" s="20"/>
+      <c r="BT7" s="20"/>
+      <c r="BU7" s="20"/>
+      <c r="BV7" s="20"/>
+      <c r="BW7" s="20"/>
+      <c r="BX7" s="20"/>
+      <c r="BY7" s="20"/>
+      <c r="BZ7" s="20"/>
+      <c r="CA7" s="20"/>
+      <c r="CB7" s="20"/>
+      <c r="CC7" s="20"/>
+      <c r="CD7" s="20"/>
+      <c r="CE7" s="20"/>
+      <c r="CF7" s="20"/>
+      <c r="CG7" s="20"/>
+      <c r="CH7" s="20"/>
+      <c r="CI7" s="20"/>
+      <c r="CJ7" s="20"/>
+      <c r="CK7" s="20"/>
+      <c r="CL7" s="20"/>
+      <c r="CM7" s="20"/>
+      <c r="CN7" s="20"/>
+      <c r="CO7" s="20"/>
+      <c r="CP7" s="20"/>
+      <c r="CQ7" s="20"/>
+      <c r="CR7" s="20"/>
+      <c r="CS7" s="20"/>
+      <c r="CT7" s="20"/>
+      <c r="CU7" s="20"/>
+      <c r="CV7" s="20"/>
+      <c r="CW7" s="20"/>
+      <c r="CX7" s="20"/>
+      <c r="CY7" s="20"/>
+      <c r="CZ7" s="20"/>
+      <c r="DA7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -2249,108 +2280,108 @@
         <v/>
       </c>
       <c r="C8" s="16"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="21"/>
-      <c r="AE8" s="21"/>
-      <c r="AF8" s="21"/>
-      <c r="AG8" s="21"/>
-      <c r="AH8" s="21"/>
-      <c r="AI8" s="21"/>
-      <c r="AJ8" s="21"/>
-      <c r="AK8" s="21"/>
-      <c r="AL8" s="21"/>
-      <c r="AM8" s="21"/>
-      <c r="AN8" s="21"/>
-      <c r="AO8" s="21"/>
-      <c r="AP8" s="21"/>
-      <c r="AQ8" s="21"/>
-      <c r="AR8" s="21"/>
-      <c r="AS8" s="21"/>
-      <c r="AT8" s="21"/>
-      <c r="AU8" s="21"/>
-      <c r="AV8" s="21"/>
-      <c r="AW8" s="21"/>
-      <c r="AX8" s="21"/>
-      <c r="AY8" s="21"/>
-      <c r="AZ8" s="21"/>
-      <c r="BA8" s="21"/>
-      <c r="BB8" s="21"/>
-      <c r="BC8" s="21"/>
-      <c r="BD8" s="21"/>
-      <c r="BE8" s="21"/>
-      <c r="BF8" s="21"/>
-      <c r="BG8" s="21"/>
-      <c r="BH8" s="21"/>
-      <c r="BI8" s="21"/>
-      <c r="BJ8" s="21"/>
-      <c r="BK8" s="21"/>
-      <c r="BL8" s="21"/>
-      <c r="BM8" s="21"/>
-      <c r="BN8" s="21"/>
-      <c r="BO8" s="21"/>
-      <c r="BP8" s="21"/>
-      <c r="BQ8" s="21"/>
-      <c r="BR8" s="21"/>
-      <c r="BS8" s="21"/>
-      <c r="BT8" s="21"/>
-      <c r="BU8" s="21"/>
-      <c r="BV8" s="21"/>
-      <c r="BW8" s="21"/>
-      <c r="BX8" s="21"/>
-      <c r="BY8" s="21"/>
-      <c r="BZ8" s="21"/>
-      <c r="CA8" s="21"/>
-      <c r="CB8" s="21"/>
-      <c r="CC8" s="21"/>
-      <c r="CD8" s="21"/>
-      <c r="CE8" s="21"/>
-      <c r="CF8" s="21"/>
-      <c r="CG8" s="21"/>
-      <c r="CH8" s="21"/>
-      <c r="CI8" s="21"/>
-      <c r="CJ8" s="21"/>
-      <c r="CK8" s="21"/>
-      <c r="CL8" s="21"/>
-      <c r="CM8" s="21"/>
-      <c r="CN8" s="21"/>
-      <c r="CO8" s="21"/>
-      <c r="CP8" s="21"/>
-      <c r="CQ8" s="21"/>
-      <c r="CR8" s="21"/>
-      <c r="CS8" s="21"/>
-      <c r="CT8" s="21"/>
-      <c r="CU8" s="21"/>
-      <c r="CV8" s="21"/>
-      <c r="CW8" s="21"/>
-      <c r="CX8" s="21"/>
-      <c r="CY8" s="21"/>
-      <c r="CZ8" s="21"/>
-      <c r="DA8" s="21"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="20"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="20"/>
+      <c r="AM8" s="20"/>
+      <c r="AN8" s="20"/>
+      <c r="AO8" s="20"/>
+      <c r="AP8" s="20"/>
+      <c r="AQ8" s="20"/>
+      <c r="AR8" s="20"/>
+      <c r="AS8" s="20"/>
+      <c r="AT8" s="20"/>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="20"/>
+      <c r="AW8" s="20"/>
+      <c r="AX8" s="20"/>
+      <c r="AY8" s="20"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="20"/>
+      <c r="BB8" s="20"/>
+      <c r="BC8" s="20"/>
+      <c r="BD8" s="20"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="20"/>
+      <c r="BG8" s="20"/>
+      <c r="BH8" s="20"/>
+      <c r="BI8" s="20"/>
+      <c r="BJ8" s="20"/>
+      <c r="BK8" s="20"/>
+      <c r="BL8" s="20"/>
+      <c r="BM8" s="20"/>
+      <c r="BN8" s="20"/>
+      <c r="BO8" s="20"/>
+      <c r="BP8" s="20"/>
+      <c r="BQ8" s="20"/>
+      <c r="BR8" s="20"/>
+      <c r="BS8" s="20"/>
+      <c r="BT8" s="20"/>
+      <c r="BU8" s="20"/>
+      <c r="BV8" s="20"/>
+      <c r="BW8" s="20"/>
+      <c r="BX8" s="20"/>
+      <c r="BY8" s="20"/>
+      <c r="BZ8" s="20"/>
+      <c r="CA8" s="20"/>
+      <c r="CB8" s="20"/>
+      <c r="CC8" s="20"/>
+      <c r="CD8" s="20"/>
+      <c r="CE8" s="20"/>
+      <c r="CF8" s="20"/>
+      <c r="CG8" s="20"/>
+      <c r="CH8" s="20"/>
+      <c r="CI8" s="20"/>
+      <c r="CJ8" s="20"/>
+      <c r="CK8" s="20"/>
+      <c r="CL8" s="20"/>
+      <c r="CM8" s="20"/>
+      <c r="CN8" s="20"/>
+      <c r="CO8" s="20"/>
+      <c r="CP8" s="20"/>
+      <c r="CQ8" s="20"/>
+      <c r="CR8" s="20"/>
+      <c r="CS8" s="20"/>
+      <c r="CT8" s="20"/>
+      <c r="CU8" s="20"/>
+      <c r="CV8" s="20"/>
+      <c r="CW8" s="20"/>
+      <c r="CX8" s="20"/>
+      <c r="CY8" s="20"/>
+      <c r="CZ8" s="20"/>
+      <c r="DA8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -2361,108 +2392,108 @@
         <v/>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
-      <c r="AE9" s="21"/>
-      <c r="AF9" s="21"/>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
-      <c r="AI9" s="21"/>
-      <c r="AJ9" s="21"/>
-      <c r="AK9" s="21"/>
-      <c r="AL9" s="21"/>
-      <c r="AM9" s="21"/>
-      <c r="AN9" s="21"/>
-      <c r="AO9" s="21"/>
-      <c r="AP9" s="21"/>
-      <c r="AQ9" s="21"/>
-      <c r="AR9" s="21"/>
-      <c r="AS9" s="21"/>
-      <c r="AT9" s="21"/>
-      <c r="AU9" s="21"/>
-      <c r="AV9" s="21"/>
-      <c r="AW9" s="21"/>
-      <c r="AX9" s="21"/>
-      <c r="AY9" s="21"/>
-      <c r="AZ9" s="21"/>
-      <c r="BA9" s="21"/>
-      <c r="BB9" s="21"/>
-      <c r="BC9" s="21"/>
-      <c r="BD9" s="21"/>
-      <c r="BE9" s="21"/>
-      <c r="BF9" s="21"/>
-      <c r="BG9" s="21"/>
-      <c r="BH9" s="21"/>
-      <c r="BI9" s="21"/>
-      <c r="BJ9" s="21"/>
-      <c r="BK9" s="21"/>
-      <c r="BL9" s="21"/>
-      <c r="BM9" s="21"/>
-      <c r="BN9" s="21"/>
-      <c r="BO9" s="21"/>
-      <c r="BP9" s="21"/>
-      <c r="BQ9" s="21"/>
-      <c r="BR9" s="21"/>
-      <c r="BS9" s="21"/>
-      <c r="BT9" s="21"/>
-      <c r="BU9" s="21"/>
-      <c r="BV9" s="21"/>
-      <c r="BW9" s="21"/>
-      <c r="BX9" s="21"/>
-      <c r="BY9" s="21"/>
-      <c r="BZ9" s="21"/>
-      <c r="CA9" s="21"/>
-      <c r="CB9" s="21"/>
-      <c r="CC9" s="21"/>
-      <c r="CD9" s="21"/>
-      <c r="CE9" s="21"/>
-      <c r="CF9" s="21"/>
-      <c r="CG9" s="21"/>
-      <c r="CH9" s="21"/>
-      <c r="CI9" s="21"/>
-      <c r="CJ9" s="21"/>
-      <c r="CK9" s="21"/>
-      <c r="CL9" s="21"/>
-      <c r="CM9" s="21"/>
-      <c r="CN9" s="21"/>
-      <c r="CO9" s="21"/>
-      <c r="CP9" s="21"/>
-      <c r="CQ9" s="21"/>
-      <c r="CR9" s="21"/>
-      <c r="CS9" s="21"/>
-      <c r="CT9" s="21"/>
-      <c r="CU9" s="21"/>
-      <c r="CV9" s="21"/>
-      <c r="CW9" s="21"/>
-      <c r="CX9" s="21"/>
-      <c r="CY9" s="21"/>
-      <c r="CZ9" s="21"/>
-      <c r="DA9" s="21"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="20"/>
+      <c r="AJ9" s="20"/>
+      <c r="AK9" s="20"/>
+      <c r="AL9" s="20"/>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="20"/>
+      <c r="AO9" s="20"/>
+      <c r="AP9" s="20"/>
+      <c r="AQ9" s="20"/>
+      <c r="AR9" s="20"/>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="20"/>
+      <c r="AU9" s="20"/>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="20"/>
+      <c r="AY9" s="20"/>
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="20"/>
+      <c r="BB9" s="20"/>
+      <c r="BC9" s="20"/>
+      <c r="BD9" s="20"/>
+      <c r="BE9" s="20"/>
+      <c r="BF9" s="20"/>
+      <c r="BG9" s="20"/>
+      <c r="BH9" s="20"/>
+      <c r="BI9" s="20"/>
+      <c r="BJ9" s="20"/>
+      <c r="BK9" s="20"/>
+      <c r="BL9" s="20"/>
+      <c r="BM9" s="20"/>
+      <c r="BN9" s="20"/>
+      <c r="BO9" s="20"/>
+      <c r="BP9" s="20"/>
+      <c r="BQ9" s="20"/>
+      <c r="BR9" s="20"/>
+      <c r="BS9" s="20"/>
+      <c r="BT9" s="20"/>
+      <c r="BU9" s="20"/>
+      <c r="BV9" s="20"/>
+      <c r="BW9" s="20"/>
+      <c r="BX9" s="20"/>
+      <c r="BY9" s="20"/>
+      <c r="BZ9" s="20"/>
+      <c r="CA9" s="20"/>
+      <c r="CB9" s="20"/>
+      <c r="CC9" s="20"/>
+      <c r="CD9" s="20"/>
+      <c r="CE9" s="20"/>
+      <c r="CF9" s="20"/>
+      <c r="CG9" s="20"/>
+      <c r="CH9" s="20"/>
+      <c r="CI9" s="20"/>
+      <c r="CJ9" s="20"/>
+      <c r="CK9" s="20"/>
+      <c r="CL9" s="20"/>
+      <c r="CM9" s="20"/>
+      <c r="CN9" s="20"/>
+      <c r="CO9" s="20"/>
+      <c r="CP9" s="20"/>
+      <c r="CQ9" s="20"/>
+      <c r="CR9" s="20"/>
+      <c r="CS9" s="20"/>
+      <c r="CT9" s="20"/>
+      <c r="CU9" s="20"/>
+      <c r="CV9" s="20"/>
+      <c r="CW9" s="20"/>
+      <c r="CX9" s="20"/>
+      <c r="CY9" s="20"/>
+      <c r="CZ9" s="20"/>
+      <c r="DA9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -2473,108 +2504,108 @@
         <v/>
       </c>
       <c r="C10" s="16"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="21"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="21"/>
-      <c r="Z10" s="21"/>
-      <c r="AA10" s="21"/>
-      <c r="AB10" s="21"/>
-      <c r="AC10" s="21"/>
-      <c r="AD10" s="21"/>
-      <c r="AE10" s="21"/>
-      <c r="AF10" s="21"/>
-      <c r="AG10" s="21"/>
-      <c r="AH10" s="21"/>
-      <c r="AI10" s="21"/>
-      <c r="AJ10" s="21"/>
-      <c r="AK10" s="21"/>
-      <c r="AL10" s="21"/>
-      <c r="AM10" s="21"/>
-      <c r="AN10" s="21"/>
-      <c r="AO10" s="21"/>
-      <c r="AP10" s="21"/>
-      <c r="AQ10" s="21"/>
-      <c r="AR10" s="21"/>
-      <c r="AS10" s="21"/>
-      <c r="AT10" s="21"/>
-      <c r="AU10" s="21"/>
-      <c r="AV10" s="21"/>
-      <c r="AW10" s="21"/>
-      <c r="AX10" s="21"/>
-      <c r="AY10" s="21"/>
-      <c r="AZ10" s="21"/>
-      <c r="BA10" s="21"/>
-      <c r="BB10" s="21"/>
-      <c r="BC10" s="21"/>
-      <c r="BD10" s="21"/>
-      <c r="BE10" s="21"/>
-      <c r="BF10" s="21"/>
-      <c r="BG10" s="21"/>
-      <c r="BH10" s="21"/>
-      <c r="BI10" s="21"/>
-      <c r="BJ10" s="21"/>
-      <c r="BK10" s="21"/>
-      <c r="BL10" s="21"/>
-      <c r="BM10" s="21"/>
-      <c r="BN10" s="21"/>
-      <c r="BO10" s="21"/>
-      <c r="BP10" s="21"/>
-      <c r="BQ10" s="21"/>
-      <c r="BR10" s="21"/>
-      <c r="BS10" s="21"/>
-      <c r="BT10" s="21"/>
-      <c r="BU10" s="21"/>
-      <c r="BV10" s="21"/>
-      <c r="BW10" s="21"/>
-      <c r="BX10" s="21"/>
-      <c r="BY10" s="21"/>
-      <c r="BZ10" s="21"/>
-      <c r="CA10" s="21"/>
-      <c r="CB10" s="21"/>
-      <c r="CC10" s="21"/>
-      <c r="CD10" s="21"/>
-      <c r="CE10" s="21"/>
-      <c r="CF10" s="21"/>
-      <c r="CG10" s="21"/>
-      <c r="CH10" s="21"/>
-      <c r="CI10" s="21"/>
-      <c r="CJ10" s="21"/>
-      <c r="CK10" s="21"/>
-      <c r="CL10" s="21"/>
-      <c r="CM10" s="21"/>
-      <c r="CN10" s="21"/>
-      <c r="CO10" s="21"/>
-      <c r="CP10" s="21"/>
-      <c r="CQ10" s="21"/>
-      <c r="CR10" s="21"/>
-      <c r="CS10" s="21"/>
-      <c r="CT10" s="21"/>
-      <c r="CU10" s="21"/>
-      <c r="CV10" s="21"/>
-      <c r="CW10" s="21"/>
-      <c r="CX10" s="21"/>
-      <c r="CY10" s="21"/>
-      <c r="CZ10" s="21"/>
-      <c r="DA10" s="21"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="20"/>
+      <c r="AK10" s="20"/>
+      <c r="AL10" s="20"/>
+      <c r="AM10" s="20"/>
+      <c r="AN10" s="20"/>
+      <c r="AO10" s="20"/>
+      <c r="AP10" s="20"/>
+      <c r="AQ10" s="20"/>
+      <c r="AR10" s="20"/>
+      <c r="AS10" s="20"/>
+      <c r="AT10" s="20"/>
+      <c r="AU10" s="20"/>
+      <c r="AV10" s="20"/>
+      <c r="AW10" s="20"/>
+      <c r="AX10" s="20"/>
+      <c r="AY10" s="20"/>
+      <c r="AZ10" s="20"/>
+      <c r="BA10" s="20"/>
+      <c r="BB10" s="20"/>
+      <c r="BC10" s="20"/>
+      <c r="BD10" s="20"/>
+      <c r="BE10" s="20"/>
+      <c r="BF10" s="20"/>
+      <c r="BG10" s="20"/>
+      <c r="BH10" s="20"/>
+      <c r="BI10" s="20"/>
+      <c r="BJ10" s="20"/>
+      <c r="BK10" s="20"/>
+      <c r="BL10" s="20"/>
+      <c r="BM10" s="20"/>
+      <c r="BN10" s="20"/>
+      <c r="BO10" s="20"/>
+      <c r="BP10" s="20"/>
+      <c r="BQ10" s="20"/>
+      <c r="BR10" s="20"/>
+      <c r="BS10" s="20"/>
+      <c r="BT10" s="20"/>
+      <c r="BU10" s="20"/>
+      <c r="BV10" s="20"/>
+      <c r="BW10" s="20"/>
+      <c r="BX10" s="20"/>
+      <c r="BY10" s="20"/>
+      <c r="BZ10" s="20"/>
+      <c r="CA10" s="20"/>
+      <c r="CB10" s="20"/>
+      <c r="CC10" s="20"/>
+      <c r="CD10" s="20"/>
+      <c r="CE10" s="20"/>
+      <c r="CF10" s="20"/>
+      <c r="CG10" s="20"/>
+      <c r="CH10" s="20"/>
+      <c r="CI10" s="20"/>
+      <c r="CJ10" s="20"/>
+      <c r="CK10" s="20"/>
+      <c r="CL10" s="20"/>
+      <c r="CM10" s="20"/>
+      <c r="CN10" s="20"/>
+      <c r="CO10" s="20"/>
+      <c r="CP10" s="20"/>
+      <c r="CQ10" s="20"/>
+      <c r="CR10" s="20"/>
+      <c r="CS10" s="20"/>
+      <c r="CT10" s="20"/>
+      <c r="CU10" s="20"/>
+      <c r="CV10" s="20"/>
+      <c r="CW10" s="20"/>
+      <c r="CX10" s="20"/>
+      <c r="CY10" s="20"/>
+      <c r="CZ10" s="20"/>
+      <c r="DA10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -2585,108 +2616,108 @@
         <v/>
       </c>
       <c r="C11" s="16"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="21"/>
-      <c r="AG11" s="21"/>
-      <c r="AH11" s="21"/>
-      <c r="AI11" s="21"/>
-      <c r="AJ11" s="21"/>
-      <c r="AK11" s="21"/>
-      <c r="AL11" s="21"/>
-      <c r="AM11" s="21"/>
-      <c r="AN11" s="21"/>
-      <c r="AO11" s="21"/>
-      <c r="AP11" s="21"/>
-      <c r="AQ11" s="21"/>
-      <c r="AR11" s="21"/>
-      <c r="AS11" s="21"/>
-      <c r="AT11" s="21"/>
-      <c r="AU11" s="21"/>
-      <c r="AV11" s="21"/>
-      <c r="AW11" s="21"/>
-      <c r="AX11" s="21"/>
-      <c r="AY11" s="21"/>
-      <c r="AZ11" s="21"/>
-      <c r="BA11" s="21"/>
-      <c r="BB11" s="21"/>
-      <c r="BC11" s="21"/>
-      <c r="BD11" s="21"/>
-      <c r="BE11" s="21"/>
-      <c r="BF11" s="21"/>
-      <c r="BG11" s="21"/>
-      <c r="BH11" s="21"/>
-      <c r="BI11" s="21"/>
-      <c r="BJ11" s="21"/>
-      <c r="BK11" s="21"/>
-      <c r="BL11" s="21"/>
-      <c r="BM11" s="21"/>
-      <c r="BN11" s="21"/>
-      <c r="BO11" s="21"/>
-      <c r="BP11" s="21"/>
-      <c r="BQ11" s="21"/>
-      <c r="BR11" s="21"/>
-      <c r="BS11" s="21"/>
-      <c r="BT11" s="21"/>
-      <c r="BU11" s="21"/>
-      <c r="BV11" s="21"/>
-      <c r="BW11" s="21"/>
-      <c r="BX11" s="21"/>
-      <c r="BY11" s="21"/>
-      <c r="BZ11" s="21"/>
-      <c r="CA11" s="21"/>
-      <c r="CB11" s="21"/>
-      <c r="CC11" s="21"/>
-      <c r="CD11" s="21"/>
-      <c r="CE11" s="21"/>
-      <c r="CF11" s="21"/>
-      <c r="CG11" s="21"/>
-      <c r="CH11" s="21"/>
-      <c r="CI11" s="21"/>
-      <c r="CJ11" s="21"/>
-      <c r="CK11" s="21"/>
-      <c r="CL11" s="21"/>
-      <c r="CM11" s="21"/>
-      <c r="CN11" s="21"/>
-      <c r="CO11" s="21"/>
-      <c r="CP11" s="21"/>
-      <c r="CQ11" s="21"/>
-      <c r="CR11" s="21"/>
-      <c r="CS11" s="21"/>
-      <c r="CT11" s="21"/>
-      <c r="CU11" s="21"/>
-      <c r="CV11" s="21"/>
-      <c r="CW11" s="21"/>
-      <c r="CX11" s="21"/>
-      <c r="CY11" s="21"/>
-      <c r="CZ11" s="21"/>
-      <c r="DA11" s="21"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="20"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="20"/>
+      <c r="AM11" s="20"/>
+      <c r="AN11" s="20"/>
+      <c r="AO11" s="20"/>
+      <c r="AP11" s="20"/>
+      <c r="AQ11" s="20"/>
+      <c r="AR11" s="20"/>
+      <c r="AS11" s="20"/>
+      <c r="AT11" s="20"/>
+      <c r="AU11" s="20"/>
+      <c r="AV11" s="20"/>
+      <c r="AW11" s="20"/>
+      <c r="AX11" s="20"/>
+      <c r="AY11" s="20"/>
+      <c r="AZ11" s="20"/>
+      <c r="BA11" s="20"/>
+      <c r="BB11" s="20"/>
+      <c r="BC11" s="20"/>
+      <c r="BD11" s="20"/>
+      <c r="BE11" s="20"/>
+      <c r="BF11" s="20"/>
+      <c r="BG11" s="20"/>
+      <c r="BH11" s="20"/>
+      <c r="BI11" s="20"/>
+      <c r="BJ11" s="20"/>
+      <c r="BK11" s="20"/>
+      <c r="BL11" s="20"/>
+      <c r="BM11" s="20"/>
+      <c r="BN11" s="20"/>
+      <c r="BO11" s="20"/>
+      <c r="BP11" s="20"/>
+      <c r="BQ11" s="20"/>
+      <c r="BR11" s="20"/>
+      <c r="BS11" s="20"/>
+      <c r="BT11" s="20"/>
+      <c r="BU11" s="20"/>
+      <c r="BV11" s="20"/>
+      <c r="BW11" s="20"/>
+      <c r="BX11" s="20"/>
+      <c r="BY11" s="20"/>
+      <c r="BZ11" s="20"/>
+      <c r="CA11" s="20"/>
+      <c r="CB11" s="20"/>
+      <c r="CC11" s="20"/>
+      <c r="CD11" s="20"/>
+      <c r="CE11" s="20"/>
+      <c r="CF11" s="20"/>
+      <c r="CG11" s="20"/>
+      <c r="CH11" s="20"/>
+      <c r="CI11" s="20"/>
+      <c r="CJ11" s="20"/>
+      <c r="CK11" s="20"/>
+      <c r="CL11" s="20"/>
+      <c r="CM11" s="20"/>
+      <c r="CN11" s="20"/>
+      <c r="CO11" s="20"/>
+      <c r="CP11" s="20"/>
+      <c r="CQ11" s="20"/>
+      <c r="CR11" s="20"/>
+      <c r="CS11" s="20"/>
+      <c r="CT11" s="20"/>
+      <c r="CU11" s="20"/>
+      <c r="CV11" s="20"/>
+      <c r="CW11" s="20"/>
+      <c r="CX11" s="20"/>
+      <c r="CY11" s="20"/>
+      <c r="CZ11" s="20"/>
+      <c r="DA11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -2697,108 +2728,108 @@
         <v/>
       </c>
       <c r="C12" s="16"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="21"/>
-      <c r="AD12" s="21"/>
-      <c r="AE12" s="21"/>
-      <c r="AF12" s="21"/>
-      <c r="AG12" s="21"/>
-      <c r="AH12" s="21"/>
-      <c r="AI12" s="21"/>
-      <c r="AJ12" s="21"/>
-      <c r="AK12" s="21"/>
-      <c r="AL12" s="21"/>
-      <c r="AM12" s="21"/>
-      <c r="AN12" s="21"/>
-      <c r="AO12" s="21"/>
-      <c r="AP12" s="21"/>
-      <c r="AQ12" s="21"/>
-      <c r="AR12" s="21"/>
-      <c r="AS12" s="21"/>
-      <c r="AT12" s="21"/>
-      <c r="AU12" s="21"/>
-      <c r="AV12" s="21"/>
-      <c r="AW12" s="21"/>
-      <c r="AX12" s="21"/>
-      <c r="AY12" s="21"/>
-      <c r="AZ12" s="21"/>
-      <c r="BA12" s="21"/>
-      <c r="BB12" s="21"/>
-      <c r="BC12" s="21"/>
-      <c r="BD12" s="21"/>
-      <c r="BE12" s="21"/>
-      <c r="BF12" s="21"/>
-      <c r="BG12" s="21"/>
-      <c r="BH12" s="21"/>
-      <c r="BI12" s="21"/>
-      <c r="BJ12" s="21"/>
-      <c r="BK12" s="21"/>
-      <c r="BL12" s="21"/>
-      <c r="BM12" s="21"/>
-      <c r="BN12" s="21"/>
-      <c r="BO12" s="21"/>
-      <c r="BP12" s="21"/>
-      <c r="BQ12" s="21"/>
-      <c r="BR12" s="21"/>
-      <c r="BS12" s="21"/>
-      <c r="BT12" s="21"/>
-      <c r="BU12" s="21"/>
-      <c r="BV12" s="21"/>
-      <c r="BW12" s="21"/>
-      <c r="BX12" s="21"/>
-      <c r="BY12" s="21"/>
-      <c r="BZ12" s="21"/>
-      <c r="CA12" s="21"/>
-      <c r="CB12" s="21"/>
-      <c r="CC12" s="21"/>
-      <c r="CD12" s="21"/>
-      <c r="CE12" s="21"/>
-      <c r="CF12" s="21"/>
-      <c r="CG12" s="21"/>
-      <c r="CH12" s="21"/>
-      <c r="CI12" s="21"/>
-      <c r="CJ12" s="21"/>
-      <c r="CK12" s="21"/>
-      <c r="CL12" s="21"/>
-      <c r="CM12" s="21"/>
-      <c r="CN12" s="21"/>
-      <c r="CO12" s="21"/>
-      <c r="CP12" s="21"/>
-      <c r="CQ12" s="21"/>
-      <c r="CR12" s="21"/>
-      <c r="CS12" s="21"/>
-      <c r="CT12" s="21"/>
-      <c r="CU12" s="21"/>
-      <c r="CV12" s="21"/>
-      <c r="CW12" s="21"/>
-      <c r="CX12" s="21"/>
-      <c r="CY12" s="21"/>
-      <c r="CZ12" s="21"/>
-      <c r="DA12" s="21"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
+      <c r="AH12" s="20"/>
+      <c r="AI12" s="20"/>
+      <c r="AJ12" s="20"/>
+      <c r="AK12" s="20"/>
+      <c r="AL12" s="20"/>
+      <c r="AM12" s="20"/>
+      <c r="AN12" s="20"/>
+      <c r="AO12" s="20"/>
+      <c r="AP12" s="20"/>
+      <c r="AQ12" s="20"/>
+      <c r="AR12" s="20"/>
+      <c r="AS12" s="20"/>
+      <c r="AT12" s="20"/>
+      <c r="AU12" s="20"/>
+      <c r="AV12" s="20"/>
+      <c r="AW12" s="20"/>
+      <c r="AX12" s="20"/>
+      <c r="AY12" s="20"/>
+      <c r="AZ12" s="20"/>
+      <c r="BA12" s="20"/>
+      <c r="BB12" s="20"/>
+      <c r="BC12" s="20"/>
+      <c r="BD12" s="20"/>
+      <c r="BE12" s="20"/>
+      <c r="BF12" s="20"/>
+      <c r="BG12" s="20"/>
+      <c r="BH12" s="20"/>
+      <c r="BI12" s="20"/>
+      <c r="BJ12" s="20"/>
+      <c r="BK12" s="20"/>
+      <c r="BL12" s="20"/>
+      <c r="BM12" s="20"/>
+      <c r="BN12" s="20"/>
+      <c r="BO12" s="20"/>
+      <c r="BP12" s="20"/>
+      <c r="BQ12" s="20"/>
+      <c r="BR12" s="20"/>
+      <c r="BS12" s="20"/>
+      <c r="BT12" s="20"/>
+      <c r="BU12" s="20"/>
+      <c r="BV12" s="20"/>
+      <c r="BW12" s="20"/>
+      <c r="BX12" s="20"/>
+      <c r="BY12" s="20"/>
+      <c r="BZ12" s="20"/>
+      <c r="CA12" s="20"/>
+      <c r="CB12" s="20"/>
+      <c r="CC12" s="20"/>
+      <c r="CD12" s="20"/>
+      <c r="CE12" s="20"/>
+      <c r="CF12" s="20"/>
+      <c r="CG12" s="20"/>
+      <c r="CH12" s="20"/>
+      <c r="CI12" s="20"/>
+      <c r="CJ12" s="20"/>
+      <c r="CK12" s="20"/>
+      <c r="CL12" s="20"/>
+      <c r="CM12" s="20"/>
+      <c r="CN12" s="20"/>
+      <c r="CO12" s="20"/>
+      <c r="CP12" s="20"/>
+      <c r="CQ12" s="20"/>
+      <c r="CR12" s="20"/>
+      <c r="CS12" s="20"/>
+      <c r="CT12" s="20"/>
+      <c r="CU12" s="20"/>
+      <c r="CV12" s="20"/>
+      <c r="CW12" s="20"/>
+      <c r="CX12" s="20"/>
+      <c r="CY12" s="20"/>
+      <c r="CZ12" s="20"/>
+      <c r="DA12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -2809,108 +2840,108 @@
         <v/>
       </c>
       <c r="C13" s="16"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
-      <c r="AS13" s="21"/>
-      <c r="AT13" s="21"/>
-      <c r="AU13" s="21"/>
-      <c r="AV13" s="21"/>
-      <c r="AW13" s="21"/>
-      <c r="AX13" s="21"/>
-      <c r="AY13" s="21"/>
-      <c r="AZ13" s="21"/>
-      <c r="BA13" s="21"/>
-      <c r="BB13" s="21"/>
-      <c r="BC13" s="21"/>
-      <c r="BD13" s="21"/>
-      <c r="BE13" s="21"/>
-      <c r="BF13" s="21"/>
-      <c r="BG13" s="21"/>
-      <c r="BH13" s="21"/>
-      <c r="BI13" s="21"/>
-      <c r="BJ13" s="21"/>
-      <c r="BK13" s="21"/>
-      <c r="BL13" s="21"/>
-      <c r="BM13" s="21"/>
-      <c r="BN13" s="21"/>
-      <c r="BO13" s="21"/>
-      <c r="BP13" s="21"/>
-      <c r="BQ13" s="21"/>
-      <c r="BR13" s="21"/>
-      <c r="BS13" s="21"/>
-      <c r="BT13" s="21"/>
-      <c r="BU13" s="21"/>
-      <c r="BV13" s="21"/>
-      <c r="BW13" s="21"/>
-      <c r="BX13" s="21"/>
-      <c r="BY13" s="21"/>
-      <c r="BZ13" s="21"/>
-      <c r="CA13" s="21"/>
-      <c r="CB13" s="21"/>
-      <c r="CC13" s="21"/>
-      <c r="CD13" s="21"/>
-      <c r="CE13" s="21"/>
-      <c r="CF13" s="21"/>
-      <c r="CG13" s="21"/>
-      <c r="CH13" s="21"/>
-      <c r="CI13" s="21"/>
-      <c r="CJ13" s="21"/>
-      <c r="CK13" s="21"/>
-      <c r="CL13" s="21"/>
-      <c r="CM13" s="21"/>
-      <c r="CN13" s="21"/>
-      <c r="CO13" s="21"/>
-      <c r="CP13" s="21"/>
-      <c r="CQ13" s="21"/>
-      <c r="CR13" s="21"/>
-      <c r="CS13" s="21"/>
-      <c r="CT13" s="21"/>
-      <c r="CU13" s="21"/>
-      <c r="CV13" s="21"/>
-      <c r="CW13" s="21"/>
-      <c r="CX13" s="21"/>
-      <c r="CY13" s="21"/>
-      <c r="CZ13" s="21"/>
-      <c r="DA13" s="21"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
+      <c r="AH13" s="20"/>
+      <c r="AI13" s="20"/>
+      <c r="AJ13" s="20"/>
+      <c r="AK13" s="20"/>
+      <c r="AL13" s="20"/>
+      <c r="AM13" s="20"/>
+      <c r="AN13" s="20"/>
+      <c r="AO13" s="20"/>
+      <c r="AP13" s="20"/>
+      <c r="AQ13" s="20"/>
+      <c r="AR13" s="20"/>
+      <c r="AS13" s="20"/>
+      <c r="AT13" s="20"/>
+      <c r="AU13" s="20"/>
+      <c r="AV13" s="20"/>
+      <c r="AW13" s="20"/>
+      <c r="AX13" s="20"/>
+      <c r="AY13" s="20"/>
+      <c r="AZ13" s="20"/>
+      <c r="BA13" s="20"/>
+      <c r="BB13" s="20"/>
+      <c r="BC13" s="20"/>
+      <c r="BD13" s="20"/>
+      <c r="BE13" s="20"/>
+      <c r="BF13" s="20"/>
+      <c r="BG13" s="20"/>
+      <c r="BH13" s="20"/>
+      <c r="BI13" s="20"/>
+      <c r="BJ13" s="20"/>
+      <c r="BK13" s="20"/>
+      <c r="BL13" s="20"/>
+      <c r="BM13" s="20"/>
+      <c r="BN13" s="20"/>
+      <c r="BO13" s="20"/>
+      <c r="BP13" s="20"/>
+      <c r="BQ13" s="20"/>
+      <c r="BR13" s="20"/>
+      <c r="BS13" s="20"/>
+      <c r="BT13" s="20"/>
+      <c r="BU13" s="20"/>
+      <c r="BV13" s="20"/>
+      <c r="BW13" s="20"/>
+      <c r="BX13" s="20"/>
+      <c r="BY13" s="20"/>
+      <c r="BZ13" s="20"/>
+      <c r="CA13" s="20"/>
+      <c r="CB13" s="20"/>
+      <c r="CC13" s="20"/>
+      <c r="CD13" s="20"/>
+      <c r="CE13" s="20"/>
+      <c r="CF13" s="20"/>
+      <c r="CG13" s="20"/>
+      <c r="CH13" s="20"/>
+      <c r="CI13" s="20"/>
+      <c r="CJ13" s="20"/>
+      <c r="CK13" s="20"/>
+      <c r="CL13" s="20"/>
+      <c r="CM13" s="20"/>
+      <c r="CN13" s="20"/>
+      <c r="CO13" s="20"/>
+      <c r="CP13" s="20"/>
+      <c r="CQ13" s="20"/>
+      <c r="CR13" s="20"/>
+      <c r="CS13" s="20"/>
+      <c r="CT13" s="20"/>
+      <c r="CU13" s="20"/>
+      <c r="CV13" s="20"/>
+      <c r="CW13" s="20"/>
+      <c r="CX13" s="20"/>
+      <c r="CY13" s="20"/>
+      <c r="CZ13" s="20"/>
+      <c r="DA13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -2921,108 +2952,108 @@
         <v/>
       </c>
       <c r="C14" s="16"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
-      <c r="AK14" s="21"/>
-      <c r="AL14" s="21"/>
-      <c r="AM14" s="21"/>
-      <c r="AN14" s="21"/>
-      <c r="AO14" s="21"/>
-      <c r="AP14" s="21"/>
-      <c r="AQ14" s="21"/>
-      <c r="AR14" s="21"/>
-      <c r="AS14" s="21"/>
-      <c r="AT14" s="21"/>
-      <c r="AU14" s="21"/>
-      <c r="AV14" s="21"/>
-      <c r="AW14" s="21"/>
-      <c r="AX14" s="21"/>
-      <c r="AY14" s="21"/>
-      <c r="AZ14" s="21"/>
-      <c r="BA14" s="21"/>
-      <c r="BB14" s="21"/>
-      <c r="BC14" s="21"/>
-      <c r="BD14" s="21"/>
-      <c r="BE14" s="21"/>
-      <c r="BF14" s="21"/>
-      <c r="BG14" s="21"/>
-      <c r="BH14" s="21"/>
-      <c r="BI14" s="21"/>
-      <c r="BJ14" s="21"/>
-      <c r="BK14" s="21"/>
-      <c r="BL14" s="21"/>
-      <c r="BM14" s="21"/>
-      <c r="BN14" s="21"/>
-      <c r="BO14" s="21"/>
-      <c r="BP14" s="21"/>
-      <c r="BQ14" s="21"/>
-      <c r="BR14" s="21"/>
-      <c r="BS14" s="21"/>
-      <c r="BT14" s="21"/>
-      <c r="BU14" s="21"/>
-      <c r="BV14" s="21"/>
-      <c r="BW14" s="21"/>
-      <c r="BX14" s="21"/>
-      <c r="BY14" s="21"/>
-      <c r="BZ14" s="21"/>
-      <c r="CA14" s="21"/>
-      <c r="CB14" s="21"/>
-      <c r="CC14" s="21"/>
-      <c r="CD14" s="21"/>
-      <c r="CE14" s="21"/>
-      <c r="CF14" s="21"/>
-      <c r="CG14" s="21"/>
-      <c r="CH14" s="21"/>
-      <c r="CI14" s="21"/>
-      <c r="CJ14" s="21"/>
-      <c r="CK14" s="21"/>
-      <c r="CL14" s="21"/>
-      <c r="CM14" s="21"/>
-      <c r="CN14" s="21"/>
-      <c r="CO14" s="21"/>
-      <c r="CP14" s="21"/>
-      <c r="CQ14" s="21"/>
-      <c r="CR14" s="21"/>
-      <c r="CS14" s="21"/>
-      <c r="CT14" s="21"/>
-      <c r="CU14" s="21"/>
-      <c r="CV14" s="21"/>
-      <c r="CW14" s="21"/>
-      <c r="CX14" s="21"/>
-      <c r="CY14" s="21"/>
-      <c r="CZ14" s="21"/>
-      <c r="DA14" s="21"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="20"/>
+      <c r="AH14" s="20"/>
+      <c r="AI14" s="20"/>
+      <c r="AJ14" s="20"/>
+      <c r="AK14" s="20"/>
+      <c r="AL14" s="20"/>
+      <c r="AM14" s="20"/>
+      <c r="AN14" s="20"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="20"/>
+      <c r="AQ14" s="20"/>
+      <c r="AR14" s="20"/>
+      <c r="AS14" s="20"/>
+      <c r="AT14" s="20"/>
+      <c r="AU14" s="20"/>
+      <c r="AV14" s="20"/>
+      <c r="AW14" s="20"/>
+      <c r="AX14" s="20"/>
+      <c r="AY14" s="20"/>
+      <c r="AZ14" s="20"/>
+      <c r="BA14" s="20"/>
+      <c r="BB14" s="20"/>
+      <c r="BC14" s="20"/>
+      <c r="BD14" s="20"/>
+      <c r="BE14" s="20"/>
+      <c r="BF14" s="20"/>
+      <c r="BG14" s="20"/>
+      <c r="BH14" s="20"/>
+      <c r="BI14" s="20"/>
+      <c r="BJ14" s="20"/>
+      <c r="BK14" s="20"/>
+      <c r="BL14" s="20"/>
+      <c r="BM14" s="20"/>
+      <c r="BN14" s="20"/>
+      <c r="BO14" s="20"/>
+      <c r="BP14" s="20"/>
+      <c r="BQ14" s="20"/>
+      <c r="BR14" s="20"/>
+      <c r="BS14" s="20"/>
+      <c r="BT14" s="20"/>
+      <c r="BU14" s="20"/>
+      <c r="BV14" s="20"/>
+      <c r="BW14" s="20"/>
+      <c r="BX14" s="20"/>
+      <c r="BY14" s="20"/>
+      <c r="BZ14" s="20"/>
+      <c r="CA14" s="20"/>
+      <c r="CB14" s="20"/>
+      <c r="CC14" s="20"/>
+      <c r="CD14" s="20"/>
+      <c r="CE14" s="20"/>
+      <c r="CF14" s="20"/>
+      <c r="CG14" s="20"/>
+      <c r="CH14" s="20"/>
+      <c r="CI14" s="20"/>
+      <c r="CJ14" s="20"/>
+      <c r="CK14" s="20"/>
+      <c r="CL14" s="20"/>
+      <c r="CM14" s="20"/>
+      <c r="CN14" s="20"/>
+      <c r="CO14" s="20"/>
+      <c r="CP14" s="20"/>
+      <c r="CQ14" s="20"/>
+      <c r="CR14" s="20"/>
+      <c r="CS14" s="20"/>
+      <c r="CT14" s="20"/>
+      <c r="CU14" s="20"/>
+      <c r="CV14" s="20"/>
+      <c r="CW14" s="20"/>
+      <c r="CX14" s="20"/>
+      <c r="CY14" s="20"/>
+      <c r="CZ14" s="20"/>
+      <c r="DA14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -3033,108 +3064,108 @@
         <v/>
       </c>
       <c r="C15" s="16"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
-      <c r="AI15" s="21"/>
-      <c r="AJ15" s="21"/>
-      <c r="AK15" s="21"/>
-      <c r="AL15" s="21"/>
-      <c r="AM15" s="21"/>
-      <c r="AN15" s="21"/>
-      <c r="AO15" s="21"/>
-      <c r="AP15" s="21"/>
-      <c r="AQ15" s="21"/>
-      <c r="AR15" s="21"/>
-      <c r="AS15" s="21"/>
-      <c r="AT15" s="21"/>
-      <c r="AU15" s="21"/>
-      <c r="AV15" s="21"/>
-      <c r="AW15" s="21"/>
-      <c r="AX15" s="21"/>
-      <c r="AY15" s="21"/>
-      <c r="AZ15" s="21"/>
-      <c r="BA15" s="21"/>
-      <c r="BB15" s="21"/>
-      <c r="BC15" s="21"/>
-      <c r="BD15" s="21"/>
-      <c r="BE15" s="21"/>
-      <c r="BF15" s="21"/>
-      <c r="BG15" s="21"/>
-      <c r="BH15" s="21"/>
-      <c r="BI15" s="21"/>
-      <c r="BJ15" s="21"/>
-      <c r="BK15" s="21"/>
-      <c r="BL15" s="21"/>
-      <c r="BM15" s="21"/>
-      <c r="BN15" s="21"/>
-      <c r="BO15" s="21"/>
-      <c r="BP15" s="21"/>
-      <c r="BQ15" s="21"/>
-      <c r="BR15" s="21"/>
-      <c r="BS15" s="21"/>
-      <c r="BT15" s="21"/>
-      <c r="BU15" s="21"/>
-      <c r="BV15" s="21"/>
-      <c r="BW15" s="21"/>
-      <c r="BX15" s="21"/>
-      <c r="BY15" s="21"/>
-      <c r="BZ15" s="21"/>
-      <c r="CA15" s="21"/>
-      <c r="CB15" s="21"/>
-      <c r="CC15" s="21"/>
-      <c r="CD15" s="21"/>
-      <c r="CE15" s="21"/>
-      <c r="CF15" s="21"/>
-      <c r="CG15" s="21"/>
-      <c r="CH15" s="21"/>
-      <c r="CI15" s="21"/>
-      <c r="CJ15" s="21"/>
-      <c r="CK15" s="21"/>
-      <c r="CL15" s="21"/>
-      <c r="CM15" s="21"/>
-      <c r="CN15" s="21"/>
-      <c r="CO15" s="21"/>
-      <c r="CP15" s="21"/>
-      <c r="CQ15" s="21"/>
-      <c r="CR15" s="21"/>
-      <c r="CS15" s="21"/>
-      <c r="CT15" s="21"/>
-      <c r="CU15" s="21"/>
-      <c r="CV15" s="21"/>
-      <c r="CW15" s="21"/>
-      <c r="CX15" s="21"/>
-      <c r="CY15" s="21"/>
-      <c r="CZ15" s="21"/>
-      <c r="DA15" s="21"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="20"/>
+      <c r="AJ15" s="20"/>
+      <c r="AK15" s="20"/>
+      <c r="AL15" s="20"/>
+      <c r="AM15" s="20"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="20"/>
+      <c r="AQ15" s="20"/>
+      <c r="AR15" s="20"/>
+      <c r="AS15" s="20"/>
+      <c r="AT15" s="20"/>
+      <c r="AU15" s="20"/>
+      <c r="AV15" s="20"/>
+      <c r="AW15" s="20"/>
+      <c r="AX15" s="20"/>
+      <c r="AY15" s="20"/>
+      <c r="AZ15" s="20"/>
+      <c r="BA15" s="20"/>
+      <c r="BB15" s="20"/>
+      <c r="BC15" s="20"/>
+      <c r="BD15" s="20"/>
+      <c r="BE15" s="20"/>
+      <c r="BF15" s="20"/>
+      <c r="BG15" s="20"/>
+      <c r="BH15" s="20"/>
+      <c r="BI15" s="20"/>
+      <c r="BJ15" s="20"/>
+      <c r="BK15" s="20"/>
+      <c r="BL15" s="20"/>
+      <c r="BM15" s="20"/>
+      <c r="BN15" s="20"/>
+      <c r="BO15" s="20"/>
+      <c r="BP15" s="20"/>
+      <c r="BQ15" s="20"/>
+      <c r="BR15" s="20"/>
+      <c r="BS15" s="20"/>
+      <c r="BT15" s="20"/>
+      <c r="BU15" s="20"/>
+      <c r="BV15" s="20"/>
+      <c r="BW15" s="20"/>
+      <c r="BX15" s="20"/>
+      <c r="BY15" s="20"/>
+      <c r="BZ15" s="20"/>
+      <c r="CA15" s="20"/>
+      <c r="CB15" s="20"/>
+      <c r="CC15" s="20"/>
+      <c r="CD15" s="20"/>
+      <c r="CE15" s="20"/>
+      <c r="CF15" s="20"/>
+      <c r="CG15" s="20"/>
+      <c r="CH15" s="20"/>
+      <c r="CI15" s="20"/>
+      <c r="CJ15" s="20"/>
+      <c r="CK15" s="20"/>
+      <c r="CL15" s="20"/>
+      <c r="CM15" s="20"/>
+      <c r="CN15" s="20"/>
+      <c r="CO15" s="20"/>
+      <c r="CP15" s="20"/>
+      <c r="CQ15" s="20"/>
+      <c r="CR15" s="20"/>
+      <c r="CS15" s="20"/>
+      <c r="CT15" s="20"/>
+      <c r="CU15" s="20"/>
+      <c r="CV15" s="20"/>
+      <c r="CW15" s="20"/>
+      <c r="CX15" s="20"/>
+      <c r="CY15" s="20"/>
+      <c r="CZ15" s="20"/>
+      <c r="DA15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -3145,108 +3176,108 @@
         <v/>
       </c>
       <c r="C16" s="16"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="21"/>
-      <c r="AF16" s="21"/>
-      <c r="AG16" s="21"/>
-      <c r="AH16" s="21"/>
-      <c r="AI16" s="21"/>
-      <c r="AJ16" s="21"/>
-      <c r="AK16" s="21"/>
-      <c r="AL16" s="21"/>
-      <c r="AM16" s="21"/>
-      <c r="AN16" s="21"/>
-      <c r="AO16" s="21"/>
-      <c r="AP16" s="21"/>
-      <c r="AQ16" s="21"/>
-      <c r="AR16" s="21"/>
-      <c r="AS16" s="21"/>
-      <c r="AT16" s="21"/>
-      <c r="AU16" s="21"/>
-      <c r="AV16" s="21"/>
-      <c r="AW16" s="21"/>
-      <c r="AX16" s="21"/>
-      <c r="AY16" s="21"/>
-      <c r="AZ16" s="21"/>
-      <c r="BA16" s="21"/>
-      <c r="BB16" s="21"/>
-      <c r="BC16" s="21"/>
-      <c r="BD16" s="21"/>
-      <c r="BE16" s="21"/>
-      <c r="BF16" s="21"/>
-      <c r="BG16" s="21"/>
-      <c r="BH16" s="21"/>
-      <c r="BI16" s="21"/>
-      <c r="BJ16" s="21"/>
-      <c r="BK16" s="21"/>
-      <c r="BL16" s="21"/>
-      <c r="BM16" s="21"/>
-      <c r="BN16" s="21"/>
-      <c r="BO16" s="21"/>
-      <c r="BP16" s="21"/>
-      <c r="BQ16" s="21"/>
-      <c r="BR16" s="21"/>
-      <c r="BS16" s="21"/>
-      <c r="BT16" s="21"/>
-      <c r="BU16" s="21"/>
-      <c r="BV16" s="21"/>
-      <c r="BW16" s="21"/>
-      <c r="BX16" s="21"/>
-      <c r="BY16" s="21"/>
-      <c r="BZ16" s="21"/>
-      <c r="CA16" s="21"/>
-      <c r="CB16" s="21"/>
-      <c r="CC16" s="21"/>
-      <c r="CD16" s="21"/>
-      <c r="CE16" s="21"/>
-      <c r="CF16" s="21"/>
-      <c r="CG16" s="21"/>
-      <c r="CH16" s="21"/>
-      <c r="CI16" s="21"/>
-      <c r="CJ16" s="21"/>
-      <c r="CK16" s="21"/>
-      <c r="CL16" s="21"/>
-      <c r="CM16" s="21"/>
-      <c r="CN16" s="21"/>
-      <c r="CO16" s="21"/>
-      <c r="CP16" s="21"/>
-      <c r="CQ16" s="21"/>
-      <c r="CR16" s="21"/>
-      <c r="CS16" s="21"/>
-      <c r="CT16" s="21"/>
-      <c r="CU16" s="21"/>
-      <c r="CV16" s="21"/>
-      <c r="CW16" s="21"/>
-      <c r="CX16" s="21"/>
-      <c r="CY16" s="21"/>
-      <c r="CZ16" s="21"/>
-      <c r="DA16" s="21"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="20"/>
+      <c r="AH16" s="20"/>
+      <c r="AI16" s="20"/>
+      <c r="AJ16" s="20"/>
+      <c r="AK16" s="20"/>
+      <c r="AL16" s="20"/>
+      <c r="AM16" s="20"/>
+      <c r="AN16" s="20"/>
+      <c r="AO16" s="20"/>
+      <c r="AP16" s="20"/>
+      <c r="AQ16" s="20"/>
+      <c r="AR16" s="20"/>
+      <c r="AS16" s="20"/>
+      <c r="AT16" s="20"/>
+      <c r="AU16" s="20"/>
+      <c r="AV16" s="20"/>
+      <c r="AW16" s="20"/>
+      <c r="AX16" s="20"/>
+      <c r="AY16" s="20"/>
+      <c r="AZ16" s="20"/>
+      <c r="BA16" s="20"/>
+      <c r="BB16" s="20"/>
+      <c r="BC16" s="20"/>
+      <c r="BD16" s="20"/>
+      <c r="BE16" s="20"/>
+      <c r="BF16" s="20"/>
+      <c r="BG16" s="20"/>
+      <c r="BH16" s="20"/>
+      <c r="BI16" s="20"/>
+      <c r="BJ16" s="20"/>
+      <c r="BK16" s="20"/>
+      <c r="BL16" s="20"/>
+      <c r="BM16" s="20"/>
+      <c r="BN16" s="20"/>
+      <c r="BO16" s="20"/>
+      <c r="BP16" s="20"/>
+      <c r="BQ16" s="20"/>
+      <c r="BR16" s="20"/>
+      <c r="BS16" s="20"/>
+      <c r="BT16" s="20"/>
+      <c r="BU16" s="20"/>
+      <c r="BV16" s="20"/>
+      <c r="BW16" s="20"/>
+      <c r="BX16" s="20"/>
+      <c r="BY16" s="20"/>
+      <c r="BZ16" s="20"/>
+      <c r="CA16" s="20"/>
+      <c r="CB16" s="20"/>
+      <c r="CC16" s="20"/>
+      <c r="CD16" s="20"/>
+      <c r="CE16" s="20"/>
+      <c r="CF16" s="20"/>
+      <c r="CG16" s="20"/>
+      <c r="CH16" s="20"/>
+      <c r="CI16" s="20"/>
+      <c r="CJ16" s="20"/>
+      <c r="CK16" s="20"/>
+      <c r="CL16" s="20"/>
+      <c r="CM16" s="20"/>
+      <c r="CN16" s="20"/>
+      <c r="CO16" s="20"/>
+      <c r="CP16" s="20"/>
+      <c r="CQ16" s="20"/>
+      <c r="CR16" s="20"/>
+      <c r="CS16" s="20"/>
+      <c r="CT16" s="20"/>
+      <c r="CU16" s="20"/>
+      <c r="CV16" s="20"/>
+      <c r="CW16" s="20"/>
+      <c r="CX16" s="20"/>
+      <c r="CY16" s="20"/>
+      <c r="CZ16" s="20"/>
+      <c r="DA16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -3257,108 +3288,108 @@
         <v/>
       </c>
       <c r="C17" s="16"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="21"/>
-      <c r="AE17" s="21"/>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="21"/>
-      <c r="AH17" s="21"/>
-      <c r="AI17" s="21"/>
-      <c r="AJ17" s="21"/>
-      <c r="AK17" s="21"/>
-      <c r="AL17" s="21"/>
-      <c r="AM17" s="21"/>
-      <c r="AN17" s="21"/>
-      <c r="AO17" s="21"/>
-      <c r="AP17" s="21"/>
-      <c r="AQ17" s="21"/>
-      <c r="AR17" s="21"/>
-      <c r="AS17" s="21"/>
-      <c r="AT17" s="21"/>
-      <c r="AU17" s="21"/>
-      <c r="AV17" s="21"/>
-      <c r="AW17" s="21"/>
-      <c r="AX17" s="21"/>
-      <c r="AY17" s="21"/>
-      <c r="AZ17" s="21"/>
-      <c r="BA17" s="21"/>
-      <c r="BB17" s="21"/>
-      <c r="BC17" s="21"/>
-      <c r="BD17" s="21"/>
-      <c r="BE17" s="21"/>
-      <c r="BF17" s="21"/>
-      <c r="BG17" s="21"/>
-      <c r="BH17" s="21"/>
-      <c r="BI17" s="21"/>
-      <c r="BJ17" s="21"/>
-      <c r="BK17" s="21"/>
-      <c r="BL17" s="21"/>
-      <c r="BM17" s="21"/>
-      <c r="BN17" s="21"/>
-      <c r="BO17" s="21"/>
-      <c r="BP17" s="21"/>
-      <c r="BQ17" s="21"/>
-      <c r="BR17" s="21"/>
-      <c r="BS17" s="21"/>
-      <c r="BT17" s="21"/>
-      <c r="BU17" s="21"/>
-      <c r="BV17" s="21"/>
-      <c r="BW17" s="21"/>
-      <c r="BX17" s="21"/>
-      <c r="BY17" s="21"/>
-      <c r="BZ17" s="21"/>
-      <c r="CA17" s="21"/>
-      <c r="CB17" s="21"/>
-      <c r="CC17" s="21"/>
-      <c r="CD17" s="21"/>
-      <c r="CE17" s="21"/>
-      <c r="CF17" s="21"/>
-      <c r="CG17" s="21"/>
-      <c r="CH17" s="21"/>
-      <c r="CI17" s="21"/>
-      <c r="CJ17" s="21"/>
-      <c r="CK17" s="21"/>
-      <c r="CL17" s="21"/>
-      <c r="CM17" s="21"/>
-      <c r="CN17" s="21"/>
-      <c r="CO17" s="21"/>
-      <c r="CP17" s="21"/>
-      <c r="CQ17" s="21"/>
-      <c r="CR17" s="21"/>
-      <c r="CS17" s="21"/>
-      <c r="CT17" s="21"/>
-      <c r="CU17" s="21"/>
-      <c r="CV17" s="21"/>
-      <c r="CW17" s="21"/>
-      <c r="CX17" s="21"/>
-      <c r="CY17" s="21"/>
-      <c r="CZ17" s="21"/>
-      <c r="DA17" s="21"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="20"/>
+      <c r="AH17" s="20"/>
+      <c r="AI17" s="20"/>
+      <c r="AJ17" s="20"/>
+      <c r="AK17" s="20"/>
+      <c r="AL17" s="20"/>
+      <c r="AM17" s="20"/>
+      <c r="AN17" s="20"/>
+      <c r="AO17" s="20"/>
+      <c r="AP17" s="20"/>
+      <c r="AQ17" s="20"/>
+      <c r="AR17" s="20"/>
+      <c r="AS17" s="20"/>
+      <c r="AT17" s="20"/>
+      <c r="AU17" s="20"/>
+      <c r="AV17" s="20"/>
+      <c r="AW17" s="20"/>
+      <c r="AX17" s="20"/>
+      <c r="AY17" s="20"/>
+      <c r="AZ17" s="20"/>
+      <c r="BA17" s="20"/>
+      <c r="BB17" s="20"/>
+      <c r="BC17" s="20"/>
+      <c r="BD17" s="20"/>
+      <c r="BE17" s="20"/>
+      <c r="BF17" s="20"/>
+      <c r="BG17" s="20"/>
+      <c r="BH17" s="20"/>
+      <c r="BI17" s="20"/>
+      <c r="BJ17" s="20"/>
+      <c r="BK17" s="20"/>
+      <c r="BL17" s="20"/>
+      <c r="BM17" s="20"/>
+      <c r="BN17" s="20"/>
+      <c r="BO17" s="20"/>
+      <c r="BP17" s="20"/>
+      <c r="BQ17" s="20"/>
+      <c r="BR17" s="20"/>
+      <c r="BS17" s="20"/>
+      <c r="BT17" s="20"/>
+      <c r="BU17" s="20"/>
+      <c r="BV17" s="20"/>
+      <c r="BW17" s="20"/>
+      <c r="BX17" s="20"/>
+      <c r="BY17" s="20"/>
+      <c r="BZ17" s="20"/>
+      <c r="CA17" s="20"/>
+      <c r="CB17" s="20"/>
+      <c r="CC17" s="20"/>
+      <c r="CD17" s="20"/>
+      <c r="CE17" s="20"/>
+      <c r="CF17" s="20"/>
+      <c r="CG17" s="20"/>
+      <c r="CH17" s="20"/>
+      <c r="CI17" s="20"/>
+      <c r="CJ17" s="20"/>
+      <c r="CK17" s="20"/>
+      <c r="CL17" s="20"/>
+      <c r="CM17" s="20"/>
+      <c r="CN17" s="20"/>
+      <c r="CO17" s="20"/>
+      <c r="CP17" s="20"/>
+      <c r="CQ17" s="20"/>
+      <c r="CR17" s="20"/>
+      <c r="CS17" s="20"/>
+      <c r="CT17" s="20"/>
+      <c r="CU17" s="20"/>
+      <c r="CV17" s="20"/>
+      <c r="CW17" s="20"/>
+      <c r="CX17" s="20"/>
+      <c r="CY17" s="20"/>
+      <c r="CZ17" s="20"/>
+      <c r="DA17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -3369,108 +3400,108 @@
         <v/>
       </c>
       <c r="C18" s="16"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="21"/>
-      <c r="AE18" s="21"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="21"/>
-      <c r="AI18" s="21"/>
-      <c r="AJ18" s="21"/>
-      <c r="AK18" s="21"/>
-      <c r="AL18" s="21"/>
-      <c r="AM18" s="21"/>
-      <c r="AN18" s="21"/>
-      <c r="AO18" s="21"/>
-      <c r="AP18" s="21"/>
-      <c r="AQ18" s="21"/>
-      <c r="AR18" s="21"/>
-      <c r="AS18" s="21"/>
-      <c r="AT18" s="21"/>
-      <c r="AU18" s="21"/>
-      <c r="AV18" s="21"/>
-      <c r="AW18" s="21"/>
-      <c r="AX18" s="21"/>
-      <c r="AY18" s="21"/>
-      <c r="AZ18" s="21"/>
-      <c r="BA18" s="21"/>
-      <c r="BB18" s="21"/>
-      <c r="BC18" s="21"/>
-      <c r="BD18" s="21"/>
-      <c r="BE18" s="21"/>
-      <c r="BF18" s="21"/>
-      <c r="BG18" s="21"/>
-      <c r="BH18" s="21"/>
-      <c r="BI18" s="21"/>
-      <c r="BJ18" s="21"/>
-      <c r="BK18" s="21"/>
-      <c r="BL18" s="21"/>
-      <c r="BM18" s="21"/>
-      <c r="BN18" s="21"/>
-      <c r="BO18" s="21"/>
-      <c r="BP18" s="21"/>
-      <c r="BQ18" s="21"/>
-      <c r="BR18" s="21"/>
-      <c r="BS18" s="21"/>
-      <c r="BT18" s="21"/>
-      <c r="BU18" s="21"/>
-      <c r="BV18" s="21"/>
-      <c r="BW18" s="21"/>
-      <c r="BX18" s="21"/>
-      <c r="BY18" s="21"/>
-      <c r="BZ18" s="21"/>
-      <c r="CA18" s="21"/>
-      <c r="CB18" s="21"/>
-      <c r="CC18" s="21"/>
-      <c r="CD18" s="21"/>
-      <c r="CE18" s="21"/>
-      <c r="CF18" s="21"/>
-      <c r="CG18" s="21"/>
-      <c r="CH18" s="21"/>
-      <c r="CI18" s="21"/>
-      <c r="CJ18" s="21"/>
-      <c r="CK18" s="21"/>
-      <c r="CL18" s="21"/>
-      <c r="CM18" s="21"/>
-      <c r="CN18" s="21"/>
-      <c r="CO18" s="21"/>
-      <c r="CP18" s="21"/>
-      <c r="CQ18" s="21"/>
-      <c r="CR18" s="21"/>
-      <c r="CS18" s="21"/>
-      <c r="CT18" s="21"/>
-      <c r="CU18" s="21"/>
-      <c r="CV18" s="21"/>
-      <c r="CW18" s="21"/>
-      <c r="CX18" s="21"/>
-      <c r="CY18" s="21"/>
-      <c r="CZ18" s="21"/>
-      <c r="DA18" s="21"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="20"/>
+      <c r="AI18" s="20"/>
+      <c r="AJ18" s="20"/>
+      <c r="AK18" s="20"/>
+      <c r="AL18" s="20"/>
+      <c r="AM18" s="20"/>
+      <c r="AN18" s="20"/>
+      <c r="AO18" s="20"/>
+      <c r="AP18" s="20"/>
+      <c r="AQ18" s="20"/>
+      <c r="AR18" s="20"/>
+      <c r="AS18" s="20"/>
+      <c r="AT18" s="20"/>
+      <c r="AU18" s="20"/>
+      <c r="AV18" s="20"/>
+      <c r="AW18" s="20"/>
+      <c r="AX18" s="20"/>
+      <c r="AY18" s="20"/>
+      <c r="AZ18" s="20"/>
+      <c r="BA18" s="20"/>
+      <c r="BB18" s="20"/>
+      <c r="BC18" s="20"/>
+      <c r="BD18" s="20"/>
+      <c r="BE18" s="20"/>
+      <c r="BF18" s="20"/>
+      <c r="BG18" s="20"/>
+      <c r="BH18" s="20"/>
+      <c r="BI18" s="20"/>
+      <c r="BJ18" s="20"/>
+      <c r="BK18" s="20"/>
+      <c r="BL18" s="20"/>
+      <c r="BM18" s="20"/>
+      <c r="BN18" s="20"/>
+      <c r="BO18" s="20"/>
+      <c r="BP18" s="20"/>
+      <c r="BQ18" s="20"/>
+      <c r="BR18" s="20"/>
+      <c r="BS18" s="20"/>
+      <c r="BT18" s="20"/>
+      <c r="BU18" s="20"/>
+      <c r="BV18" s="20"/>
+      <c r="BW18" s="20"/>
+      <c r="BX18" s="20"/>
+      <c r="BY18" s="20"/>
+      <c r="BZ18" s="20"/>
+      <c r="CA18" s="20"/>
+      <c r="CB18" s="20"/>
+      <c r="CC18" s="20"/>
+      <c r="CD18" s="20"/>
+      <c r="CE18" s="20"/>
+      <c r="CF18" s="20"/>
+      <c r="CG18" s="20"/>
+      <c r="CH18" s="20"/>
+      <c r="CI18" s="20"/>
+      <c r="CJ18" s="20"/>
+      <c r="CK18" s="20"/>
+      <c r="CL18" s="20"/>
+      <c r="CM18" s="20"/>
+      <c r="CN18" s="20"/>
+      <c r="CO18" s="20"/>
+      <c r="CP18" s="20"/>
+      <c r="CQ18" s="20"/>
+      <c r="CR18" s="20"/>
+      <c r="CS18" s="20"/>
+      <c r="CT18" s="20"/>
+      <c r="CU18" s="20"/>
+      <c r="CV18" s="20"/>
+      <c r="CW18" s="20"/>
+      <c r="CX18" s="20"/>
+      <c r="CY18" s="20"/>
+      <c r="CZ18" s="20"/>
+      <c r="DA18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -3481,108 +3512,108 @@
         <v/>
       </c>
       <c r="C19" s="16"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
-      <c r="AI19" s="21"/>
-      <c r="AJ19" s="21"/>
-      <c r="AK19" s="21"/>
-      <c r="AL19" s="21"/>
-      <c r="AM19" s="21"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="21"/>
-      <c r="AP19" s="21"/>
-      <c r="AQ19" s="21"/>
-      <c r="AR19" s="21"/>
-      <c r="AS19" s="21"/>
-      <c r="AT19" s="21"/>
-      <c r="AU19" s="21"/>
-      <c r="AV19" s="21"/>
-      <c r="AW19" s="21"/>
-      <c r="AX19" s="21"/>
-      <c r="AY19" s="21"/>
-      <c r="AZ19" s="21"/>
-      <c r="BA19" s="21"/>
-      <c r="BB19" s="21"/>
-      <c r="BC19" s="21"/>
-      <c r="BD19" s="21"/>
-      <c r="BE19" s="21"/>
-      <c r="BF19" s="21"/>
-      <c r="BG19" s="21"/>
-      <c r="BH19" s="21"/>
-      <c r="BI19" s="21"/>
-      <c r="BJ19" s="21"/>
-      <c r="BK19" s="21"/>
-      <c r="BL19" s="21"/>
-      <c r="BM19" s="21"/>
-      <c r="BN19" s="21"/>
-      <c r="BO19" s="21"/>
-      <c r="BP19" s="21"/>
-      <c r="BQ19" s="21"/>
-      <c r="BR19" s="21"/>
-      <c r="BS19" s="21"/>
-      <c r="BT19" s="21"/>
-      <c r="BU19" s="21"/>
-      <c r="BV19" s="21"/>
-      <c r="BW19" s="21"/>
-      <c r="BX19" s="21"/>
-      <c r="BY19" s="21"/>
-      <c r="BZ19" s="21"/>
-      <c r="CA19" s="21"/>
-      <c r="CB19" s="21"/>
-      <c r="CC19" s="21"/>
-      <c r="CD19" s="21"/>
-      <c r="CE19" s="21"/>
-      <c r="CF19" s="21"/>
-      <c r="CG19" s="21"/>
-      <c r="CH19" s="21"/>
-      <c r="CI19" s="21"/>
-      <c r="CJ19" s="21"/>
-      <c r="CK19" s="21"/>
-      <c r="CL19" s="21"/>
-      <c r="CM19" s="21"/>
-      <c r="CN19" s="21"/>
-      <c r="CO19" s="21"/>
-      <c r="CP19" s="21"/>
-      <c r="CQ19" s="21"/>
-      <c r="CR19" s="21"/>
-      <c r="CS19" s="21"/>
-      <c r="CT19" s="21"/>
-      <c r="CU19" s="21"/>
-      <c r="CV19" s="21"/>
-      <c r="CW19" s="21"/>
-      <c r="CX19" s="21"/>
-      <c r="CY19" s="21"/>
-      <c r="CZ19" s="21"/>
-      <c r="DA19" s="21"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="20"/>
+      <c r="AE19" s="20"/>
+      <c r="AF19" s="20"/>
+      <c r="AG19" s="20"/>
+      <c r="AH19" s="20"/>
+      <c r="AI19" s="20"/>
+      <c r="AJ19" s="20"/>
+      <c r="AK19" s="20"/>
+      <c r="AL19" s="20"/>
+      <c r="AM19" s="20"/>
+      <c r="AN19" s="20"/>
+      <c r="AO19" s="20"/>
+      <c r="AP19" s="20"/>
+      <c r="AQ19" s="20"/>
+      <c r="AR19" s="20"/>
+      <c r="AS19" s="20"/>
+      <c r="AT19" s="20"/>
+      <c r="AU19" s="20"/>
+      <c r="AV19" s="20"/>
+      <c r="AW19" s="20"/>
+      <c r="AX19" s="20"/>
+      <c r="AY19" s="20"/>
+      <c r="AZ19" s="20"/>
+      <c r="BA19" s="20"/>
+      <c r="BB19" s="20"/>
+      <c r="BC19" s="20"/>
+      <c r="BD19" s="20"/>
+      <c r="BE19" s="20"/>
+      <c r="BF19" s="20"/>
+      <c r="BG19" s="20"/>
+      <c r="BH19" s="20"/>
+      <c r="BI19" s="20"/>
+      <c r="BJ19" s="20"/>
+      <c r="BK19" s="20"/>
+      <c r="BL19" s="20"/>
+      <c r="BM19" s="20"/>
+      <c r="BN19" s="20"/>
+      <c r="BO19" s="20"/>
+      <c r="BP19" s="20"/>
+      <c r="BQ19" s="20"/>
+      <c r="BR19" s="20"/>
+      <c r="BS19" s="20"/>
+      <c r="BT19" s="20"/>
+      <c r="BU19" s="20"/>
+      <c r="BV19" s="20"/>
+      <c r="BW19" s="20"/>
+      <c r="BX19" s="20"/>
+      <c r="BY19" s="20"/>
+      <c r="BZ19" s="20"/>
+      <c r="CA19" s="20"/>
+      <c r="CB19" s="20"/>
+      <c r="CC19" s="20"/>
+      <c r="CD19" s="20"/>
+      <c r="CE19" s="20"/>
+      <c r="CF19" s="20"/>
+      <c r="CG19" s="20"/>
+      <c r="CH19" s="20"/>
+      <c r="CI19" s="20"/>
+      <c r="CJ19" s="20"/>
+      <c r="CK19" s="20"/>
+      <c r="CL19" s="20"/>
+      <c r="CM19" s="20"/>
+      <c r="CN19" s="20"/>
+      <c r="CO19" s="20"/>
+      <c r="CP19" s="20"/>
+      <c r="CQ19" s="20"/>
+      <c r="CR19" s="20"/>
+      <c r="CS19" s="20"/>
+      <c r="CT19" s="20"/>
+      <c r="CU19" s="20"/>
+      <c r="CV19" s="20"/>
+      <c r="CW19" s="20"/>
+      <c r="CX19" s="20"/>
+      <c r="CY19" s="20"/>
+      <c r="CZ19" s="20"/>
+      <c r="DA19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -3593,108 +3624,108 @@
         <v/>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-      <c r="AB20" s="21"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="21"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="21"/>
-      <c r="AH20" s="21"/>
-      <c r="AI20" s="21"/>
-      <c r="AJ20" s="21"/>
-      <c r="AK20" s="21"/>
-      <c r="AL20" s="21"/>
-      <c r="AM20" s="21"/>
-      <c r="AN20" s="21"/>
-      <c r="AO20" s="21"/>
-      <c r="AP20" s="21"/>
-      <c r="AQ20" s="21"/>
-      <c r="AR20" s="21"/>
-      <c r="AS20" s="21"/>
-      <c r="AT20" s="21"/>
-      <c r="AU20" s="21"/>
-      <c r="AV20" s="21"/>
-      <c r="AW20" s="21"/>
-      <c r="AX20" s="21"/>
-      <c r="AY20" s="21"/>
-      <c r="AZ20" s="21"/>
-      <c r="BA20" s="21"/>
-      <c r="BB20" s="21"/>
-      <c r="BC20" s="21"/>
-      <c r="BD20" s="21"/>
-      <c r="BE20" s="21"/>
-      <c r="BF20" s="21"/>
-      <c r="BG20" s="21"/>
-      <c r="BH20" s="21"/>
-      <c r="BI20" s="21"/>
-      <c r="BJ20" s="21"/>
-      <c r="BK20" s="21"/>
-      <c r="BL20" s="21"/>
-      <c r="BM20" s="21"/>
-      <c r="BN20" s="21"/>
-      <c r="BO20" s="21"/>
-      <c r="BP20" s="21"/>
-      <c r="BQ20" s="21"/>
-      <c r="BR20" s="21"/>
-      <c r="BS20" s="21"/>
-      <c r="BT20" s="21"/>
-      <c r="BU20" s="21"/>
-      <c r="BV20" s="21"/>
-      <c r="BW20" s="21"/>
-      <c r="BX20" s="21"/>
-      <c r="BY20" s="21"/>
-      <c r="BZ20" s="21"/>
-      <c r="CA20" s="21"/>
-      <c r="CB20" s="21"/>
-      <c r="CC20" s="21"/>
-      <c r="CD20" s="21"/>
-      <c r="CE20" s="21"/>
-      <c r="CF20" s="21"/>
-      <c r="CG20" s="21"/>
-      <c r="CH20" s="21"/>
-      <c r="CI20" s="21"/>
-      <c r="CJ20" s="21"/>
-      <c r="CK20" s="21"/>
-      <c r="CL20" s="21"/>
-      <c r="CM20" s="21"/>
-      <c r="CN20" s="21"/>
-      <c r="CO20" s="21"/>
-      <c r="CP20" s="21"/>
-      <c r="CQ20" s="21"/>
-      <c r="CR20" s="21"/>
-      <c r="CS20" s="21"/>
-      <c r="CT20" s="21"/>
-      <c r="CU20" s="21"/>
-      <c r="CV20" s="21"/>
-      <c r="CW20" s="21"/>
-      <c r="CX20" s="21"/>
-      <c r="CY20" s="21"/>
-      <c r="CZ20" s="21"/>
-      <c r="DA20" s="21"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
+      <c r="AG20" s="20"/>
+      <c r="AH20" s="20"/>
+      <c r="AI20" s="20"/>
+      <c r="AJ20" s="20"/>
+      <c r="AK20" s="20"/>
+      <c r="AL20" s="20"/>
+      <c r="AM20" s="20"/>
+      <c r="AN20" s="20"/>
+      <c r="AO20" s="20"/>
+      <c r="AP20" s="20"/>
+      <c r="AQ20" s="20"/>
+      <c r="AR20" s="20"/>
+      <c r="AS20" s="20"/>
+      <c r="AT20" s="20"/>
+      <c r="AU20" s="20"/>
+      <c r="AV20" s="20"/>
+      <c r="AW20" s="20"/>
+      <c r="AX20" s="20"/>
+      <c r="AY20" s="20"/>
+      <c r="AZ20" s="20"/>
+      <c r="BA20" s="20"/>
+      <c r="BB20" s="20"/>
+      <c r="BC20" s="20"/>
+      <c r="BD20" s="20"/>
+      <c r="BE20" s="20"/>
+      <c r="BF20" s="20"/>
+      <c r="BG20" s="20"/>
+      <c r="BH20" s="20"/>
+      <c r="BI20" s="20"/>
+      <c r="BJ20" s="20"/>
+      <c r="BK20" s="20"/>
+      <c r="BL20" s="20"/>
+      <c r="BM20" s="20"/>
+      <c r="BN20" s="20"/>
+      <c r="BO20" s="20"/>
+      <c r="BP20" s="20"/>
+      <c r="BQ20" s="20"/>
+      <c r="BR20" s="20"/>
+      <c r="BS20" s="20"/>
+      <c r="BT20" s="20"/>
+      <c r="BU20" s="20"/>
+      <c r="BV20" s="20"/>
+      <c r="BW20" s="20"/>
+      <c r="BX20" s="20"/>
+      <c r="BY20" s="20"/>
+      <c r="BZ20" s="20"/>
+      <c r="CA20" s="20"/>
+      <c r="CB20" s="20"/>
+      <c r="CC20" s="20"/>
+      <c r="CD20" s="20"/>
+      <c r="CE20" s="20"/>
+      <c r="CF20" s="20"/>
+      <c r="CG20" s="20"/>
+      <c r="CH20" s="20"/>
+      <c r="CI20" s="20"/>
+      <c r="CJ20" s="20"/>
+      <c r="CK20" s="20"/>
+      <c r="CL20" s="20"/>
+      <c r="CM20" s="20"/>
+      <c r="CN20" s="20"/>
+      <c r="CO20" s="20"/>
+      <c r="CP20" s="20"/>
+      <c r="CQ20" s="20"/>
+      <c r="CR20" s="20"/>
+      <c r="CS20" s="20"/>
+      <c r="CT20" s="20"/>
+      <c r="CU20" s="20"/>
+      <c r="CV20" s="20"/>
+      <c r="CW20" s="20"/>
+      <c r="CX20" s="20"/>
+      <c r="CY20" s="20"/>
+      <c r="CZ20" s="20"/>
+      <c r="DA20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -3705,108 +3736,108 @@
         <v/>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="21"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="21"/>
-      <c r="AJ21" s="21"/>
-      <c r="AK21" s="21"/>
-      <c r="AL21" s="21"/>
-      <c r="AM21" s="21"/>
-      <c r="AN21" s="21"/>
-      <c r="AO21" s="21"/>
-      <c r="AP21" s="21"/>
-      <c r="AQ21" s="21"/>
-      <c r="AR21" s="21"/>
-      <c r="AS21" s="21"/>
-      <c r="AT21" s="21"/>
-      <c r="AU21" s="21"/>
-      <c r="AV21" s="21"/>
-      <c r="AW21" s="21"/>
-      <c r="AX21" s="21"/>
-      <c r="AY21" s="21"/>
-      <c r="AZ21" s="21"/>
-      <c r="BA21" s="21"/>
-      <c r="BB21" s="21"/>
-      <c r="BC21" s="21"/>
-      <c r="BD21" s="21"/>
-      <c r="BE21" s="21"/>
-      <c r="BF21" s="21"/>
-      <c r="BG21" s="21"/>
-      <c r="BH21" s="21"/>
-      <c r="BI21" s="21"/>
-      <c r="BJ21" s="21"/>
-      <c r="BK21" s="21"/>
-      <c r="BL21" s="21"/>
-      <c r="BM21" s="21"/>
-      <c r="BN21" s="21"/>
-      <c r="BO21" s="21"/>
-      <c r="BP21" s="21"/>
-      <c r="BQ21" s="21"/>
-      <c r="BR21" s="21"/>
-      <c r="BS21" s="21"/>
-      <c r="BT21" s="21"/>
-      <c r="BU21" s="21"/>
-      <c r="BV21" s="21"/>
-      <c r="BW21" s="21"/>
-      <c r="BX21" s="21"/>
-      <c r="BY21" s="21"/>
-      <c r="BZ21" s="21"/>
-      <c r="CA21" s="21"/>
-      <c r="CB21" s="21"/>
-      <c r="CC21" s="21"/>
-      <c r="CD21" s="21"/>
-      <c r="CE21" s="21"/>
-      <c r="CF21" s="21"/>
-      <c r="CG21" s="21"/>
-      <c r="CH21" s="21"/>
-      <c r="CI21" s="21"/>
-      <c r="CJ21" s="21"/>
-      <c r="CK21" s="21"/>
-      <c r="CL21" s="21"/>
-      <c r="CM21" s="21"/>
-      <c r="CN21" s="21"/>
-      <c r="CO21" s="21"/>
-      <c r="CP21" s="21"/>
-      <c r="CQ21" s="21"/>
-      <c r="CR21" s="21"/>
-      <c r="CS21" s="21"/>
-      <c r="CT21" s="21"/>
-      <c r="CU21" s="21"/>
-      <c r="CV21" s="21"/>
-      <c r="CW21" s="21"/>
-      <c r="CX21" s="21"/>
-      <c r="CY21" s="21"/>
-      <c r="CZ21" s="21"/>
-      <c r="DA21" s="21"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
+      <c r="AH21" s="20"/>
+      <c r="AI21" s="20"/>
+      <c r="AJ21" s="20"/>
+      <c r="AK21" s="20"/>
+      <c r="AL21" s="20"/>
+      <c r="AM21" s="20"/>
+      <c r="AN21" s="20"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="20"/>
+      <c r="AQ21" s="20"/>
+      <c r="AR21" s="20"/>
+      <c r="AS21" s="20"/>
+      <c r="AT21" s="20"/>
+      <c r="AU21" s="20"/>
+      <c r="AV21" s="20"/>
+      <c r="AW21" s="20"/>
+      <c r="AX21" s="20"/>
+      <c r="AY21" s="20"/>
+      <c r="AZ21" s="20"/>
+      <c r="BA21" s="20"/>
+      <c r="BB21" s="20"/>
+      <c r="BC21" s="20"/>
+      <c r="BD21" s="20"/>
+      <c r="BE21" s="20"/>
+      <c r="BF21" s="20"/>
+      <c r="BG21" s="20"/>
+      <c r="BH21" s="20"/>
+      <c r="BI21" s="20"/>
+      <c r="BJ21" s="20"/>
+      <c r="BK21" s="20"/>
+      <c r="BL21" s="20"/>
+      <c r="BM21" s="20"/>
+      <c r="BN21" s="20"/>
+      <c r="BO21" s="20"/>
+      <c r="BP21" s="20"/>
+      <c r="BQ21" s="20"/>
+      <c r="BR21" s="20"/>
+      <c r="BS21" s="20"/>
+      <c r="BT21" s="20"/>
+      <c r="BU21" s="20"/>
+      <c r="BV21" s="20"/>
+      <c r="BW21" s="20"/>
+      <c r="BX21" s="20"/>
+      <c r="BY21" s="20"/>
+      <c r="BZ21" s="20"/>
+      <c r="CA21" s="20"/>
+      <c r="CB21" s="20"/>
+      <c r="CC21" s="20"/>
+      <c r="CD21" s="20"/>
+      <c r="CE21" s="20"/>
+      <c r="CF21" s="20"/>
+      <c r="CG21" s="20"/>
+      <c r="CH21" s="20"/>
+      <c r="CI21" s="20"/>
+      <c r="CJ21" s="20"/>
+      <c r="CK21" s="20"/>
+      <c r="CL21" s="20"/>
+      <c r="CM21" s="20"/>
+      <c r="CN21" s="20"/>
+      <c r="CO21" s="20"/>
+      <c r="CP21" s="20"/>
+      <c r="CQ21" s="20"/>
+      <c r="CR21" s="20"/>
+      <c r="CS21" s="20"/>
+      <c r="CT21" s="20"/>
+      <c r="CU21" s="20"/>
+      <c r="CV21" s="20"/>
+      <c r="CW21" s="20"/>
+      <c r="CX21" s="20"/>
+      <c r="CY21" s="20"/>
+      <c r="CZ21" s="20"/>
+      <c r="DA21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -3817,108 +3848,108 @@
         <v/>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="21"/>
-      <c r="AD22" s="21"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="21"/>
-      <c r="AG22" s="21"/>
-      <c r="AH22" s="21"/>
-      <c r="AI22" s="21"/>
-      <c r="AJ22" s="21"/>
-      <c r="AK22" s="21"/>
-      <c r="AL22" s="21"/>
-      <c r="AM22" s="21"/>
-      <c r="AN22" s="21"/>
-      <c r="AO22" s="21"/>
-      <c r="AP22" s="21"/>
-      <c r="AQ22" s="21"/>
-      <c r="AR22" s="21"/>
-      <c r="AS22" s="21"/>
-      <c r="AT22" s="21"/>
-      <c r="AU22" s="21"/>
-      <c r="AV22" s="21"/>
-      <c r="AW22" s="21"/>
-      <c r="AX22" s="21"/>
-      <c r="AY22" s="21"/>
-      <c r="AZ22" s="21"/>
-      <c r="BA22" s="21"/>
-      <c r="BB22" s="21"/>
-      <c r="BC22" s="21"/>
-      <c r="BD22" s="21"/>
-      <c r="BE22" s="21"/>
-      <c r="BF22" s="21"/>
-      <c r="BG22" s="21"/>
-      <c r="BH22" s="21"/>
-      <c r="BI22" s="21"/>
-      <c r="BJ22" s="21"/>
-      <c r="BK22" s="21"/>
-      <c r="BL22" s="21"/>
-      <c r="BM22" s="21"/>
-      <c r="BN22" s="21"/>
-      <c r="BO22" s="21"/>
-      <c r="BP22" s="21"/>
-      <c r="BQ22" s="21"/>
-      <c r="BR22" s="21"/>
-      <c r="BS22" s="21"/>
-      <c r="BT22" s="21"/>
-      <c r="BU22" s="21"/>
-      <c r="BV22" s="21"/>
-      <c r="BW22" s="21"/>
-      <c r="BX22" s="21"/>
-      <c r="BY22" s="21"/>
-      <c r="BZ22" s="21"/>
-      <c r="CA22" s="21"/>
-      <c r="CB22" s="21"/>
-      <c r="CC22" s="21"/>
-      <c r="CD22" s="21"/>
-      <c r="CE22" s="21"/>
-      <c r="CF22" s="21"/>
-      <c r="CG22" s="21"/>
-      <c r="CH22" s="21"/>
-      <c r="CI22" s="21"/>
-      <c r="CJ22" s="21"/>
-      <c r="CK22" s="21"/>
-      <c r="CL22" s="21"/>
-      <c r="CM22" s="21"/>
-      <c r="CN22" s="21"/>
-      <c r="CO22" s="21"/>
-      <c r="CP22" s="21"/>
-      <c r="CQ22" s="21"/>
-      <c r="CR22" s="21"/>
-      <c r="CS22" s="21"/>
-      <c r="CT22" s="21"/>
-      <c r="CU22" s="21"/>
-      <c r="CV22" s="21"/>
-      <c r="CW22" s="21"/>
-      <c r="CX22" s="21"/>
-      <c r="CY22" s="21"/>
-      <c r="CZ22" s="21"/>
-      <c r="DA22" s="21"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="20"/>
+      <c r="AH22" s="20"/>
+      <c r="AI22" s="20"/>
+      <c r="AJ22" s="20"/>
+      <c r="AK22" s="20"/>
+      <c r="AL22" s="20"/>
+      <c r="AM22" s="20"/>
+      <c r="AN22" s="20"/>
+      <c r="AO22" s="20"/>
+      <c r="AP22" s="20"/>
+      <c r="AQ22" s="20"/>
+      <c r="AR22" s="20"/>
+      <c r="AS22" s="20"/>
+      <c r="AT22" s="20"/>
+      <c r="AU22" s="20"/>
+      <c r="AV22" s="20"/>
+      <c r="AW22" s="20"/>
+      <c r="AX22" s="20"/>
+      <c r="AY22" s="20"/>
+      <c r="AZ22" s="20"/>
+      <c r="BA22" s="20"/>
+      <c r="BB22" s="20"/>
+      <c r="BC22" s="20"/>
+      <c r="BD22" s="20"/>
+      <c r="BE22" s="20"/>
+      <c r="BF22" s="20"/>
+      <c r="BG22" s="20"/>
+      <c r="BH22" s="20"/>
+      <c r="BI22" s="20"/>
+      <c r="BJ22" s="20"/>
+      <c r="BK22" s="20"/>
+      <c r="BL22" s="20"/>
+      <c r="BM22" s="20"/>
+      <c r="BN22" s="20"/>
+      <c r="BO22" s="20"/>
+      <c r="BP22" s="20"/>
+      <c r="BQ22" s="20"/>
+      <c r="BR22" s="20"/>
+      <c r="BS22" s="20"/>
+      <c r="BT22" s="20"/>
+      <c r="BU22" s="20"/>
+      <c r="BV22" s="20"/>
+      <c r="BW22" s="20"/>
+      <c r="BX22" s="20"/>
+      <c r="BY22" s="20"/>
+      <c r="BZ22" s="20"/>
+      <c r="CA22" s="20"/>
+      <c r="CB22" s="20"/>
+      <c r="CC22" s="20"/>
+      <c r="CD22" s="20"/>
+      <c r="CE22" s="20"/>
+      <c r="CF22" s="20"/>
+      <c r="CG22" s="20"/>
+      <c r="CH22" s="20"/>
+      <c r="CI22" s="20"/>
+      <c r="CJ22" s="20"/>
+      <c r="CK22" s="20"/>
+      <c r="CL22" s="20"/>
+      <c r="CM22" s="20"/>
+      <c r="CN22" s="20"/>
+      <c r="CO22" s="20"/>
+      <c r="CP22" s="20"/>
+      <c r="CQ22" s="20"/>
+      <c r="CR22" s="20"/>
+      <c r="CS22" s="20"/>
+      <c r="CT22" s="20"/>
+      <c r="CU22" s="20"/>
+      <c r="CV22" s="20"/>
+      <c r="CW22" s="20"/>
+      <c r="CX22" s="20"/>
+      <c r="CY22" s="20"/>
+      <c r="CZ22" s="20"/>
+      <c r="DA22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -3929,108 +3960,108 @@
         <v/>
       </c>
       <c r="C23" s="16"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21"/>
-      <c r="X23" s="21"/>
-      <c r="Y23" s="21"/>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="21"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="21"/>
-      <c r="AE23" s="21"/>
-      <c r="AF23" s="21"/>
-      <c r="AG23" s="21"/>
-      <c r="AH23" s="21"/>
-      <c r="AI23" s="21"/>
-      <c r="AJ23" s="21"/>
-      <c r="AK23" s="21"/>
-      <c r="AL23" s="21"/>
-      <c r="AM23" s="21"/>
-      <c r="AN23" s="21"/>
-      <c r="AO23" s="21"/>
-      <c r="AP23" s="21"/>
-      <c r="AQ23" s="21"/>
-      <c r="AR23" s="21"/>
-      <c r="AS23" s="21"/>
-      <c r="AT23" s="21"/>
-      <c r="AU23" s="21"/>
-      <c r="AV23" s="21"/>
-      <c r="AW23" s="21"/>
-      <c r="AX23" s="21"/>
-      <c r="AY23" s="21"/>
-      <c r="AZ23" s="21"/>
-      <c r="BA23" s="21"/>
-      <c r="BB23" s="21"/>
-      <c r="BC23" s="21"/>
-      <c r="BD23" s="21"/>
-      <c r="BE23" s="21"/>
-      <c r="BF23" s="21"/>
-      <c r="BG23" s="21"/>
-      <c r="BH23" s="21"/>
-      <c r="BI23" s="21"/>
-      <c r="BJ23" s="21"/>
-      <c r="BK23" s="21"/>
-      <c r="BL23" s="21"/>
-      <c r="BM23" s="21"/>
-      <c r="BN23" s="21"/>
-      <c r="BO23" s="21"/>
-      <c r="BP23" s="21"/>
-      <c r="BQ23" s="21"/>
-      <c r="BR23" s="21"/>
-      <c r="BS23" s="21"/>
-      <c r="BT23" s="21"/>
-      <c r="BU23" s="21"/>
-      <c r="BV23" s="21"/>
-      <c r="BW23" s="21"/>
-      <c r="BX23" s="21"/>
-      <c r="BY23" s="21"/>
-      <c r="BZ23" s="21"/>
-      <c r="CA23" s="21"/>
-      <c r="CB23" s="21"/>
-      <c r="CC23" s="21"/>
-      <c r="CD23" s="21"/>
-      <c r="CE23" s="21"/>
-      <c r="CF23" s="21"/>
-      <c r="CG23" s="21"/>
-      <c r="CH23" s="21"/>
-      <c r="CI23" s="21"/>
-      <c r="CJ23" s="21"/>
-      <c r="CK23" s="21"/>
-      <c r="CL23" s="21"/>
-      <c r="CM23" s="21"/>
-      <c r="CN23" s="21"/>
-      <c r="CO23" s="21"/>
-      <c r="CP23" s="21"/>
-      <c r="CQ23" s="21"/>
-      <c r="CR23" s="21"/>
-      <c r="CS23" s="21"/>
-      <c r="CT23" s="21"/>
-      <c r="CU23" s="21"/>
-      <c r="CV23" s="21"/>
-      <c r="CW23" s="21"/>
-      <c r="CX23" s="21"/>
-      <c r="CY23" s="21"/>
-      <c r="CZ23" s="21"/>
-      <c r="DA23" s="21"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="20"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="20"/>
+      <c r="AG23" s="20"/>
+      <c r="AH23" s="20"/>
+      <c r="AI23" s="20"/>
+      <c r="AJ23" s="20"/>
+      <c r="AK23" s="20"/>
+      <c r="AL23" s="20"/>
+      <c r="AM23" s="20"/>
+      <c r="AN23" s="20"/>
+      <c r="AO23" s="20"/>
+      <c r="AP23" s="20"/>
+      <c r="AQ23" s="20"/>
+      <c r="AR23" s="20"/>
+      <c r="AS23" s="20"/>
+      <c r="AT23" s="20"/>
+      <c r="AU23" s="20"/>
+      <c r="AV23" s="20"/>
+      <c r="AW23" s="20"/>
+      <c r="AX23" s="20"/>
+      <c r="AY23" s="20"/>
+      <c r="AZ23" s="20"/>
+      <c r="BA23" s="20"/>
+      <c r="BB23" s="20"/>
+      <c r="BC23" s="20"/>
+      <c r="BD23" s="20"/>
+      <c r="BE23" s="20"/>
+      <c r="BF23" s="20"/>
+      <c r="BG23" s="20"/>
+      <c r="BH23" s="20"/>
+      <c r="BI23" s="20"/>
+      <c r="BJ23" s="20"/>
+      <c r="BK23" s="20"/>
+      <c r="BL23" s="20"/>
+      <c r="BM23" s="20"/>
+      <c r="BN23" s="20"/>
+      <c r="BO23" s="20"/>
+      <c r="BP23" s="20"/>
+      <c r="BQ23" s="20"/>
+      <c r="BR23" s="20"/>
+      <c r="BS23" s="20"/>
+      <c r="BT23" s="20"/>
+      <c r="BU23" s="20"/>
+      <c r="BV23" s="20"/>
+      <c r="BW23" s="20"/>
+      <c r="BX23" s="20"/>
+      <c r="BY23" s="20"/>
+      <c r="BZ23" s="20"/>
+      <c r="CA23" s="20"/>
+      <c r="CB23" s="20"/>
+      <c r="CC23" s="20"/>
+      <c r="CD23" s="20"/>
+      <c r="CE23" s="20"/>
+      <c r="CF23" s="20"/>
+      <c r="CG23" s="20"/>
+      <c r="CH23" s="20"/>
+      <c r="CI23" s="20"/>
+      <c r="CJ23" s="20"/>
+      <c r="CK23" s="20"/>
+      <c r="CL23" s="20"/>
+      <c r="CM23" s="20"/>
+      <c r="CN23" s="20"/>
+      <c r="CO23" s="20"/>
+      <c r="CP23" s="20"/>
+      <c r="CQ23" s="20"/>
+      <c r="CR23" s="20"/>
+      <c r="CS23" s="20"/>
+      <c r="CT23" s="20"/>
+      <c r="CU23" s="20"/>
+      <c r="CV23" s="20"/>
+      <c r="CW23" s="20"/>
+      <c r="CX23" s="20"/>
+      <c r="CY23" s="20"/>
+      <c r="CZ23" s="20"/>
+      <c r="DA23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -4041,108 +4072,108 @@
         <v/>
       </c>
       <c r="C24" s="16"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="21"/>
-      <c r="W24" s="21"/>
-      <c r="X24" s="21"/>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="21"/>
-      <c r="AA24" s="21"/>
-      <c r="AB24" s="21"/>
-      <c r="AC24" s="21"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="21"/>
-      <c r="AF24" s="21"/>
-      <c r="AG24" s="21"/>
-      <c r="AH24" s="21"/>
-      <c r="AI24" s="21"/>
-      <c r="AJ24" s="21"/>
-      <c r="AK24" s="21"/>
-      <c r="AL24" s="21"/>
-      <c r="AM24" s="21"/>
-      <c r="AN24" s="21"/>
-      <c r="AO24" s="21"/>
-      <c r="AP24" s="21"/>
-      <c r="AQ24" s="21"/>
-      <c r="AR24" s="21"/>
-      <c r="AS24" s="21"/>
-      <c r="AT24" s="21"/>
-      <c r="AU24" s="21"/>
-      <c r="AV24" s="21"/>
-      <c r="AW24" s="21"/>
-      <c r="AX24" s="21"/>
-      <c r="AY24" s="21"/>
-      <c r="AZ24" s="21"/>
-      <c r="BA24" s="21"/>
-      <c r="BB24" s="21"/>
-      <c r="BC24" s="21"/>
-      <c r="BD24" s="21"/>
-      <c r="BE24" s="21"/>
-      <c r="BF24" s="21"/>
-      <c r="BG24" s="21"/>
-      <c r="BH24" s="21"/>
-      <c r="BI24" s="21"/>
-      <c r="BJ24" s="21"/>
-      <c r="BK24" s="21"/>
-      <c r="BL24" s="21"/>
-      <c r="BM24" s="21"/>
-      <c r="BN24" s="21"/>
-      <c r="BO24" s="21"/>
-      <c r="BP24" s="21"/>
-      <c r="BQ24" s="21"/>
-      <c r="BR24" s="21"/>
-      <c r="BS24" s="21"/>
-      <c r="BT24" s="21"/>
-      <c r="BU24" s="21"/>
-      <c r="BV24" s="21"/>
-      <c r="BW24" s="21"/>
-      <c r="BX24" s="21"/>
-      <c r="BY24" s="21"/>
-      <c r="BZ24" s="21"/>
-      <c r="CA24" s="21"/>
-      <c r="CB24" s="21"/>
-      <c r="CC24" s="21"/>
-      <c r="CD24" s="21"/>
-      <c r="CE24" s="21"/>
-      <c r="CF24" s="21"/>
-      <c r="CG24" s="21"/>
-      <c r="CH24" s="21"/>
-      <c r="CI24" s="21"/>
-      <c r="CJ24" s="21"/>
-      <c r="CK24" s="21"/>
-      <c r="CL24" s="21"/>
-      <c r="CM24" s="21"/>
-      <c r="CN24" s="21"/>
-      <c r="CO24" s="21"/>
-      <c r="CP24" s="21"/>
-      <c r="CQ24" s="21"/>
-      <c r="CR24" s="21"/>
-      <c r="CS24" s="21"/>
-      <c r="CT24" s="21"/>
-      <c r="CU24" s="21"/>
-      <c r="CV24" s="21"/>
-      <c r="CW24" s="21"/>
-      <c r="CX24" s="21"/>
-      <c r="CY24" s="21"/>
-      <c r="CZ24" s="21"/>
-      <c r="DA24" s="21"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="20"/>
+      <c r="AH24" s="20"/>
+      <c r="AI24" s="20"/>
+      <c r="AJ24" s="20"/>
+      <c r="AK24" s="20"/>
+      <c r="AL24" s="20"/>
+      <c r="AM24" s="20"/>
+      <c r="AN24" s="20"/>
+      <c r="AO24" s="20"/>
+      <c r="AP24" s="20"/>
+      <c r="AQ24" s="20"/>
+      <c r="AR24" s="20"/>
+      <c r="AS24" s="20"/>
+      <c r="AT24" s="20"/>
+      <c r="AU24" s="20"/>
+      <c r="AV24" s="20"/>
+      <c r="AW24" s="20"/>
+      <c r="AX24" s="20"/>
+      <c r="AY24" s="20"/>
+      <c r="AZ24" s="20"/>
+      <c r="BA24" s="20"/>
+      <c r="BB24" s="20"/>
+      <c r="BC24" s="20"/>
+      <c r="BD24" s="20"/>
+      <c r="BE24" s="20"/>
+      <c r="BF24" s="20"/>
+      <c r="BG24" s="20"/>
+      <c r="BH24" s="20"/>
+      <c r="BI24" s="20"/>
+      <c r="BJ24" s="20"/>
+      <c r="BK24" s="20"/>
+      <c r="BL24" s="20"/>
+      <c r="BM24" s="20"/>
+      <c r="BN24" s="20"/>
+      <c r="BO24" s="20"/>
+      <c r="BP24" s="20"/>
+      <c r="BQ24" s="20"/>
+      <c r="BR24" s="20"/>
+      <c r="BS24" s="20"/>
+      <c r="BT24" s="20"/>
+      <c r="BU24" s="20"/>
+      <c r="BV24" s="20"/>
+      <c r="BW24" s="20"/>
+      <c r="BX24" s="20"/>
+      <c r="BY24" s="20"/>
+      <c r="BZ24" s="20"/>
+      <c r="CA24" s="20"/>
+      <c r="CB24" s="20"/>
+      <c r="CC24" s="20"/>
+      <c r="CD24" s="20"/>
+      <c r="CE24" s="20"/>
+      <c r="CF24" s="20"/>
+      <c r="CG24" s="20"/>
+      <c r="CH24" s="20"/>
+      <c r="CI24" s="20"/>
+      <c r="CJ24" s="20"/>
+      <c r="CK24" s="20"/>
+      <c r="CL24" s="20"/>
+      <c r="CM24" s="20"/>
+      <c r="CN24" s="20"/>
+      <c r="CO24" s="20"/>
+      <c r="CP24" s="20"/>
+      <c r="CQ24" s="20"/>
+      <c r="CR24" s="20"/>
+      <c r="CS24" s="20"/>
+      <c r="CT24" s="20"/>
+      <c r="CU24" s="20"/>
+      <c r="CV24" s="20"/>
+      <c r="CW24" s="20"/>
+      <c r="CX24" s="20"/>
+      <c r="CY24" s="20"/>
+      <c r="CZ24" s="20"/>
+      <c r="DA24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -4153,108 +4184,108 @@
         <v/>
       </c>
       <c r="C25" s="16"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="21"/>
-      <c r="AG25" s="21"/>
-      <c r="AH25" s="21"/>
-      <c r="AI25" s="21"/>
-      <c r="AJ25" s="21"/>
-      <c r="AK25" s="21"/>
-      <c r="AL25" s="21"/>
-      <c r="AM25" s="21"/>
-      <c r="AN25" s="21"/>
-      <c r="AO25" s="21"/>
-      <c r="AP25" s="21"/>
-      <c r="AQ25" s="21"/>
-      <c r="AR25" s="21"/>
-      <c r="AS25" s="21"/>
-      <c r="AT25" s="21"/>
-      <c r="AU25" s="21"/>
-      <c r="AV25" s="21"/>
-      <c r="AW25" s="21"/>
-      <c r="AX25" s="21"/>
-      <c r="AY25" s="21"/>
-      <c r="AZ25" s="21"/>
-      <c r="BA25" s="21"/>
-      <c r="BB25" s="21"/>
-      <c r="BC25" s="21"/>
-      <c r="BD25" s="21"/>
-      <c r="BE25" s="21"/>
-      <c r="BF25" s="21"/>
-      <c r="BG25" s="21"/>
-      <c r="BH25" s="21"/>
-      <c r="BI25" s="21"/>
-      <c r="BJ25" s="21"/>
-      <c r="BK25" s="21"/>
-      <c r="BL25" s="21"/>
-      <c r="BM25" s="21"/>
-      <c r="BN25" s="21"/>
-      <c r="BO25" s="21"/>
-      <c r="BP25" s="21"/>
-      <c r="BQ25" s="21"/>
-      <c r="BR25" s="21"/>
-      <c r="BS25" s="21"/>
-      <c r="BT25" s="21"/>
-      <c r="BU25" s="21"/>
-      <c r="BV25" s="21"/>
-      <c r="BW25" s="21"/>
-      <c r="BX25" s="21"/>
-      <c r="BY25" s="21"/>
-      <c r="BZ25" s="21"/>
-      <c r="CA25" s="21"/>
-      <c r="CB25" s="21"/>
-      <c r="CC25" s="21"/>
-      <c r="CD25" s="21"/>
-      <c r="CE25" s="21"/>
-      <c r="CF25" s="21"/>
-      <c r="CG25" s="21"/>
-      <c r="CH25" s="21"/>
-      <c r="CI25" s="21"/>
-      <c r="CJ25" s="21"/>
-      <c r="CK25" s="21"/>
-      <c r="CL25" s="21"/>
-      <c r="CM25" s="21"/>
-      <c r="CN25" s="21"/>
-      <c r="CO25" s="21"/>
-      <c r="CP25" s="21"/>
-      <c r="CQ25" s="21"/>
-      <c r="CR25" s="21"/>
-      <c r="CS25" s="21"/>
-      <c r="CT25" s="21"/>
-      <c r="CU25" s="21"/>
-      <c r="CV25" s="21"/>
-      <c r="CW25" s="21"/>
-      <c r="CX25" s="21"/>
-      <c r="CY25" s="21"/>
-      <c r="CZ25" s="21"/>
-      <c r="DA25" s="21"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="20"/>
+      <c r="AE25" s="20"/>
+      <c r="AF25" s="20"/>
+      <c r="AG25" s="20"/>
+      <c r="AH25" s="20"/>
+      <c r="AI25" s="20"/>
+      <c r="AJ25" s="20"/>
+      <c r="AK25" s="20"/>
+      <c r="AL25" s="20"/>
+      <c r="AM25" s="20"/>
+      <c r="AN25" s="20"/>
+      <c r="AO25" s="20"/>
+      <c r="AP25" s="20"/>
+      <c r="AQ25" s="20"/>
+      <c r="AR25" s="20"/>
+      <c r="AS25" s="20"/>
+      <c r="AT25" s="20"/>
+      <c r="AU25" s="20"/>
+      <c r="AV25" s="20"/>
+      <c r="AW25" s="20"/>
+      <c r="AX25" s="20"/>
+      <c r="AY25" s="20"/>
+      <c r="AZ25" s="20"/>
+      <c r="BA25" s="20"/>
+      <c r="BB25" s="20"/>
+      <c r="BC25" s="20"/>
+      <c r="BD25" s="20"/>
+      <c r="BE25" s="20"/>
+      <c r="BF25" s="20"/>
+      <c r="BG25" s="20"/>
+      <c r="BH25" s="20"/>
+      <c r="BI25" s="20"/>
+      <c r="BJ25" s="20"/>
+      <c r="BK25" s="20"/>
+      <c r="BL25" s="20"/>
+      <c r="BM25" s="20"/>
+      <c r="BN25" s="20"/>
+      <c r="BO25" s="20"/>
+      <c r="BP25" s="20"/>
+      <c r="BQ25" s="20"/>
+      <c r="BR25" s="20"/>
+      <c r="BS25" s="20"/>
+      <c r="BT25" s="20"/>
+      <c r="BU25" s="20"/>
+      <c r="BV25" s="20"/>
+      <c r="BW25" s="20"/>
+      <c r="BX25" s="20"/>
+      <c r="BY25" s="20"/>
+      <c r="BZ25" s="20"/>
+      <c r="CA25" s="20"/>
+      <c r="CB25" s="20"/>
+      <c r="CC25" s="20"/>
+      <c r="CD25" s="20"/>
+      <c r="CE25" s="20"/>
+      <c r="CF25" s="20"/>
+      <c r="CG25" s="20"/>
+      <c r="CH25" s="20"/>
+      <c r="CI25" s="20"/>
+      <c r="CJ25" s="20"/>
+      <c r="CK25" s="20"/>
+      <c r="CL25" s="20"/>
+      <c r="CM25" s="20"/>
+      <c r="CN25" s="20"/>
+      <c r="CO25" s="20"/>
+      <c r="CP25" s="20"/>
+      <c r="CQ25" s="20"/>
+      <c r="CR25" s="20"/>
+      <c r="CS25" s="20"/>
+      <c r="CT25" s="20"/>
+      <c r="CU25" s="20"/>
+      <c r="CV25" s="20"/>
+      <c r="CW25" s="20"/>
+      <c r="CX25" s="20"/>
+      <c r="CY25" s="20"/>
+      <c r="CZ25" s="20"/>
+      <c r="DA25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -4265,108 +4296,108 @@
         <v/>
       </c>
       <c r="C26" s="16"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
-      <c r="AE26" s="21"/>
-      <c r="AF26" s="21"/>
-      <c r="AG26" s="21"/>
-      <c r="AH26" s="21"/>
-      <c r="AI26" s="21"/>
-      <c r="AJ26" s="21"/>
-      <c r="AK26" s="21"/>
-      <c r="AL26" s="21"/>
-      <c r="AM26" s="21"/>
-      <c r="AN26" s="21"/>
-      <c r="AO26" s="21"/>
-      <c r="AP26" s="21"/>
-      <c r="AQ26" s="21"/>
-      <c r="AR26" s="21"/>
-      <c r="AS26" s="21"/>
-      <c r="AT26" s="21"/>
-      <c r="AU26" s="21"/>
-      <c r="AV26" s="21"/>
-      <c r="AW26" s="21"/>
-      <c r="AX26" s="21"/>
-      <c r="AY26" s="21"/>
-      <c r="AZ26" s="21"/>
-      <c r="BA26" s="21"/>
-      <c r="BB26" s="21"/>
-      <c r="BC26" s="21"/>
-      <c r="BD26" s="21"/>
-      <c r="BE26" s="21"/>
-      <c r="BF26" s="21"/>
-      <c r="BG26" s="21"/>
-      <c r="BH26" s="21"/>
-      <c r="BI26" s="21"/>
-      <c r="BJ26" s="21"/>
-      <c r="BK26" s="21"/>
-      <c r="BL26" s="21"/>
-      <c r="BM26" s="21"/>
-      <c r="BN26" s="21"/>
-      <c r="BO26" s="21"/>
-      <c r="BP26" s="21"/>
-      <c r="BQ26" s="21"/>
-      <c r="BR26" s="21"/>
-      <c r="BS26" s="21"/>
-      <c r="BT26" s="21"/>
-      <c r="BU26" s="21"/>
-      <c r="BV26" s="21"/>
-      <c r="BW26" s="21"/>
-      <c r="BX26" s="21"/>
-      <c r="BY26" s="21"/>
-      <c r="BZ26" s="21"/>
-      <c r="CA26" s="21"/>
-      <c r="CB26" s="21"/>
-      <c r="CC26" s="21"/>
-      <c r="CD26" s="21"/>
-      <c r="CE26" s="21"/>
-      <c r="CF26" s="21"/>
-      <c r="CG26" s="21"/>
-      <c r="CH26" s="21"/>
-      <c r="CI26" s="21"/>
-      <c r="CJ26" s="21"/>
-      <c r="CK26" s="21"/>
-      <c r="CL26" s="21"/>
-      <c r="CM26" s="21"/>
-      <c r="CN26" s="21"/>
-      <c r="CO26" s="21"/>
-      <c r="CP26" s="21"/>
-      <c r="CQ26" s="21"/>
-      <c r="CR26" s="21"/>
-      <c r="CS26" s="21"/>
-      <c r="CT26" s="21"/>
-      <c r="CU26" s="21"/>
-      <c r="CV26" s="21"/>
-      <c r="CW26" s="21"/>
-      <c r="CX26" s="21"/>
-      <c r="CY26" s="21"/>
-      <c r="CZ26" s="21"/>
-      <c r="DA26" s="21"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="20"/>
+      <c r="AD26" s="20"/>
+      <c r="AE26" s="20"/>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="20"/>
+      <c r="AH26" s="20"/>
+      <c r="AI26" s="20"/>
+      <c r="AJ26" s="20"/>
+      <c r="AK26" s="20"/>
+      <c r="AL26" s="20"/>
+      <c r="AM26" s="20"/>
+      <c r="AN26" s="20"/>
+      <c r="AO26" s="20"/>
+      <c r="AP26" s="20"/>
+      <c r="AQ26" s="20"/>
+      <c r="AR26" s="20"/>
+      <c r="AS26" s="20"/>
+      <c r="AT26" s="20"/>
+      <c r="AU26" s="20"/>
+      <c r="AV26" s="20"/>
+      <c r="AW26" s="20"/>
+      <c r="AX26" s="20"/>
+      <c r="AY26" s="20"/>
+      <c r="AZ26" s="20"/>
+      <c r="BA26" s="20"/>
+      <c r="BB26" s="20"/>
+      <c r="BC26" s="20"/>
+      <c r="BD26" s="20"/>
+      <c r="BE26" s="20"/>
+      <c r="BF26" s="20"/>
+      <c r="BG26" s="20"/>
+      <c r="BH26" s="20"/>
+      <c r="BI26" s="20"/>
+      <c r="BJ26" s="20"/>
+      <c r="BK26" s="20"/>
+      <c r="BL26" s="20"/>
+      <c r="BM26" s="20"/>
+      <c r="BN26" s="20"/>
+      <c r="BO26" s="20"/>
+      <c r="BP26" s="20"/>
+      <c r="BQ26" s="20"/>
+      <c r="BR26" s="20"/>
+      <c r="BS26" s="20"/>
+      <c r="BT26" s="20"/>
+      <c r="BU26" s="20"/>
+      <c r="BV26" s="20"/>
+      <c r="BW26" s="20"/>
+      <c r="BX26" s="20"/>
+      <c r="BY26" s="20"/>
+      <c r="BZ26" s="20"/>
+      <c r="CA26" s="20"/>
+      <c r="CB26" s="20"/>
+      <c r="CC26" s="20"/>
+      <c r="CD26" s="20"/>
+      <c r="CE26" s="20"/>
+      <c r="CF26" s="20"/>
+      <c r="CG26" s="20"/>
+      <c r="CH26" s="20"/>
+      <c r="CI26" s="20"/>
+      <c r="CJ26" s="20"/>
+      <c r="CK26" s="20"/>
+      <c r="CL26" s="20"/>
+      <c r="CM26" s="20"/>
+      <c r="CN26" s="20"/>
+      <c r="CO26" s="20"/>
+      <c r="CP26" s="20"/>
+      <c r="CQ26" s="20"/>
+      <c r="CR26" s="20"/>
+      <c r="CS26" s="20"/>
+      <c r="CT26" s="20"/>
+      <c r="CU26" s="20"/>
+      <c r="CV26" s="20"/>
+      <c r="CW26" s="20"/>
+      <c r="CX26" s="20"/>
+      <c r="CY26" s="20"/>
+      <c r="CZ26" s="20"/>
+      <c r="DA26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
@@ -4377,108 +4408,108 @@
         <v/>
       </c>
       <c r="C27" s="16"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="21"/>
-      <c r="W27" s="21"/>
-      <c r="X27" s="21"/>
-      <c r="Y27" s="21"/>
-      <c r="Z27" s="21"/>
-      <c r="AA27" s="21"/>
-      <c r="AB27" s="21"/>
-      <c r="AC27" s="21"/>
-      <c r="AD27" s="21"/>
-      <c r="AE27" s="21"/>
-      <c r="AF27" s="21"/>
-      <c r="AG27" s="21"/>
-      <c r="AH27" s="21"/>
-      <c r="AI27" s="21"/>
-      <c r="AJ27" s="21"/>
-      <c r="AK27" s="21"/>
-      <c r="AL27" s="21"/>
-      <c r="AM27" s="21"/>
-      <c r="AN27" s="21"/>
-      <c r="AO27" s="21"/>
-      <c r="AP27" s="21"/>
-      <c r="AQ27" s="21"/>
-      <c r="AR27" s="21"/>
-      <c r="AS27" s="21"/>
-      <c r="AT27" s="21"/>
-      <c r="AU27" s="21"/>
-      <c r="AV27" s="21"/>
-      <c r="AW27" s="21"/>
-      <c r="AX27" s="21"/>
-      <c r="AY27" s="21"/>
-      <c r="AZ27" s="21"/>
-      <c r="BA27" s="21"/>
-      <c r="BB27" s="21"/>
-      <c r="BC27" s="21"/>
-      <c r="BD27" s="21"/>
-      <c r="BE27" s="21"/>
-      <c r="BF27" s="21"/>
-      <c r="BG27" s="21"/>
-      <c r="BH27" s="21"/>
-      <c r="BI27" s="21"/>
-      <c r="BJ27" s="21"/>
-      <c r="BK27" s="21"/>
-      <c r="BL27" s="21"/>
-      <c r="BM27" s="21"/>
-      <c r="BN27" s="21"/>
-      <c r="BO27" s="21"/>
-      <c r="BP27" s="21"/>
-      <c r="BQ27" s="21"/>
-      <c r="BR27" s="21"/>
-      <c r="BS27" s="21"/>
-      <c r="BT27" s="21"/>
-      <c r="BU27" s="21"/>
-      <c r="BV27" s="21"/>
-      <c r="BW27" s="21"/>
-      <c r="BX27" s="21"/>
-      <c r="BY27" s="21"/>
-      <c r="BZ27" s="21"/>
-      <c r="CA27" s="21"/>
-      <c r="CB27" s="21"/>
-      <c r="CC27" s="21"/>
-      <c r="CD27" s="21"/>
-      <c r="CE27" s="21"/>
-      <c r="CF27" s="21"/>
-      <c r="CG27" s="21"/>
-      <c r="CH27" s="21"/>
-      <c r="CI27" s="21"/>
-      <c r="CJ27" s="21"/>
-      <c r="CK27" s="21"/>
-      <c r="CL27" s="21"/>
-      <c r="CM27" s="21"/>
-      <c r="CN27" s="21"/>
-      <c r="CO27" s="21"/>
-      <c r="CP27" s="21"/>
-      <c r="CQ27" s="21"/>
-      <c r="CR27" s="21"/>
-      <c r="CS27" s="21"/>
-      <c r="CT27" s="21"/>
-      <c r="CU27" s="21"/>
-      <c r="CV27" s="21"/>
-      <c r="CW27" s="21"/>
-      <c r="CX27" s="21"/>
-      <c r="CY27" s="21"/>
-      <c r="CZ27" s="21"/>
-      <c r="DA27" s="21"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AD27" s="20"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="20"/>
+      <c r="AG27" s="20"/>
+      <c r="AH27" s="20"/>
+      <c r="AI27" s="20"/>
+      <c r="AJ27" s="20"/>
+      <c r="AK27" s="20"/>
+      <c r="AL27" s="20"/>
+      <c r="AM27" s="20"/>
+      <c r="AN27" s="20"/>
+      <c r="AO27" s="20"/>
+      <c r="AP27" s="20"/>
+      <c r="AQ27" s="20"/>
+      <c r="AR27" s="20"/>
+      <c r="AS27" s="20"/>
+      <c r="AT27" s="20"/>
+      <c r="AU27" s="20"/>
+      <c r="AV27" s="20"/>
+      <c r="AW27" s="20"/>
+      <c r="AX27" s="20"/>
+      <c r="AY27" s="20"/>
+      <c r="AZ27" s="20"/>
+      <c r="BA27" s="20"/>
+      <c r="BB27" s="20"/>
+      <c r="BC27" s="20"/>
+      <c r="BD27" s="20"/>
+      <c r="BE27" s="20"/>
+      <c r="BF27" s="20"/>
+      <c r="BG27" s="20"/>
+      <c r="BH27" s="20"/>
+      <c r="BI27" s="20"/>
+      <c r="BJ27" s="20"/>
+      <c r="BK27" s="20"/>
+      <c r="BL27" s="20"/>
+      <c r="BM27" s="20"/>
+      <c r="BN27" s="20"/>
+      <c r="BO27" s="20"/>
+      <c r="BP27" s="20"/>
+      <c r="BQ27" s="20"/>
+      <c r="BR27" s="20"/>
+      <c r="BS27" s="20"/>
+      <c r="BT27" s="20"/>
+      <c r="BU27" s="20"/>
+      <c r="BV27" s="20"/>
+      <c r="BW27" s="20"/>
+      <c r="BX27" s="20"/>
+      <c r="BY27" s="20"/>
+      <c r="BZ27" s="20"/>
+      <c r="CA27" s="20"/>
+      <c r="CB27" s="20"/>
+      <c r="CC27" s="20"/>
+      <c r="CD27" s="20"/>
+      <c r="CE27" s="20"/>
+      <c r="CF27" s="20"/>
+      <c r="CG27" s="20"/>
+      <c r="CH27" s="20"/>
+      <c r="CI27" s="20"/>
+      <c r="CJ27" s="20"/>
+      <c r="CK27" s="20"/>
+      <c r="CL27" s="20"/>
+      <c r="CM27" s="20"/>
+      <c r="CN27" s="20"/>
+      <c r="CO27" s="20"/>
+      <c r="CP27" s="20"/>
+      <c r="CQ27" s="20"/>
+      <c r="CR27" s="20"/>
+      <c r="CS27" s="20"/>
+      <c r="CT27" s="20"/>
+      <c r="CU27" s="20"/>
+      <c r="CV27" s="20"/>
+      <c r="CW27" s="20"/>
+      <c r="CX27" s="20"/>
+      <c r="CY27" s="20"/>
+      <c r="CZ27" s="20"/>
+      <c r="DA27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
@@ -4489,108 +4520,108 @@
         <v/>
       </c>
       <c r="C28" s="16"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
-      <c r="Y28" s="21"/>
-      <c r="Z28" s="21"/>
-      <c r="AA28" s="21"/>
-      <c r="AB28" s="21"/>
-      <c r="AC28" s="21"/>
-      <c r="AD28" s="21"/>
-      <c r="AE28" s="21"/>
-      <c r="AF28" s="21"/>
-      <c r="AG28" s="21"/>
-      <c r="AH28" s="21"/>
-      <c r="AI28" s="21"/>
-      <c r="AJ28" s="21"/>
-      <c r="AK28" s="21"/>
-      <c r="AL28" s="21"/>
-      <c r="AM28" s="21"/>
-      <c r="AN28" s="21"/>
-      <c r="AO28" s="21"/>
-      <c r="AP28" s="21"/>
-      <c r="AQ28" s="21"/>
-      <c r="AR28" s="21"/>
-      <c r="AS28" s="21"/>
-      <c r="AT28" s="21"/>
-      <c r="AU28" s="21"/>
-      <c r="AV28" s="21"/>
-      <c r="AW28" s="21"/>
-      <c r="AX28" s="21"/>
-      <c r="AY28" s="21"/>
-      <c r="AZ28" s="21"/>
-      <c r="BA28" s="21"/>
-      <c r="BB28" s="21"/>
-      <c r="BC28" s="21"/>
-      <c r="BD28" s="21"/>
-      <c r="BE28" s="21"/>
-      <c r="BF28" s="21"/>
-      <c r="BG28" s="21"/>
-      <c r="BH28" s="21"/>
-      <c r="BI28" s="21"/>
-      <c r="BJ28" s="21"/>
-      <c r="BK28" s="21"/>
-      <c r="BL28" s="21"/>
-      <c r="BM28" s="21"/>
-      <c r="BN28" s="21"/>
-      <c r="BO28" s="21"/>
-      <c r="BP28" s="21"/>
-      <c r="BQ28" s="21"/>
-      <c r="BR28" s="21"/>
-      <c r="BS28" s="21"/>
-      <c r="BT28" s="21"/>
-      <c r="BU28" s="21"/>
-      <c r="BV28" s="21"/>
-      <c r="BW28" s="21"/>
-      <c r="BX28" s="21"/>
-      <c r="BY28" s="21"/>
-      <c r="BZ28" s="21"/>
-      <c r="CA28" s="21"/>
-      <c r="CB28" s="21"/>
-      <c r="CC28" s="21"/>
-      <c r="CD28" s="21"/>
-      <c r="CE28" s="21"/>
-      <c r="CF28" s="21"/>
-      <c r="CG28" s="21"/>
-      <c r="CH28" s="21"/>
-      <c r="CI28" s="21"/>
-      <c r="CJ28" s="21"/>
-      <c r="CK28" s="21"/>
-      <c r="CL28" s="21"/>
-      <c r="CM28" s="21"/>
-      <c r="CN28" s="21"/>
-      <c r="CO28" s="21"/>
-      <c r="CP28" s="21"/>
-      <c r="CQ28" s="21"/>
-      <c r="CR28" s="21"/>
-      <c r="CS28" s="21"/>
-      <c r="CT28" s="21"/>
-      <c r="CU28" s="21"/>
-      <c r="CV28" s="21"/>
-      <c r="CW28" s="21"/>
-      <c r="CX28" s="21"/>
-      <c r="CY28" s="21"/>
-      <c r="CZ28" s="21"/>
-      <c r="DA28" s="21"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="20"/>
+      <c r="AD28" s="20"/>
+      <c r="AE28" s="20"/>
+      <c r="AF28" s="20"/>
+      <c r="AG28" s="20"/>
+      <c r="AH28" s="20"/>
+      <c r="AI28" s="20"/>
+      <c r="AJ28" s="20"/>
+      <c r="AK28" s="20"/>
+      <c r="AL28" s="20"/>
+      <c r="AM28" s="20"/>
+      <c r="AN28" s="20"/>
+      <c r="AO28" s="20"/>
+      <c r="AP28" s="20"/>
+      <c r="AQ28" s="20"/>
+      <c r="AR28" s="20"/>
+      <c r="AS28" s="20"/>
+      <c r="AT28" s="20"/>
+      <c r="AU28" s="20"/>
+      <c r="AV28" s="20"/>
+      <c r="AW28" s="20"/>
+      <c r="AX28" s="20"/>
+      <c r="AY28" s="20"/>
+      <c r="AZ28" s="20"/>
+      <c r="BA28" s="20"/>
+      <c r="BB28" s="20"/>
+      <c r="BC28" s="20"/>
+      <c r="BD28" s="20"/>
+      <c r="BE28" s="20"/>
+      <c r="BF28" s="20"/>
+      <c r="BG28" s="20"/>
+      <c r="BH28" s="20"/>
+      <c r="BI28" s="20"/>
+      <c r="BJ28" s="20"/>
+      <c r="BK28" s="20"/>
+      <c r="BL28" s="20"/>
+      <c r="BM28" s="20"/>
+      <c r="BN28" s="20"/>
+      <c r="BO28" s="20"/>
+      <c r="BP28" s="20"/>
+      <c r="BQ28" s="20"/>
+      <c r="BR28" s="20"/>
+      <c r="BS28" s="20"/>
+      <c r="BT28" s="20"/>
+      <c r="BU28" s="20"/>
+      <c r="BV28" s="20"/>
+      <c r="BW28" s="20"/>
+      <c r="BX28" s="20"/>
+      <c r="BY28" s="20"/>
+      <c r="BZ28" s="20"/>
+      <c r="CA28" s="20"/>
+      <c r="CB28" s="20"/>
+      <c r="CC28" s="20"/>
+      <c r="CD28" s="20"/>
+      <c r="CE28" s="20"/>
+      <c r="CF28" s="20"/>
+      <c r="CG28" s="20"/>
+      <c r="CH28" s="20"/>
+      <c r="CI28" s="20"/>
+      <c r="CJ28" s="20"/>
+      <c r="CK28" s="20"/>
+      <c r="CL28" s="20"/>
+      <c r="CM28" s="20"/>
+      <c r="CN28" s="20"/>
+      <c r="CO28" s="20"/>
+      <c r="CP28" s="20"/>
+      <c r="CQ28" s="20"/>
+      <c r="CR28" s="20"/>
+      <c r="CS28" s="20"/>
+      <c r="CT28" s="20"/>
+      <c r="CU28" s="20"/>
+      <c r="CV28" s="20"/>
+      <c r="CW28" s="20"/>
+      <c r="CX28" s="20"/>
+      <c r="CY28" s="20"/>
+      <c r="CZ28" s="20"/>
+      <c r="DA28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
@@ -4601,317 +4632,317 @@
         <v/>
       </c>
       <c r="C29" s="16"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="21"/>
-      <c r="X29" s="21"/>
-      <c r="Y29" s="21"/>
-      <c r="Z29" s="21"/>
-      <c r="AA29" s="21"/>
-      <c r="AB29" s="21"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="21"/>
-      <c r="AE29" s="21"/>
-      <c r="AF29" s="21"/>
-      <c r="AG29" s="21"/>
-      <c r="AH29" s="21"/>
-      <c r="AI29" s="21"/>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="21"/>
-      <c r="AL29" s="21"/>
-      <c r="AM29" s="21"/>
-      <c r="AN29" s="21"/>
-      <c r="AO29" s="21"/>
-      <c r="AP29" s="21"/>
-      <c r="AQ29" s="21"/>
-      <c r="AR29" s="21"/>
-      <c r="AS29" s="21"/>
-      <c r="AT29" s="21"/>
-      <c r="AU29" s="21"/>
-      <c r="AV29" s="21"/>
-      <c r="AW29" s="21"/>
-      <c r="AX29" s="21"/>
-      <c r="AY29" s="21"/>
-      <c r="AZ29" s="21"/>
-      <c r="BA29" s="21"/>
-      <c r="BB29" s="21"/>
-      <c r="BC29" s="21"/>
-      <c r="BD29" s="21"/>
-      <c r="BE29" s="21"/>
-      <c r="BF29" s="21"/>
-      <c r="BG29" s="21"/>
-      <c r="BH29" s="21"/>
-      <c r="BI29" s="21"/>
-      <c r="BJ29" s="21"/>
-      <c r="BK29" s="21"/>
-      <c r="BL29" s="21"/>
-      <c r="BM29" s="21"/>
-      <c r="BN29" s="21"/>
-      <c r="BO29" s="21"/>
-      <c r="BP29" s="21"/>
-      <c r="BQ29" s="21"/>
-      <c r="BR29" s="21"/>
-      <c r="BS29" s="21"/>
-      <c r="BT29" s="21"/>
-      <c r="BU29" s="21"/>
-      <c r="BV29" s="21"/>
-      <c r="BW29" s="21"/>
-      <c r="BX29" s="21"/>
-      <c r="BY29" s="21"/>
-      <c r="BZ29" s="21"/>
-      <c r="CA29" s="21"/>
-      <c r="CB29" s="21"/>
-      <c r="CC29" s="21"/>
-      <c r="CD29" s="21"/>
-      <c r="CE29" s="21"/>
-      <c r="CF29" s="21"/>
-      <c r="CG29" s="21"/>
-      <c r="CH29" s="21"/>
-      <c r="CI29" s="21"/>
-      <c r="CJ29" s="21"/>
-      <c r="CK29" s="21"/>
-      <c r="CL29" s="21"/>
-      <c r="CM29" s="21"/>
-      <c r="CN29" s="21"/>
-      <c r="CO29" s="21"/>
-      <c r="CP29" s="21"/>
-      <c r="CQ29" s="21"/>
-      <c r="CR29" s="21"/>
-      <c r="CS29" s="21"/>
-      <c r="CT29" s="21"/>
-      <c r="CU29" s="21"/>
-      <c r="CV29" s="21"/>
-      <c r="CW29" s="21"/>
-      <c r="CX29" s="21"/>
-      <c r="CY29" s="21"/>
-      <c r="CZ29" s="21"/>
-      <c r="DA29" s="21"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="20"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="20"/>
+      <c r="AL29" s="20"/>
+      <c r="AM29" s="20"/>
+      <c r="AN29" s="20"/>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="20"/>
+      <c r="AQ29" s="20"/>
+      <c r="AR29" s="20"/>
+      <c r="AS29" s="20"/>
+      <c r="AT29" s="20"/>
+      <c r="AU29" s="20"/>
+      <c r="AV29" s="20"/>
+      <c r="AW29" s="20"/>
+      <c r="AX29" s="20"/>
+      <c r="AY29" s="20"/>
+      <c r="AZ29" s="20"/>
+      <c r="BA29" s="20"/>
+      <c r="BB29" s="20"/>
+      <c r="BC29" s="20"/>
+      <c r="BD29" s="20"/>
+      <c r="BE29" s="20"/>
+      <c r="BF29" s="20"/>
+      <c r="BG29" s="20"/>
+      <c r="BH29" s="20"/>
+      <c r="BI29" s="20"/>
+      <c r="BJ29" s="20"/>
+      <c r="BK29" s="20"/>
+      <c r="BL29" s="20"/>
+      <c r="BM29" s="20"/>
+      <c r="BN29" s="20"/>
+      <c r="BO29" s="20"/>
+      <c r="BP29" s="20"/>
+      <c r="BQ29" s="20"/>
+      <c r="BR29" s="20"/>
+      <c r="BS29" s="20"/>
+      <c r="BT29" s="20"/>
+      <c r="BU29" s="20"/>
+      <c r="BV29" s="20"/>
+      <c r="BW29" s="20"/>
+      <c r="BX29" s="20"/>
+      <c r="BY29" s="20"/>
+      <c r="BZ29" s="20"/>
+      <c r="CA29" s="20"/>
+      <c r="CB29" s="20"/>
+      <c r="CC29" s="20"/>
+      <c r="CD29" s="20"/>
+      <c r="CE29" s="20"/>
+      <c r="CF29" s="20"/>
+      <c r="CG29" s="20"/>
+      <c r="CH29" s="20"/>
+      <c r="CI29" s="20"/>
+      <c r="CJ29" s="20"/>
+      <c r="CK29" s="20"/>
+      <c r="CL29" s="20"/>
+      <c r="CM29" s="20"/>
+      <c r="CN29" s="20"/>
+      <c r="CO29" s="20"/>
+      <c r="CP29" s="20"/>
+      <c r="CQ29" s="20"/>
+      <c r="CR29" s="20"/>
+      <c r="CS29" s="20"/>
+      <c r="CT29" s="20"/>
+      <c r="CU29" s="20"/>
+      <c r="CV29" s="20"/>
+      <c r="CW29" s="20"/>
+      <c r="CX29" s="20"/>
+      <c r="CY29" s="20"/>
+      <c r="CZ29" s="20"/>
+      <c r="DA29" s="20"/>
     </row>
     <row r="30" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="15" t="str">
         <f aca="false">IF(SUM(D30:AML30)&gt;0,SUM(D30:AML30),"")</f>
         <v/>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="23"/>
-      <c r="AB30" s="23"/>
-      <c r="AC30" s="23"/>
-      <c r="AD30" s="23"/>
-      <c r="AE30" s="23"/>
-      <c r="AF30" s="23"/>
-      <c r="AG30" s="23"/>
-      <c r="AH30" s="23"/>
-      <c r="AI30" s="23"/>
-      <c r="AJ30" s="23"/>
-      <c r="AK30" s="23"/>
-      <c r="AL30" s="23"/>
-      <c r="AM30" s="23"/>
-      <c r="AN30" s="23"/>
-      <c r="AO30" s="23"/>
-      <c r="AP30" s="23"/>
-      <c r="AQ30" s="23"/>
-      <c r="AR30" s="23"/>
-      <c r="AS30" s="23"/>
-      <c r="AT30" s="23"/>
-      <c r="AU30" s="23"/>
-      <c r="AV30" s="23"/>
-      <c r="AW30" s="23"/>
-      <c r="AX30" s="23"/>
-      <c r="AY30" s="23"/>
-      <c r="AZ30" s="23"/>
-      <c r="BA30" s="23"/>
-      <c r="BB30" s="23"/>
-      <c r="BC30" s="23"/>
-      <c r="BD30" s="23"/>
-      <c r="BE30" s="23"/>
-      <c r="BF30" s="23"/>
-      <c r="BG30" s="23"/>
-      <c r="BH30" s="23"/>
-      <c r="BI30" s="23"/>
-      <c r="BJ30" s="23"/>
-      <c r="BK30" s="23"/>
-      <c r="BL30" s="23"/>
-      <c r="BM30" s="23"/>
-      <c r="BN30" s="23"/>
-      <c r="BO30" s="23"/>
-      <c r="BP30" s="23"/>
-      <c r="BQ30" s="23"/>
-      <c r="BR30" s="23"/>
-      <c r="BS30" s="23"/>
-      <c r="BT30" s="23"/>
-      <c r="BU30" s="23"/>
-      <c r="BV30" s="23"/>
-      <c r="BW30" s="23"/>
-      <c r="BX30" s="23"/>
-      <c r="BY30" s="23"/>
-      <c r="BZ30" s="23"/>
-      <c r="CA30" s="23"/>
-      <c r="CB30" s="23"/>
-      <c r="CC30" s="23"/>
-      <c r="CD30" s="23"/>
-      <c r="CE30" s="23"/>
-      <c r="CF30" s="23"/>
-      <c r="CG30" s="23"/>
-      <c r="CH30" s="23"/>
-      <c r="CI30" s="23"/>
-      <c r="CJ30" s="23"/>
-      <c r="CK30" s="23"/>
-      <c r="CL30" s="23"/>
-      <c r="CM30" s="23"/>
-      <c r="CN30" s="23"/>
-      <c r="CO30" s="23"/>
-      <c r="CP30" s="23"/>
-      <c r="CQ30" s="23"/>
-      <c r="CR30" s="23"/>
-      <c r="CS30" s="23"/>
-      <c r="CT30" s="23"/>
-      <c r="CU30" s="23"/>
-      <c r="CV30" s="23"/>
-      <c r="CW30" s="23"/>
-      <c r="CX30" s="23"/>
-      <c r="CY30" s="23"/>
-      <c r="CZ30" s="23"/>
-      <c r="DA30" s="23"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="22"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
+      <c r="AE30" s="22"/>
+      <c r="AF30" s="22"/>
+      <c r="AG30" s="22"/>
+      <c r="AH30" s="22"/>
+      <c r="AI30" s="22"/>
+      <c r="AJ30" s="22"/>
+      <c r="AK30" s="22"/>
+      <c r="AL30" s="22"/>
+      <c r="AM30" s="22"/>
+      <c r="AN30" s="22"/>
+      <c r="AO30" s="22"/>
+      <c r="AP30" s="22"/>
+      <c r="AQ30" s="22"/>
+      <c r="AR30" s="22"/>
+      <c r="AS30" s="22"/>
+      <c r="AT30" s="22"/>
+      <c r="AU30" s="22"/>
+      <c r="AV30" s="22"/>
+      <c r="AW30" s="22"/>
+      <c r="AX30" s="22"/>
+      <c r="AY30" s="22"/>
+      <c r="AZ30" s="22"/>
+      <c r="BA30" s="22"/>
+      <c r="BB30" s="22"/>
+      <c r="BC30" s="22"/>
+      <c r="BD30" s="22"/>
+      <c r="BE30" s="22"/>
+      <c r="BF30" s="22"/>
+      <c r="BG30" s="22"/>
+      <c r="BH30" s="22"/>
+      <c r="BI30" s="22"/>
+      <c r="BJ30" s="22"/>
+      <c r="BK30" s="22"/>
+      <c r="BL30" s="22"/>
+      <c r="BM30" s="22"/>
+      <c r="BN30" s="22"/>
+      <c r="BO30" s="22"/>
+      <c r="BP30" s="22"/>
+      <c r="BQ30" s="22"/>
+      <c r="BR30" s="22"/>
+      <c r="BS30" s="22"/>
+      <c r="BT30" s="22"/>
+      <c r="BU30" s="22"/>
+      <c r="BV30" s="22"/>
+      <c r="BW30" s="22"/>
+      <c r="BX30" s="22"/>
+      <c r="BY30" s="22"/>
+      <c r="BZ30" s="22"/>
+      <c r="CA30" s="22"/>
+      <c r="CB30" s="22"/>
+      <c r="CC30" s="22"/>
+      <c r="CD30" s="22"/>
+      <c r="CE30" s="22"/>
+      <c r="CF30" s="22"/>
+      <c r="CG30" s="22"/>
+      <c r="CH30" s="22"/>
+      <c r="CI30" s="22"/>
+      <c r="CJ30" s="22"/>
+      <c r="CK30" s="22"/>
+      <c r="CL30" s="22"/>
+      <c r="CM30" s="22"/>
+      <c r="CN30" s="22"/>
+      <c r="CO30" s="22"/>
+      <c r="CP30" s="22"/>
+      <c r="CQ30" s="22"/>
+      <c r="CR30" s="22"/>
+      <c r="CS30" s="22"/>
+      <c r="CT30" s="22"/>
+      <c r="CU30" s="22"/>
+      <c r="CV30" s="22"/>
+      <c r="CW30" s="22"/>
+      <c r="CX30" s="22"/>
+      <c r="CY30" s="22"/>
+      <c r="CZ30" s="22"/>
+      <c r="DA30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="str">
         <f aca="false">IF(SUM(D31:AML31)&gt;0,SUM(D31:AML31),"")</f>
         <v/>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(D32:AML32)&gt;0,SUM(D32:AML32),"")</f>
         <v/>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24"/>
+      <c r="A33" s="23"/>
       <c r="B33" s="15" t="str">
         <f aca="false">IF(SUM(D33:AML33)&gt;0,SUM(D33:AML33),"")</f>
         <v/>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24"/>
+      <c r="A34" s="23"/>
       <c r="B34" s="15" t="str">
         <f aca="false">IF(SUM(D34:AML34)&gt;0,SUM(D34:AML34),"")</f>
         <v/>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24"/>
+      <c r="A35" s="23"/>
       <c r="B35" s="15" t="str">
         <f aca="false">IF(SUM(D35:AML35)&gt;0,SUM(D35:AML35),"")</f>
         <v/>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="15" t="str">
@@ -6282,16 +6313,16 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="请输入考试分数（整数、小数，可以为负数）。" promptTitle="请输入考试分数。" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4:DX256" type="decimal">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="请勿更改。" promptTitle="请勿更改" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3:DX3 B4:B256" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="批注的内容会被当作评语。" promptTitle="提示：" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A4:A256" type="none">
       <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="notEqual" prompt="请输入考试分数（整数、小数，可以为负数）。" promptTitle="请输入考试分数。" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4:DX256" type="decimal">
+      <formula1>-256</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/src/fnschool/exam/data/score.xlsx
+++ b/src/fnschool/exam/data/score.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Larry Wei</author>
+    <author>Wei Larry</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -258,7 +258,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">开始时间：</t>
   </si>
@@ -281,115 +281,10 @@
     <t xml:space="preserve">1、拼音词语（4分）</t>
   </si>
   <si>
-    <t xml:space="preserve">2、读音（4分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3、多音字（2分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4、错别字（4分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5、字义（4分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6、字义（3分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7、积累运用（28分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8、口语交际（5分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9、课内阅读（10分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10、课外阅读（11分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11、习作：特别的_____或写人（25分）</t>
-  </si>
-  <si>
     <t xml:space="preserve">平均分</t>
   </si>
   <si>
     <t xml:space="preserve">王一</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄二</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陆三</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玉四</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鲁五</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陈六</t>
-  </si>
-  <si>
-    <t xml:space="preserve">林七</t>
-  </si>
-  <si>
-    <t xml:space="preserve">罗八</t>
-  </si>
-  <si>
-    <t xml:space="preserve">刘九</t>
-  </si>
-  <si>
-    <t xml:space="preserve">罗十</t>
-  </si>
-  <si>
-    <t xml:space="preserve">何十一</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄十二</t>
-  </si>
-  <si>
-    <t xml:space="preserve">李十三</t>
-  </si>
-  <si>
-    <t xml:space="preserve">苏十四</t>
-  </si>
-  <si>
-    <t xml:space="preserve">李十五</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陈十六</t>
-  </si>
-  <si>
-    <t xml:space="preserve">张十七</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄十八</t>
-  </si>
-  <si>
-    <t xml:space="preserve">王十九</t>
-  </si>
-  <si>
-    <t xml:space="preserve">何二十</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陆二十一</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卢二十二</t>
-  </si>
-  <si>
-    <t xml:space="preserve">韦二十三</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陆二十四</t>
-  </si>
-  <si>
-    <t xml:space="preserve">韦二十五</t>
-  </si>
-  <si>
-    <t xml:space="preserve">苏二十六</t>
   </si>
 </sst>
 </file>
@@ -505,7 +400,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -549,6 +444,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFF4000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,6 +543,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -640,23 +554,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -684,11 +594,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -700,7 +610,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -729,37 +639,6 @@
     <cellStyle name="very good" xfId="22"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <font>
-        <name val="AR PL UKai CN"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <sz val="10"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="@"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left style="mediumDashed">
-          <color rgb="FFBF0041"/>
-        </left>
-        <right style="mediumDashed">
-          <color rgb="FFBF0041"/>
-        </right>
-        <top style="mediumDashed">
-          <color rgb="FFBF0041"/>
-        </top>
-        <bottom style="mediumDashed">
-          <color rgb="FFBF0041"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <name val="Noto Sans CJK SC"/>
@@ -861,6 +740,37 @@
           <color rgb="FFBF0041"/>
         </top>
         <bottom style="thin">
+          <color rgb="FFBF0041"/>
+        </bottom>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="AR PL UKai CN"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="@"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="mediumDashed">
+          <color rgb="FFBF0041"/>
+        </left>
+        <right style="mediumDashed">
+          <color rgb="FFBF0041"/>
+        </right>
+        <top style="mediumDashed">
+          <color rgb="FFBF0041"/>
+        </top>
+        <bottom style="mediumDashed">
           <color rgb="FFBF0041"/>
         </bottom>
         <diagonal/>
@@ -1066,159 +976,139 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
       <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
       <c r="O1" s="4"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="6"/>
-      <c r="AO1" s="6"/>
-      <c r="AP1" s="6"/>
-      <c r="AQ1" s="6"/>
-      <c r="AR1" s="6"/>
-      <c r="AS1" s="6"/>
-      <c r="AT1" s="6"/>
-      <c r="AU1" s="6"/>
-      <c r="AV1" s="6"/>
-      <c r="AW1" s="6"/>
-      <c r="AX1" s="6"/>
-      <c r="AY1" s="6"/>
-      <c r="AZ1" s="6"/>
-      <c r="BA1" s="6"/>
-      <c r="BB1" s="6"/>
-      <c r="BC1" s="6"/>
-      <c r="BD1" s="6"/>
-      <c r="BE1" s="6"/>
-      <c r="BF1" s="6"/>
-      <c r="BG1" s="6"/>
-      <c r="BH1" s="6"/>
-      <c r="BI1" s="6"/>
-      <c r="BJ1" s="6"/>
-      <c r="BK1" s="6"/>
-      <c r="BL1" s="6"/>
-      <c r="BM1" s="6"/>
-      <c r="BN1" s="6"/>
-      <c r="BO1" s="6"/>
-      <c r="BP1" s="6"/>
-      <c r="BQ1" s="6"/>
-      <c r="BR1" s="6"/>
-      <c r="BS1" s="6"/>
-      <c r="BT1" s="6"/>
-      <c r="BU1" s="6"/>
-      <c r="BV1" s="6"/>
-      <c r="BW1" s="6"/>
-      <c r="BX1" s="6"/>
-      <c r="BY1" s="6"/>
-      <c r="BZ1" s="6"/>
-      <c r="CA1" s="6"/>
-      <c r="CB1" s="6"/>
-      <c r="CC1" s="6"/>
-      <c r="CD1" s="6"/>
-      <c r="CE1" s="6"/>
-      <c r="CF1" s="6"/>
-      <c r="CG1" s="6"/>
-      <c r="CH1" s="6"/>
-      <c r="CI1" s="6"/>
-      <c r="CJ1" s="6"/>
-      <c r="CK1" s="6"/>
-      <c r="CL1" s="6"/>
-      <c r="CM1" s="6"/>
-      <c r="CN1" s="6"/>
-      <c r="CO1" s="6"/>
-      <c r="CP1" s="6"/>
-      <c r="CQ1" s="6"/>
-      <c r="CR1" s="6"/>
-      <c r="CS1" s="6"/>
-      <c r="CT1" s="6"/>
-      <c r="CU1" s="6"/>
-      <c r="CV1" s="6"/>
-      <c r="CW1" s="6"/>
-      <c r="CX1" s="6"/>
-      <c r="CY1" s="6"/>
-      <c r="CZ1" s="6"/>
-      <c r="DA1" s="6"/>
-    </row>
-    <row r="2" s="11" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
+      <c r="AT1" s="7"/>
+      <c r="AU1" s="7"/>
+      <c r="AV1" s="7"/>
+      <c r="AW1" s="7"/>
+      <c r="AX1" s="7"/>
+      <c r="AY1" s="7"/>
+      <c r="AZ1" s="7"/>
+      <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
+      <c r="BC1" s="7"/>
+      <c r="BD1" s="7"/>
+      <c r="BE1" s="7"/>
+      <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
+      <c r="BH1" s="7"/>
+      <c r="BI1" s="7"/>
+      <c r="BJ1" s="7"/>
+      <c r="BK1" s="7"/>
+      <c r="BL1" s="7"/>
+      <c r="BM1" s="7"/>
+      <c r="BN1" s="7"/>
+      <c r="BO1" s="7"/>
+      <c r="BP1" s="7"/>
+      <c r="BQ1" s="7"/>
+      <c r="BR1" s="7"/>
+      <c r="BS1" s="7"/>
+      <c r="BT1" s="7"/>
+      <c r="BU1" s="7"/>
+      <c r="BV1" s="7"/>
+      <c r="BW1" s="7"/>
+      <c r="BX1" s="7"/>
+      <c r="BY1" s="7"/>
+      <c r="BZ1" s="7"/>
+      <c r="CA1" s="7"/>
+      <c r="CB1" s="7"/>
+      <c r="CC1" s="7"/>
+      <c r="CD1" s="7"/>
+      <c r="CE1" s="7"/>
+      <c r="CF1" s="7"/>
+      <c r="CG1" s="7"/>
+      <c r="CH1" s="7"/>
+      <c r="CI1" s="7"/>
+      <c r="CJ1" s="7"/>
+      <c r="CK1" s="7"/>
+      <c r="CL1" s="7"/>
+      <c r="CM1" s="7"/>
+      <c r="CN1" s="7"/>
+      <c r="CO1" s="7"/>
+      <c r="CP1" s="7"/>
+      <c r="CQ1" s="7"/>
+      <c r="CR1" s="7"/>
+      <c r="CS1" s="7"/>
+      <c r="CT1" s="7"/>
+      <c r="CU1" s="7"/>
+      <c r="CV1" s="7"/>
+      <c r="CW1" s="7"/>
+      <c r="CX1" s="7"/>
+      <c r="CY1" s="7"/>
+      <c r="CZ1" s="7"/>
+      <c r="DA1" s="7"/>
+    </row>
+    <row r="2" s="11" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="10"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
@@ -1312,7 +1202,7 @@
     </row>
     <row r="3" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B3" s="13" t="str">
         <f aca="false">IF(SUM(B4:B1027)&gt;0,AVERAGE(B4:B1027),"")</f>
@@ -1825,7 +1715,7 @@
     </row>
     <row r="4" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B4" s="15" t="str">
         <f aca="false">IF(SUM(D4:AML4)&gt;0,SUM(D4:AML4),"")</f>
@@ -1936,9 +1826,7 @@
       <c r="DA4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A5" s="4"/>
       <c r="B5" s="15" t="str">
         <f aca="false">IF(SUM(D5:AML5)&gt;0,SUM(D5:AML5),"")</f>
         <v/>
@@ -2048,9 +1936,7 @@
       <c r="DA5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A6" s="4"/>
       <c r="B6" s="15" t="str">
         <f aca="false">IF(SUM(D6:AML6)&gt;0,SUM(D6:AML6),"")</f>
         <v/>
@@ -2160,9 +2046,7 @@
       <c r="DA6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A7" s="4"/>
       <c r="B7" s="15" t="str">
         <f aca="false">IF(SUM(D7:AML7)&gt;0,SUM(D7:AML7),"")</f>
         <v/>
@@ -2272,9 +2156,7 @@
       <c r="DA7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="A8" s="4"/>
       <c r="B8" s="15" t="str">
         <f aca="false">IF(SUM(D8:AML8)&gt;0,SUM(D8:AML8),"")</f>
         <v/>
@@ -2384,9 +2266,7 @@
       <c r="DA8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="15" t="str">
         <f aca="false">IF(SUM(D9:AML9)&gt;0,SUM(D9:AML9),"")</f>
         <v/>
@@ -2496,9 +2376,7 @@
       <c r="DA9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="15" t="str">
         <f aca="false">IF(SUM(D10:AML10)&gt;0,SUM(D10:AML10),"")</f>
         <v/>
@@ -2608,9 +2486,7 @@
       <c r="DA10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="A11" s="4"/>
       <c r="B11" s="15" t="str">
         <f aca="false">IF(SUM(D11:AML11)&gt;0,SUM(D11:AML11),"")</f>
         <v/>
@@ -2720,9 +2596,7 @@
       <c r="DA11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A12" s="4"/>
       <c r="B12" s="15" t="str">
         <f aca="false">IF(SUM(D12:AML12)&gt;0,SUM(D12:AML12),"")</f>
         <v/>
@@ -2832,9 +2706,7 @@
       <c r="DA12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="15" t="str">
         <f aca="false">IF(SUM(D13:AML13)&gt;0,SUM(D13:AML13),"")</f>
         <v/>
@@ -2944,9 +2816,7 @@
       <c r="DA13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A14" s="4"/>
       <c r="B14" s="15" t="str">
         <f aca="false">IF(SUM(D14:AML14)&gt;0,SUM(D14:AML14),"")</f>
         <v/>
@@ -3056,9 +2926,7 @@
       <c r="DA14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="A15" s="4"/>
       <c r="B15" s="15" t="str">
         <f aca="false">IF(SUM(D15:AML15)&gt;0,SUM(D15:AML15),"")</f>
         <v/>
@@ -3168,9 +3036,7 @@
       <c r="DA15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A16" s="4"/>
       <c r="B16" s="15" t="str">
         <f aca="false">IF(SUM(D16:AML16)&gt;0,SUM(D16:AML16),"")</f>
         <v/>
@@ -3280,9 +3146,7 @@
       <c r="DA16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="A17" s="4"/>
       <c r="B17" s="15" t="str">
         <f aca="false">IF(SUM(D17:AML17)&gt;0,SUM(D17:AML17),"")</f>
         <v/>
@@ -3392,9 +3256,7 @@
       <c r="DA17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="A18" s="4"/>
       <c r="B18" s="15" t="str">
         <f aca="false">IF(SUM(D18:AML18)&gt;0,SUM(D18:AML18),"")</f>
         <v/>
@@ -3504,9 +3366,7 @@
       <c r="DA18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="A19" s="4"/>
       <c r="B19" s="15" t="str">
         <f aca="false">IF(SUM(D19:AML19)&gt;0,SUM(D19:AML19),"")</f>
         <v/>
@@ -3616,9 +3476,7 @@
       <c r="DA19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A20" s="4"/>
       <c r="B20" s="15" t="str">
         <f aca="false">IF(SUM(D20:AML20)&gt;0,SUM(D20:AML20),"")</f>
         <v/>
@@ -3728,9 +3586,7 @@
       <c r="DA20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="A21" s="4"/>
       <c r="B21" s="15" t="str">
         <f aca="false">IF(SUM(D21:AML21)&gt;0,SUM(D21:AML21),"")</f>
         <v/>
@@ -3840,9 +3696,7 @@
       <c r="DA21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="A22" s="4"/>
       <c r="B22" s="15" t="str">
         <f aca="false">IF(SUM(D22:AML22)&gt;0,SUM(D22:AML22),"")</f>
         <v/>
@@ -3952,9 +3806,7 @@
       <c r="DA22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="A23" s="4"/>
       <c r="B23" s="15" t="str">
         <f aca="false">IF(SUM(D23:AML23)&gt;0,SUM(D23:AML23),"")</f>
         <v/>
@@ -4064,9 +3916,7 @@
       <c r="DA23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="A24" s="4"/>
       <c r="B24" s="15" t="str">
         <f aca="false">IF(SUM(D24:AML24)&gt;0,SUM(D24:AML24),"")</f>
         <v/>
@@ -4176,9 +4026,7 @@
       <c r="DA24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A25" s="4"/>
       <c r="B25" s="15" t="str">
         <f aca="false">IF(SUM(D25:AML25)&gt;0,SUM(D25:AML25),"")</f>
         <v/>
@@ -4288,9 +4136,7 @@
       <c r="DA25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A26" s="4"/>
       <c r="B26" s="15" t="str">
         <f aca="false">IF(SUM(D26:AML26)&gt;0,SUM(D26:AML26),"")</f>
         <v/>
@@ -4400,9 +4246,7 @@
       <c r="DA26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="A27" s="4"/>
       <c r="B27" s="15" t="str">
         <f aca="false">IF(SUM(D27:AML27)&gt;0,SUM(D27:AML27),"")</f>
         <v/>
@@ -4512,9 +4356,7 @@
       <c r="DA27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="A28" s="4"/>
       <c r="B28" s="15" t="str">
         <f aca="false">IF(SUM(D28:AML28)&gt;0,SUM(D28:AML28),"")</f>
         <v/>
@@ -4624,9 +4466,7 @@
       <c r="DA28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="A29" s="4"/>
       <c r="B29" s="15" t="str">
         <f aca="false">IF(SUM(D29:AML29)&gt;0,SUM(D29:AML29),"")</f>
         <v/>
@@ -6275,29 +6115,37 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D2:XFD2">
-    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="(" dxfId="0">
+  <conditionalFormatting sqref="B3:C1048576">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>65</formula>
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>50</formula>
+      <formula>65</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0.001</formula>
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="(" dxfId="4">
       <formula>NOT(ISERROR(SEARCH("(",D2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="（" dxfId="0">
+    <cfRule type="containsText" priority="7" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="（" dxfId="4">
       <formula>NOT(ISERROR(SEARCH("（",D2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:C1048576">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>80</formula>
+  <conditionalFormatting sqref="E2:XFD2">
+    <cfRule type="containsText" priority="8" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="(" dxfId="4">
+      <formula>NOT(ISERROR(SEARCH("(",E2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>65</formula>
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>50</formula>
-      <formula>65</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>0.001</formula>
-      <formula>50</formula>
+    <cfRule type="containsText" priority="9" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="（" dxfId="4">
+      <formula>NOT(ISERROR(SEARCH("（",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -6330,8 +6178,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
